--- a/docs/d/224/inyear.xlsx
+++ b/docs/d/224/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 22-Sep-2026. Built 2026-09-23 09:04 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:13 PDT.</t>
         </is>
       </c>
     </row>
@@ -7155,13 +7155,13 @@
         </is>
       </c>
       <c r="I67" s="4" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="J67" s="4" t="n">
         <v>33</v>
       </c>
       <c r="K67" s="4" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="L67" s="4" t="inlineStr">
         <is>
@@ -7203,7 +7203,7 @@
         <v>4</v>
       </c>
       <c r="W67" s="10" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="X67" s="10" t="n">
         <v>6</v>
@@ -10536,7 +10536,7 @@
         </is>
       </c>
       <c r="E102" s="5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F102" s="6" t="n">
         <v>10</v>
@@ -10582,14 +10582,14 @@
       <c r="Q102" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="R102" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="S102" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="T102" s="9" t="n">
-        <v>0</v>
+      <c r="R102" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="S102" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="T102" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U102" s="9" t="n">
         <v>0</v>
@@ -13155,7 +13155,7 @@
         </is>
       </c>
       <c r="E129" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F129" s="6" t="n">
         <v>10</v>
@@ -13195,8 +13195,8 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P129" s="9" t="n">
-        <v>3</v>
+      <c r="P129" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Q129" s="9" t="n">
         <v>0</v>
@@ -17408,13 +17408,13 @@
         <v>5</v>
       </c>
       <c r="D23" t="n">
-        <v>1.6</v>
+        <v>2.2</v>
       </c>
       <c r="E23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F23" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -17573,13 +17573,13 @@
         <v>6</v>
       </c>
       <c r="D28" t="n">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="E28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F28" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>

--- a/docs/d/224/inyear.xlsx
+++ b/docs/d/224/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:13 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:41 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/224/inyear.xlsx
+++ b/docs/d/224/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:41 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 26-Sep-2026. Built 2026-09-27 12:40 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>280 days remain until 30 June 2027, when these scores become final.</t>
+          <t>276 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (99 days) - 18 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (95 days) - 18 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (158 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (154 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (189 days) - 87 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (185 days) - 87 clubs short</t>
         </is>
       </c>
     </row>
@@ -2347,7 +2347,7 @@
         <v>1</v>
       </c>
       <c r="U17" s="10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V17" s="9" t="n">
         <v>0</v>
@@ -2817,7 +2817,7 @@
         </is>
       </c>
       <c r="P22" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q22" s="9" t="n">
         <v>0</v>
@@ -3455,7 +3455,7 @@
         </is>
       </c>
       <c r="E29" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F29" s="6" t="n">
         <v>10</v>
@@ -3469,13 +3469,13 @@
         </is>
       </c>
       <c r="I29" s="4" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J29" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L29" s="4" t="inlineStr">
         <is>
@@ -3513,11 +3513,11 @@
       <c r="U29" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V29" s="9" t="n">
-        <v>3</v>
+      <c r="V29" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W29" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X29" s="10" t="n">
         <v>6</v>
@@ -4369,7 +4369,7 @@
         </is>
       </c>
       <c r="P38" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q38" s="9" t="n">
         <v>0</v>
@@ -4563,7 +4563,7 @@
         </is>
       </c>
       <c r="P40" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q40" s="9" t="n">
         <v>1</v>
@@ -5827,7 +5827,7 @@
         <v>1</v>
       </c>
       <c r="Q53" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R53" s="9" t="n">
         <v>0</v>
@@ -6753,7 +6753,7 @@
         </is>
       </c>
       <c r="E63" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F63" s="6" t="n">
         <v>10</v>
@@ -6797,13 +6797,13 @@
         <v>1</v>
       </c>
       <c r="Q63" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R63" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S63" s="9" t="n">
-        <v>0</v>
+      <c r="S63" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T63" s="9" t="n">
         <v>0</v>
@@ -7197,7 +7197,7 @@
         <v>1</v>
       </c>
       <c r="U67" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V67" s="10" t="n">
         <v>4</v>
@@ -7820,7 +7820,7 @@
         </is>
       </c>
       <c r="E74" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F74" s="6" t="n">
         <v>10</v>
@@ -7872,8 +7872,8 @@
       <c r="S74" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T74" s="9" t="n">
-        <v>0</v>
+      <c r="T74" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U74" s="9" t="n">
         <v>0</v>
@@ -8222,13 +8222,13 @@
         </is>
       </c>
       <c r="I78" s="4" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J78" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K78" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L78" s="4" t="inlineStr">
         <is>
@@ -8267,7 +8267,7 @@
         <v>0</v>
       </c>
       <c r="V78" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W78" s="9" t="n">
         <v>0</v>
@@ -9704,7 +9704,7 @@
         </is>
       </c>
       <c r="P93" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q93" s="10" t="n">
         <v>2</v>
@@ -10536,7 +10536,7 @@
         </is>
       </c>
       <c r="E102" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F102" s="6" t="n">
         <v>10</v>
@@ -10586,13 +10586,13 @@
         <v>2</v>
       </c>
       <c r="S102" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="T102" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U102" s="10" t="n">
         <v>2</v>
-      </c>
-      <c r="T102" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U102" s="9" t="n">
-        <v>0</v>
       </c>
       <c r="V102" s="9" t="n">
         <v>0</v>
@@ -12323,7 +12323,7 @@
         </is>
       </c>
       <c r="P120" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q120" s="9" t="n">
         <v>0</v>
@@ -12435,7 +12435,7 @@
         <v>1</v>
       </c>
       <c r="U121" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V121" s="10" t="n">
         <v>4</v>
@@ -12587,13 +12587,13 @@
         </is>
       </c>
       <c r="I123" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J123" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K123" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L123" s="8" t="inlineStr">
         <is>
@@ -12632,7 +12632,7 @@
         <v>0</v>
       </c>
       <c r="V123" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W123" s="9" t="n">
         <v>0</v>
@@ -14457,7 +14457,7 @@
         </is>
       </c>
       <c r="P142" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q142" s="9" t="n">
         <v>0</v>
@@ -16880,7 +16880,7 @@
         <v>4</v>
       </c>
       <c r="D7" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -17111,7 +17111,7 @@
         <v>4</v>
       </c>
       <c r="D14" t="n">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -17210,7 +17210,7 @@
         <v>5</v>
       </c>
       <c r="D17" t="n">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -17408,7 +17408,7 @@
         <v>5</v>
       </c>
       <c r="D23" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="E23" t="n">
         <v>1</v>

--- a/docs/d/224/inyear.xlsx
+++ b/docs/d/224/inyear.xlsx
@@ -12,7 +12,7 @@
     <sheet name="By Area" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Club Health'!$A$1:$AA$164</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Club Health'!$A$1:$AA$165</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'By Area'!$A$1:$I$34</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 26-Sep-2026. Built 2026-09-27 12:40 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 03-Oct-2026. Built 2026-10-04 12:23 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>276 days remain until 30 June 2027, when these scores become final.</t>
+          <t>269 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (95 days) - 18 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (88 days) - 18 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (154 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (147 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (185 days) - 87 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (178 days) - 74 clubs short</t>
         </is>
       </c>
     </row>
@@ -647,7 +647,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA164"/>
+  <dimension ref="A1:AA165"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -1418,7 +1418,7 @@
         </is>
       </c>
       <c r="E8" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F8" s="6" t="n">
         <v>10</v>
@@ -1488,8 +1488,8 @@
       <c r="Y8" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z8" s="9" t="n">
-        <v>0</v>
+      <c r="Z8" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA8" s="10" t="n">
         <v>1</v>
@@ -1903,7 +1903,7 @@
         </is>
       </c>
       <c r="E13" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F13" s="6" t="n">
         <v>10</v>
@@ -1944,7 +1944,7 @@
         </is>
       </c>
       <c r="P13" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q13" s="9" t="n">
         <v>0</v>
@@ -1958,8 +1958,8 @@
       <c r="T13" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U13" s="9" t="n">
-        <v>0</v>
+      <c r="U13" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V13" s="9" t="n">
         <v>1</v>
@@ -2291,7 +2291,7 @@
         </is>
       </c>
       <c r="E17" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F17" s="6" t="n">
         <v>10</v>
@@ -2335,19 +2335,19 @@
         <v>0</v>
       </c>
       <c r="Q17" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R17" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S17" s="9" t="n">
-        <v>1</v>
+      <c r="S17" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T17" s="10" t="n">
         <v>1</v>
       </c>
       <c r="U17" s="10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="V17" s="9" t="n">
         <v>0</v>
@@ -2582,7 +2582,7 @@
         </is>
       </c>
       <c r="E20" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F20" s="6" t="n">
         <v>10</v>
@@ -2652,8 +2652,8 @@
       <c r="Y20" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z20" s="9" t="n">
-        <v>0</v>
+      <c r="Z20" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA20" s="10" t="n">
         <v>1</v>
@@ -2873,7 +2873,7 @@
         </is>
       </c>
       <c r="E23" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F23" s="6" t="n">
         <v>10</v>
@@ -2928,8 +2928,8 @@
       <c r="T23" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U23" s="9" t="n">
-        <v>0</v>
+      <c r="U23" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V23" s="10" t="n">
         <v>4</v>
@@ -3017,7 +3017,7 @@
         <v>2</v>
       </c>
       <c r="R24" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S24" s="9" t="n">
         <v>1</v>
@@ -3164,7 +3164,7 @@
         </is>
       </c>
       <c r="E26" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F26" s="6" t="n">
         <v>10</v>
@@ -3234,8 +3234,8 @@
       <c r="Y26" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z26" s="9" t="n">
-        <v>0</v>
+      <c r="Z26" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA26" s="10" t="n">
         <v>1</v>
@@ -4522,7 +4522,7 @@
         </is>
       </c>
       <c r="E40" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F40" s="6" t="n">
         <v>10</v>
@@ -4574,8 +4574,8 @@
       <c r="S40" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T40" s="9" t="n">
-        <v>0</v>
+      <c r="T40" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U40" s="9" t="n">
         <v>0</v>
@@ -4716,7 +4716,7 @@
         </is>
       </c>
       <c r="E42" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F42" s="6" t="n">
         <v>10</v>
@@ -4786,8 +4786,8 @@
       <c r="Y42" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z42" s="9" t="n">
-        <v>0</v>
+      <c r="Z42" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA42" s="10" t="n">
         <v>1</v>
@@ -5007,7 +5007,7 @@
         </is>
       </c>
       <c r="E45" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F45" s="6" t="n">
         <v>10</v>
@@ -5077,8 +5077,8 @@
       <c r="Y45" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z45" s="9" t="n">
-        <v>0</v>
+      <c r="Z45" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA45" s="10" t="n">
         <v>1</v>
@@ -5783,7 +5783,7 @@
         </is>
       </c>
       <c r="E53" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F53" s="6" t="n">
         <v>10</v>
@@ -5826,8 +5826,8 @@
       <c r="P53" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="Q53" s="9" t="n">
-        <v>1</v>
+      <c r="Q53" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R53" s="9" t="n">
         <v>0</v>
@@ -5835,8 +5835,8 @@
       <c r="S53" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T53" s="9" t="n">
-        <v>0</v>
+      <c r="T53" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U53" s="9" t="n">
         <v>0</v>
@@ -5853,8 +5853,8 @@
       <c r="Y53" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z53" s="9" t="n">
-        <v>0</v>
+      <c r="Z53" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA53" s="10" t="n">
         <v>1</v>
@@ -5880,7 +5880,7 @@
         </is>
       </c>
       <c r="E54" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F54" s="6" t="n">
         <v>10</v>
@@ -5950,8 +5950,8 @@
       <c r="Y54" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z54" s="9" t="n">
-        <v>0</v>
+      <c r="Z54" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA54" s="10" t="n">
         <v>1</v>
@@ -6712,7 +6712,7 @@
         <v>1</v>
       </c>
       <c r="U62" s="10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="V62" s="9" t="n">
         <v>0</v>
@@ -7088,7 +7088,7 @@
         <v>1</v>
       </c>
       <c r="Q66" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R66" s="9" t="n">
         <v>0</v>
@@ -7432,7 +7432,7 @@
         </is>
       </c>
       <c r="E70" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F70" s="6" t="n">
         <v>10</v>
@@ -7487,8 +7487,8 @@
       <c r="T70" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U70" s="9" t="n">
-        <v>0</v>
+      <c r="U70" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V70" s="9" t="n">
         <v>2</v>
@@ -7529,7 +7529,7 @@
         </is>
       </c>
       <c r="E71" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F71" s="6" t="n">
         <v>10</v>
@@ -7570,7 +7570,7 @@
         </is>
       </c>
       <c r="P71" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q71" s="9" t="n">
         <v>0</v>
@@ -7581,8 +7581,8 @@
       <c r="S71" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T71" s="9" t="n">
-        <v>0</v>
+      <c r="T71" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U71" s="9" t="n">
         <v>0</v>
@@ -7861,7 +7861,7 @@
         </is>
       </c>
       <c r="P74" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q74" s="9" t="n">
         <v>0</v>
@@ -8111,7 +8111,7 @@
         </is>
       </c>
       <c r="E77" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F77" s="6" t="n">
         <v>10</v>
@@ -8163,8 +8163,8 @@
       <c r="S77" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="T77" s="9" t="n">
-        <v>0</v>
+      <c r="T77" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U77" s="9" t="n">
         <v>0</v>
@@ -8499,7 +8499,7 @@
         </is>
       </c>
       <c r="E81" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F81" s="6" t="n">
         <v>10</v>
@@ -8551,8 +8551,8 @@
       <c r="S81" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T81" s="9" t="n">
-        <v>0</v>
+      <c r="T81" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U81" s="9" t="n">
         <v>0</v>
@@ -8782,15 +8782,15 @@
         </is>
       </c>
       <c r="C84" s="4" t="n">
-        <v>3281416</v>
+        <v>28680970</v>
       </c>
       <c r="D84" s="4" t="inlineStr">
         <is>
-          <t>Central Delhi Toastmasters Club</t>
+          <t>Bicaps Communicators Toastmasters Club</t>
         </is>
       </c>
       <c r="E84" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F84" s="6" t="n">
         <v>10</v>
@@ -8804,25 +8804,25 @@
         </is>
       </c>
       <c r="I84" s="4" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="J84" s="4" t="n">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="K84" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L84" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-4</v>
+      </c>
+      <c r="L84" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M84" s="7" t="n">
-        <v>46387</v>
+        <v>46446</v>
       </c>
       <c r="N84" s="4" t="inlineStr">
         <is>
-          <t>Officer list on time</t>
+          <t>Officers trained Nov-Feb</t>
         </is>
       </c>
       <c r="O84" s="8" t="inlineStr">
@@ -8831,7 +8831,7 @@
         </is>
       </c>
       <c r="P84" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q84" s="9" t="n">
         <v>0</v>
@@ -8840,7 +8840,7 @@
         <v>0</v>
       </c>
       <c r="S84" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T84" s="9" t="n">
         <v>0</v>
@@ -8849,13 +8849,13 @@
         <v>0</v>
       </c>
       <c r="V84" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="W84" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X84" s="10" t="n">
-        <v>4</v>
+      <c r="X84" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Y84" s="9" t="n">
         <v>0</v>
@@ -8863,8 +8863,8 @@
       <c r="Z84" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="AA84" s="9" t="n">
-        <v>0</v>
+      <c r="AA84" s="10" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="85">
@@ -8879,15 +8879,15 @@
         </is>
       </c>
       <c r="C85" s="4" t="n">
-        <v>1459483</v>
+        <v>3281416</v>
       </c>
       <c r="D85" s="4" t="inlineStr">
         <is>
-          <t>East Delhi Toastmasters Club</t>
+          <t>Central Delhi Toastmasters Club</t>
         </is>
       </c>
       <c r="E85" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F85" s="6" t="n">
         <v>10</v>
@@ -8901,13 +8901,13 @@
         </is>
       </c>
       <c r="I85" s="4" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="J85" s="4" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="K85" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L85" s="4" t="inlineStr">
         <is>
@@ -8915,11 +8915,11 @@
         </is>
       </c>
       <c r="M85" s="7" t="n">
-        <v>46446</v>
+        <v>46387</v>
       </c>
       <c r="N85" s="4" t="inlineStr">
         <is>
-          <t>Officers trained Nov-Feb</t>
+          <t>Officer list on time</t>
         </is>
       </c>
       <c r="O85" s="8" t="inlineStr">
@@ -8931,13 +8931,13 @@
         <v>1</v>
       </c>
       <c r="Q85" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R85" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S85" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T85" s="9" t="n">
         <v>0</v>
@@ -8945,8 +8945,8 @@
       <c r="U85" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V85" s="10" t="n">
-        <v>4</v>
+      <c r="V85" s="9" t="n">
+        <v>3</v>
       </c>
       <c r="W85" s="9" t="n">
         <v>0</v>
@@ -8960,8 +8960,8 @@
       <c r="Z85" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="AA85" s="10" t="n">
-        <v>1</v>
+      <c r="AA85" s="9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="86">
@@ -8976,15 +8976,15 @@
         </is>
       </c>
       <c r="C86" s="4" t="n">
-        <v>5346753</v>
+        <v>1459483</v>
       </c>
       <c r="D86" s="4" t="inlineStr">
         <is>
-          <t>Toastmasters Club of Speaking and Leadership</t>
+          <t>East Delhi Toastmasters Club</t>
         </is>
       </c>
       <c r="E86" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F86" s="6" t="n">
         <v>10</v>
@@ -8998,17 +8998,17 @@
         </is>
       </c>
       <c r="I86" s="4" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="J86" s="4" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="K86" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L86" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>4</v>
+      </c>
+      <c r="L86" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M86" s="7" t="n">
@@ -9025,10 +9025,10 @@
         </is>
       </c>
       <c r="P86" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q86" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R86" s="9" t="n">
         <v>0</v>
@@ -9036,26 +9036,26 @@
       <c r="S86" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T86" s="9" t="n">
-        <v>0</v>
+      <c r="T86" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U86" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V86" s="9" t="n">
-        <v>2</v>
+      <c r="V86" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W86" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X86" s="10" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Y86" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z86" s="9" t="n">
-        <v>0</v>
+      <c r="Z86" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA86" s="10" t="n">
         <v>1</v>
@@ -9073,35 +9073,35 @@
         </is>
       </c>
       <c r="C87" s="4" t="n">
-        <v>5477602</v>
+        <v>5346753</v>
       </c>
       <c r="D87" s="4" t="inlineStr">
         <is>
-          <t>Toastmasters of Delhi</t>
+          <t>Toastmasters Club of Speaking and Leadership</t>
         </is>
       </c>
       <c r="E87" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F87" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="G87" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="H87" s="4" t="inlineStr">
+        <is>
+          <t>Smedley</t>
+        </is>
+      </c>
+      <c r="I87" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="J87" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="K87" s="4" t="n">
         <v>2</v>
-      </c>
-      <c r="F87" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="G87" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="H87" s="4" t="inlineStr">
-        <is>
-          <t>Smedley</t>
-        </is>
-      </c>
-      <c r="I87" s="4" t="n">
-        <v>16</v>
-      </c>
-      <c r="J87" s="4" t="n">
-        <v>12</v>
-      </c>
-      <c r="K87" s="4" t="n">
-        <v>4</v>
       </c>
       <c r="L87" s="8" t="inlineStr">
         <is>
@@ -9139,14 +9139,14 @@
       <c r="U87" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V87" s="10" t="n">
-        <v>4</v>
+      <c r="V87" s="9" t="n">
+        <v>2</v>
       </c>
       <c r="W87" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X87" s="10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y87" s="9" t="n">
         <v>0</v>
@@ -9166,19 +9166,19 @@
       </c>
       <c r="B88" s="4" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>01</t>
         </is>
       </c>
       <c r="C88" s="4" t="n">
-        <v>5700331</v>
+        <v>5477602</v>
       </c>
       <c r="D88" s="4" t="inlineStr">
         <is>
-          <t>Delhi Toastmasters</t>
+          <t>Toastmasters of Delhi</t>
         </is>
       </c>
       <c r="E88" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F88" s="6" t="n">
         <v>10</v>
@@ -9192,17 +9192,17 @@
         </is>
       </c>
       <c r="I88" s="4" t="n">
-        <v>55</v>
+        <v>16</v>
       </c>
       <c r="J88" s="4" t="n">
-        <v>43</v>
+        <v>12</v>
       </c>
       <c r="K88" s="4" t="n">
-        <v>12</v>
-      </c>
-      <c r="L88" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>4</v>
+      </c>
+      <c r="L88" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M88" s="7" t="n">
@@ -9219,7 +9219,7 @@
         </is>
       </c>
       <c r="P88" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q88" s="9" t="n">
         <v>0</v>
@@ -9239,11 +9239,11 @@
       <c r="V88" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W88" s="10" t="n">
-        <v>8</v>
+      <c r="W88" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="X88" s="10" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Y88" s="9" t="n">
         <v>0</v>
@@ -9267,11 +9267,11 @@
         </is>
       </c>
       <c r="C89" s="4" t="n">
-        <v>28677848</v>
+        <v>5700331</v>
       </c>
       <c r="D89" s="4" t="inlineStr">
         <is>
-          <t>Janak Puri Toastmasters Club</t>
+          <t>Delhi Toastmasters</t>
         </is>
       </c>
       <c r="E89" s="5" t="n">
@@ -9289,13 +9289,13 @@
         </is>
       </c>
       <c r="I89" s="4" t="n">
-        <v>25</v>
+        <v>58</v>
       </c>
       <c r="J89" s="4" t="n">
-        <v>17</v>
+        <v>43</v>
       </c>
       <c r="K89" s="4" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="L89" s="4" t="inlineStr">
         <is>
@@ -9316,7 +9316,7 @@
         </is>
       </c>
       <c r="P89" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q89" s="9" t="n">
         <v>0</v>
@@ -9337,10 +9337,10 @@
         <v>4</v>
       </c>
       <c r="W89" s="10" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="X89" s="10" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="Y89" s="9" t="n">
         <v>0</v>
@@ -9364,15 +9364,15 @@
         </is>
       </c>
       <c r="C90" s="4" t="n">
-        <v>3123534</v>
+        <v>28677848</v>
       </c>
       <c r="D90" s="4" t="inlineStr">
         <is>
-          <t>North Spark Toastmasters Club</t>
+          <t>Janak Puri Toastmasters Club</t>
         </is>
       </c>
       <c r="E90" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F90" s="6" t="n">
         <v>10</v>
@@ -9386,13 +9386,13 @@
         </is>
       </c>
       <c r="I90" s="4" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="J90" s="4" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="K90" s="4" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="L90" s="4" t="inlineStr">
         <is>
@@ -9433,8 +9433,8 @@
       <c r="V90" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W90" s="9" t="n">
-        <v>1</v>
+      <c r="W90" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="X90" s="10" t="n">
         <v>4</v>
@@ -9442,8 +9442,8 @@
       <c r="Y90" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z90" s="9" t="n">
-        <v>0</v>
+      <c r="Z90" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA90" s="10" t="n">
         <v>1</v>
@@ -9461,15 +9461,15 @@
         </is>
       </c>
       <c r="C91" s="4" t="n">
-        <v>7827937</v>
+        <v>3123534</v>
       </c>
       <c r="D91" s="4" t="inlineStr">
         <is>
-          <t>Toastmasters Club of Storytellers</t>
+          <t>North Spark Toastmasters Club</t>
         </is>
       </c>
       <c r="E91" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F91" s="6" t="n">
         <v>10</v>
@@ -9483,17 +9483,17 @@
         </is>
       </c>
       <c r="I91" s="4" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="J91" s="4" t="n">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="K91" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="L91" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>5</v>
+      </c>
+      <c r="L91" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M91" s="7" t="n">
@@ -9513,7 +9513,7 @@
         <v>0</v>
       </c>
       <c r="Q91" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R91" s="9" t="n">
         <v>0</v>
@@ -9531,16 +9531,16 @@
         <v>4</v>
       </c>
       <c r="W91" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X91" s="10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Y91" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z91" s="10" t="n">
-        <v>1</v>
+      <c r="Z91" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA91" s="10" t="n">
         <v>1</v>
@@ -9554,43 +9554,43 @@
       </c>
       <c r="B92" s="4" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>02</t>
         </is>
       </c>
       <c r="C92" s="4" t="n">
-        <v>4892008</v>
+        <v>7827937</v>
       </c>
       <c r="D92" s="4" t="inlineStr">
         <is>
-          <t>Delhi One Toastmasters</t>
+          <t>Toastmasters Club of Storytellers</t>
         </is>
       </c>
       <c r="E92" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F92" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="G92" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="H92" s="4" t="inlineStr">
+        <is>
+          <t>Smedley</t>
+        </is>
+      </c>
+      <c r="I92" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="J92" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="K92" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="F92" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="G92" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="H92" s="4" t="inlineStr">
-        <is>
-          <t>Smedley</t>
-        </is>
-      </c>
-      <c r="I92" s="4" t="n">
-        <v>39</v>
-      </c>
-      <c r="J92" s="4" t="n">
-        <v>31</v>
-      </c>
-      <c r="K92" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="L92" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+      <c r="L92" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M92" s="7" t="n">
@@ -9607,16 +9607,16 @@
         </is>
       </c>
       <c r="P92" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q92" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R92" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S92" s="10" t="n">
-        <v>2</v>
+      <c r="S92" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="T92" s="9" t="n">
         <v>0</v>
@@ -9627,11 +9627,11 @@
       <c r="V92" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W92" s="10" t="n">
-        <v>4</v>
+      <c r="W92" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="X92" s="10" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Y92" s="9" t="n">
         <v>0</v>
@@ -9655,15 +9655,15 @@
         </is>
       </c>
       <c r="C93" s="4" t="n">
-        <v>858173</v>
+        <v>4892008</v>
       </c>
       <c r="D93" s="4" t="inlineStr">
         <is>
-          <t>Invictus Toastmasters</t>
+          <t>Delhi One Toastmasters</t>
         </is>
       </c>
       <c r="E93" s="5" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F93" s="6" t="n">
         <v>10</v>
@@ -9677,13 +9677,13 @@
         </is>
       </c>
       <c r="I93" s="4" t="n">
+        <v>39</v>
+      </c>
+      <c r="J93" s="4" t="n">
         <v>31</v>
       </c>
-      <c r="J93" s="4" t="n">
-        <v>27</v>
-      </c>
       <c r="K93" s="4" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="L93" s="4" t="inlineStr">
         <is>
@@ -9706,29 +9706,29 @@
       <c r="P93" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="Q93" s="10" t="n">
+      <c r="Q93" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R93" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S93" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="R93" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S93" s="10" t="n">
-        <v>5</v>
-      </c>
-      <c r="T93" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U93" s="10" t="n">
-        <v>1</v>
+      <c r="T93" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U93" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="V93" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W93" s="9" t="n">
-        <v>0</v>
+      <c r="W93" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="X93" s="10" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y93" s="9" t="n">
         <v>0</v>
@@ -9752,15 +9752,15 @@
         </is>
       </c>
       <c r="C94" s="4" t="n">
-        <v>5749303</v>
+        <v>858173</v>
       </c>
       <c r="D94" s="4" t="inlineStr">
         <is>
-          <t>North Delhi Toastmasters Club</t>
+          <t>Invictus Toastmasters</t>
         </is>
       </c>
       <c r="E94" s="5" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F94" s="6" t="n">
         <v>10</v>
@@ -9774,17 +9774,17 @@
         </is>
       </c>
       <c r="I94" s="4" t="n">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="J94" s="4" t="n">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="K94" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L94" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>4</v>
+      </c>
+      <c r="L94" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M94" s="7" t="n">
@@ -9801,37 +9801,37 @@
         </is>
       </c>
       <c r="P94" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q94" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="R94" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S94" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="T94" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U94" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V94" s="9" t="n">
-        <v>1</v>
+      <c r="R94" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="S94" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T94" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U94" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="V94" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W94" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X94" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Y94" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z94" s="9" t="n">
-        <v>0</v>
+      <c r="Z94" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA94" s="10" t="n">
         <v>1</v>
@@ -9849,15 +9849,15 @@
         </is>
       </c>
       <c r="C95" s="4" t="n">
-        <v>3936</v>
+        <v>5749303</v>
       </c>
       <c r="D95" s="4" t="inlineStr">
         <is>
-          <t>Toastmasters Club of New Delhi</t>
+          <t>North Delhi Toastmasters Club</t>
         </is>
       </c>
       <c r="E95" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F95" s="6" t="n">
         <v>10</v>
@@ -9871,17 +9871,17 @@
         </is>
       </c>
       <c r="I95" s="4" t="n">
-        <v>49</v>
+        <v>14</v>
       </c>
       <c r="J95" s="4" t="n">
-        <v>44</v>
+        <v>13</v>
       </c>
       <c r="K95" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="L95" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>1</v>
+      </c>
+      <c r="L95" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M95" s="7" t="n">
@@ -9898,16 +9898,16 @@
         </is>
       </c>
       <c r="P95" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q95" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
+      </c>
+      <c r="Q95" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R95" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S95" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T95" s="9" t="n">
         <v>0</v>
@@ -9915,20 +9915,20 @@
       <c r="U95" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V95" s="10" t="n">
+      <c r="V95" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="W95" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X95" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W95" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="X95" s="10" t="n">
-        <v>7</v>
-      </c>
       <c r="Y95" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z95" s="10" t="n">
-        <v>1</v>
+      <c r="Z95" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA95" s="10" t="n">
         <v>1</v>
@@ -9942,19 +9942,19 @@
       </c>
       <c r="B96" s="4" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>03</t>
         </is>
       </c>
       <c r="C96" s="4" t="n">
-        <v>2959367</v>
+        <v>3936</v>
       </c>
       <c r="D96" s="4" t="inlineStr">
         <is>
-          <t>Leaders Connect Toastmasters Club</t>
+          <t>Toastmasters Club of New Delhi</t>
         </is>
       </c>
       <c r="E96" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F96" s="6" t="n">
         <v>10</v>
@@ -9968,17 +9968,17 @@
         </is>
       </c>
       <c r="I96" s="4" t="n">
-        <v>17</v>
+        <v>49</v>
       </c>
       <c r="J96" s="4" t="n">
-        <v>14</v>
+        <v>44</v>
       </c>
       <c r="K96" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L96" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>5</v>
+      </c>
+      <c r="L96" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M96" s="7" t="n">
@@ -10012,20 +10012,20 @@
       <c r="U96" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V96" s="9" t="n">
-        <v>3</v>
+      <c r="V96" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W96" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X96" s="9" t="n">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="X96" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="Y96" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z96" s="9" t="n">
-        <v>0</v>
+      <c r="Z96" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA96" s="10" t="n">
         <v>1</v>
@@ -10043,39 +10043,39 @@
         </is>
       </c>
       <c r="C97" s="4" t="n">
-        <v>7878891</v>
+        <v>2959367</v>
       </c>
       <c r="D97" s="4" t="inlineStr">
         <is>
-          <t>Step Up Dwarka Toastmasters Club</t>
+          <t>Leaders Connect Toastmasters Club</t>
         </is>
       </c>
       <c r="E97" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F97" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="G97" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="H97" s="4" t="inlineStr">
+        <is>
+          <t>Smedley</t>
+        </is>
+      </c>
+      <c r="I97" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="J97" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="K97" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="F97" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="G97" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="H97" s="4" t="inlineStr">
-        <is>
-          <t>Smedley</t>
-        </is>
-      </c>
-      <c r="I97" s="4" t="n">
-        <v>31</v>
-      </c>
-      <c r="J97" s="4" t="n">
-        <v>22</v>
-      </c>
-      <c r="K97" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="L97" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+      <c r="L97" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M97" s="7" t="n">
@@ -10092,10 +10092,10 @@
         </is>
       </c>
       <c r="P97" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q97" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R97" s="9" t="n">
         <v>0</v>
@@ -10109,20 +10109,20 @@
       <c r="U97" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V97" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="W97" s="10" t="n">
-        <v>5</v>
-      </c>
-      <c r="X97" s="10" t="n">
-        <v>4</v>
+      <c r="V97" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="W97" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X97" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="Y97" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z97" s="10" t="n">
-        <v>1</v>
+      <c r="Z97" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA97" s="10" t="n">
         <v>1</v>
@@ -10140,15 +10140,15 @@
         </is>
       </c>
       <c r="C98" s="4" t="n">
-        <v>996285</v>
+        <v>7878891</v>
       </c>
       <c r="D98" s="4" t="inlineStr">
         <is>
-          <t>Toastmasters Club of Dwarka</t>
+          <t>Step Up Dwarka Toastmasters Club</t>
         </is>
       </c>
       <c r="E98" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F98" s="6" t="n">
         <v>10</v>
@@ -10162,13 +10162,13 @@
         </is>
       </c>
       <c r="I98" s="4" t="n">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="J98" s="4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K98" s="4" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="L98" s="4" t="inlineStr">
         <is>
@@ -10192,7 +10192,7 @@
         <v>1</v>
       </c>
       <c r="Q98" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R98" s="9" t="n">
         <v>0</v>
@@ -10209,11 +10209,11 @@
       <c r="V98" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W98" s="9" t="n">
-        <v>0</v>
+      <c r="W98" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="X98" s="10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Y98" s="9" t="n">
         <v>0</v>
@@ -10237,35 +10237,35 @@
         </is>
       </c>
       <c r="C99" s="4" t="n">
-        <v>1574616</v>
+        <v>996285</v>
       </c>
       <c r="D99" s="4" t="inlineStr">
         <is>
-          <t>Toastmasters Club of West Delhi</t>
+          <t>Toastmasters Club of Dwarka</t>
         </is>
       </c>
       <c r="E99" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F99" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="G99" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="H99" s="4" t="inlineStr">
+        <is>
+          <t>Smedley</t>
+        </is>
+      </c>
+      <c r="I99" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="J99" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="K99" s="4" t="n">
         <v>4</v>
-      </c>
-      <c r="F99" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="G99" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="H99" s="4" t="inlineStr">
-        <is>
-          <t>Smedley</t>
-        </is>
-      </c>
-      <c r="I99" s="4" t="n">
-        <v>43</v>
-      </c>
-      <c r="J99" s="4" t="n">
-        <v>33</v>
-      </c>
-      <c r="K99" s="4" t="n">
-        <v>10</v>
       </c>
       <c r="L99" s="4" t="inlineStr">
         <is>
@@ -10297,8 +10297,8 @@
       <c r="S99" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T99" s="10" t="n">
-        <v>1</v>
+      <c r="T99" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U99" s="9" t="n">
         <v>0</v>
@@ -10306,11 +10306,11 @@
       <c r="V99" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W99" s="10" t="n">
-        <v>6</v>
+      <c r="W99" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="X99" s="10" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Y99" s="9" t="n">
         <v>0</v>
@@ -10325,24 +10325,24 @@
     <row r="100">
       <c r="A100" s="4" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>E</t>
         </is>
       </c>
       <c r="B100" s="4" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>04</t>
         </is>
       </c>
       <c r="C100" s="4" t="n">
-        <v>6044728</v>
+        <v>1574616</v>
       </c>
       <c r="D100" s="4" t="inlineStr">
         <is>
-          <t>Lucknow Toastmasters Club</t>
+          <t>Toastmasters Club of West Delhi</t>
         </is>
       </c>
       <c r="E100" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F100" s="6" t="n">
         <v>10</v>
@@ -10356,10 +10356,10 @@
         </is>
       </c>
       <c r="I100" s="4" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="J100" s="4" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="K100" s="4" t="n">
         <v>10</v>
@@ -10394,8 +10394,8 @@
       <c r="S100" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T100" s="9" t="n">
-        <v>0</v>
+      <c r="T100" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U100" s="9" t="n">
         <v>0</v>
@@ -10431,15 +10431,15 @@
         </is>
       </c>
       <c r="C101" s="4" t="n">
-        <v>28679131</v>
+        <v>6044728</v>
       </c>
       <c r="D101" s="4" t="inlineStr">
         <is>
-          <t>Renukoot Toastmasters Club</t>
+          <t>Lucknow Toastmasters Club</t>
         </is>
       </c>
       <c r="E101" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F101" s="6" t="n">
         <v>10</v>
@@ -10453,13 +10453,13 @@
         </is>
       </c>
       <c r="I101" s="4" t="n">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="J101" s="4" t="n">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="K101" s="4" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L101" s="4" t="inlineStr">
         <is>
@@ -10480,7 +10480,7 @@
         </is>
       </c>
       <c r="P101" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q101" s="9" t="n">
         <v>0</v>
@@ -10497,20 +10497,20 @@
       <c r="U101" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V101" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W101" s="9" t="n">
-        <v>0</v>
+      <c r="V101" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W101" s="10" t="n">
+        <v>6</v>
       </c>
       <c r="X101" s="10" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="Y101" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z101" s="9" t="n">
-        <v>0</v>
+      <c r="Z101" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA101" s="10" t="n">
         <v>1</v>
@@ -10528,15 +10528,15 @@
         </is>
       </c>
       <c r="C102" s="4" t="n">
-        <v>28677670</v>
+        <v>28679131</v>
       </c>
       <c r="D102" s="4" t="inlineStr">
         <is>
-          <t>SRMS Toastmasters Club</t>
+          <t>Renukoot Toastmasters Club</t>
         </is>
       </c>
       <c r="E102" s="5" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F102" s="6" t="n">
         <v>10</v>
@@ -10550,17 +10550,17 @@
         </is>
       </c>
       <c r="I102" s="4" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="J102" s="4" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="K102" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L102" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="L102" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M102" s="7" t="n">
@@ -10576,32 +10576,32 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P102" s="10" t="n">
-        <v>5</v>
-      </c>
-      <c r="Q102" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="R102" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="S102" s="10" t="n">
+      <c r="P102" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q102" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R102" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S102" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T102" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U102" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V102" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W102" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X102" s="10" t="n">
         <v>4</v>
-      </c>
-      <c r="T102" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U102" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="V102" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W102" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X102" s="10" t="n">
-        <v>7</v>
       </c>
       <c r="Y102" s="9" t="n">
         <v>0</v>
@@ -10625,15 +10625,15 @@
         </is>
       </c>
       <c r="C103" s="4" t="n">
-        <v>7870082</v>
+        <v>28677670</v>
       </c>
       <c r="D103" s="4" t="inlineStr">
         <is>
-          <t>Toastmasters Club of Lucknow</t>
+          <t>SRMS Toastmasters Club</t>
         </is>
       </c>
       <c r="E103" s="5" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F103" s="6" t="n">
         <v>10</v>
@@ -10647,17 +10647,17 @@
         </is>
       </c>
       <c r="I103" s="4" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="J103" s="4" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="K103" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L103" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+      <c r="L103" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M103" s="7" t="n">
@@ -10673,23 +10673,23 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P103" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q103" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="R103" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S103" s="9" t="n">
-        <v>0</v>
+      <c r="P103" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q103" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="R103" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="S103" s="10" t="n">
+        <v>6</v>
       </c>
       <c r="T103" s="10" t="n">
         <v>1</v>
       </c>
       <c r="U103" s="10" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="V103" s="9" t="n">
         <v>0</v>
@@ -10703,8 +10703,8 @@
       <c r="Y103" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z103" s="10" t="n">
-        <v>1</v>
+      <c r="Z103" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA103" s="10" t="n">
         <v>1</v>
@@ -10722,15 +10722,15 @@
         </is>
       </c>
       <c r="C104" s="4" t="n">
-        <v>28676433</v>
+        <v>7870082</v>
       </c>
       <c r="D104" s="4" t="inlineStr">
         <is>
-          <t>UGI Toastmasters Club</t>
+          <t>Toastmasters Club of Lucknow</t>
         </is>
       </c>
       <c r="E104" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F104" s="6" t="n">
         <v>10</v>
@@ -10744,10 +10744,10 @@
         </is>
       </c>
       <c r="I104" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J104" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K104" s="4" t="n">
         <v>0</v>
@@ -10782,11 +10782,11 @@
       <c r="S104" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T104" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U104" s="9" t="n">
-        <v>0</v>
+      <c r="T104" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U104" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="V104" s="9" t="n">
         <v>0</v>
@@ -10800,8 +10800,8 @@
       <c r="Y104" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z104" s="9" t="n">
-        <v>0</v>
+      <c r="Z104" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA104" s="10" t="n">
         <v>1</v>
@@ -10815,19 +10815,19 @@
       </c>
       <c r="B105" s="4" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>01</t>
         </is>
       </c>
       <c r="C105" s="4" t="n">
-        <v>28677813</v>
+        <v>28676433</v>
       </c>
       <c r="D105" s="4" t="inlineStr">
         <is>
-          <t>Idemia Toastmasters Club</t>
+          <t>UGI Toastmasters Club</t>
         </is>
       </c>
       <c r="E105" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F105" s="6" t="n">
         <v>10</v>
@@ -10841,10 +10841,10 @@
         </is>
       </c>
       <c r="I105" s="4" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J105" s="4" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="K105" s="4" t="n">
         <v>0</v>
@@ -10868,16 +10868,16 @@
         </is>
       </c>
       <c r="P105" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q105" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="Q105" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R105" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S105" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T105" s="9" t="n">
         <v>0</v>
@@ -10892,13 +10892,13 @@
         <v>0</v>
       </c>
       <c r="X105" s="10" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="Y105" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z105" s="9" t="n">
-        <v>0</v>
+      <c r="Z105" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA105" s="10" t="n">
         <v>1</v>
@@ -10916,11 +10916,11 @@
         </is>
       </c>
       <c r="C106" s="4" t="n">
-        <v>28679641</v>
+        <v>28677813</v>
       </c>
       <c r="D106" s="4" t="inlineStr">
         <is>
-          <t>Optimus Toastmasters Club</t>
+          <t>Idemia Toastmasters Club</t>
         </is>
       </c>
       <c r="E106" s="5" t="n">
@@ -10989,7 +10989,7 @@
         <v>0</v>
       </c>
       <c r="X106" s="10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Y106" s="9" t="n">
         <v>0</v>
@@ -11013,11 +11013,11 @@
         </is>
       </c>
       <c r="C107" s="4" t="n">
-        <v>28679152</v>
+        <v>28679641</v>
       </c>
       <c r="D107" s="4" t="inlineStr">
         <is>
-          <t>UKG Toastmasters Noida #1</t>
+          <t>Optimus Toastmasters Club</t>
         </is>
       </c>
       <c r="E107" s="5" t="n">
@@ -11035,25 +11035,25 @@
         </is>
       </c>
       <c r="I107" s="4" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="J107" s="4" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="K107" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L107" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="L107" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M107" s="7" t="n">
-        <v>46387</v>
+        <v>46446</v>
       </c>
       <c r="N107" s="4" t="inlineStr">
         <is>
-          <t>Officer list on time</t>
+          <t>Officers trained Nov-Feb</t>
         </is>
       </c>
       <c r="O107" s="8" t="inlineStr">
@@ -11086,7 +11086,7 @@
         <v>0</v>
       </c>
       <c r="X107" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Y107" s="9" t="n">
         <v>0</v>
@@ -11094,8 +11094,8 @@
       <c r="Z107" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="AA107" s="9" t="n">
-        <v>0</v>
+      <c r="AA107" s="10" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="108">
@@ -11110,11 +11110,11 @@
         </is>
       </c>
       <c r="C108" s="4" t="n">
-        <v>28679153</v>
+        <v>28679152</v>
       </c>
       <c r="D108" s="4" t="inlineStr">
         <is>
-          <t>UKG Toastmasters Noida #2</t>
+          <t>UKG Toastmasters Noida #1</t>
         </is>
       </c>
       <c r="E108" s="5" t="n">
@@ -11183,7 +11183,7 @@
         <v>0</v>
       </c>
       <c r="X108" s="10" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Y108" s="9" t="n">
         <v>0</v>
@@ -11207,11 +11207,11 @@
         </is>
       </c>
       <c r="C109" s="4" t="n">
-        <v>28679312</v>
+        <v>28679153</v>
       </c>
       <c r="D109" s="4" t="inlineStr">
         <is>
-          <t>UKG Toastmasters Noida #3</t>
+          <t>UKG Toastmasters Noida #2</t>
         </is>
       </c>
       <c r="E109" s="5" t="n">
@@ -11229,10 +11229,10 @@
         </is>
       </c>
       <c r="I109" s="4" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="J109" s="4" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="K109" s="4" t="n">
         <v>0</v>
@@ -11256,7 +11256,7 @@
         </is>
       </c>
       <c r="P109" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q109" s="9" t="n">
         <v>0</v>
@@ -11279,8 +11279,8 @@
       <c r="W109" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X109" s="9" t="n">
-        <v>0</v>
+      <c r="X109" s="10" t="n">
+        <v>6</v>
       </c>
       <c r="Y109" s="9" t="n">
         <v>0</v>
@@ -11304,11 +11304,11 @@
         </is>
       </c>
       <c r="C110" s="4" t="n">
-        <v>28679313</v>
+        <v>28679312</v>
       </c>
       <c r="D110" s="4" t="inlineStr">
         <is>
-          <t>UKG Toastmasters Noida #4</t>
+          <t>UKG Toastmasters Noida #3</t>
         </is>
       </c>
       <c r="E110" s="5" t="n">
@@ -11326,10 +11326,10 @@
         </is>
       </c>
       <c r="I110" s="4" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="J110" s="4" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="K110" s="4" t="n">
         <v>0</v>
@@ -11377,7 +11377,7 @@
         <v>0</v>
       </c>
       <c r="X110" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Y110" s="9" t="n">
         <v>0</v>
@@ -11397,19 +11397,19 @@
       </c>
       <c r="B111" s="4" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>02</t>
         </is>
       </c>
       <c r="C111" s="4" t="n">
-        <v>5972216</v>
+        <v>28679313</v>
       </c>
       <c r="D111" s="4" t="inlineStr">
         <is>
-          <t>Kanpur Toastmasters Club</t>
+          <t>UKG Toastmasters Noida #4</t>
         </is>
       </c>
       <c r="E111" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F111" s="6" t="n">
         <v>10</v>
@@ -11423,25 +11423,25 @@
         </is>
       </c>
       <c r="I111" s="4" t="n">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="J111" s="4" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="K111" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="L111" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>0</v>
+      </c>
+      <c r="L111" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M111" s="7" t="n">
-        <v>46446</v>
+        <v>46387</v>
       </c>
       <c r="N111" s="4" t="inlineStr">
         <is>
-          <t>Officers trained Nov-Feb</t>
+          <t>Officer list on time</t>
         </is>
       </c>
       <c r="O111" s="8" t="inlineStr">
@@ -11467,23 +11467,23 @@
       <c r="U111" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V111" s="10" t="n">
-        <v>4</v>
+      <c r="V111" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="W111" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X111" s="10" t="n">
-        <v>5</v>
+      <c r="X111" s="9" t="n">
+        <v>3</v>
       </c>
       <c r="Y111" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z111" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA111" s="10" t="n">
-        <v>1</v>
+      <c r="Z111" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA111" s="9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="112">
@@ -11498,15 +11498,15 @@
         </is>
       </c>
       <c r="C112" s="4" t="n">
-        <v>7993552</v>
+        <v>5972216</v>
       </c>
       <c r="D112" s="4" t="inlineStr">
         <is>
-          <t>Toastmasters Club IITK #01</t>
+          <t>Kanpur Toastmasters Club</t>
         </is>
       </c>
       <c r="E112" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F112" s="6" t="n">
         <v>10</v>
@@ -11520,17 +11520,17 @@
         </is>
       </c>
       <c r="I112" s="4" t="n">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="J112" s="4" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="K112" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L112" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>4</v>
+      </c>
+      <c r="L112" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M112" s="7" t="n">
@@ -11547,10 +11547,10 @@
         </is>
       </c>
       <c r="P112" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q112" s="10" t="n">
-        <v>2</v>
+        <v>0</v>
+      </c>
+      <c r="Q112" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="R112" s="9" t="n">
         <v>0</v>
@@ -11564,8 +11564,8 @@
       <c r="U112" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V112" s="9" t="n">
-        <v>0</v>
+      <c r="V112" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W112" s="9" t="n">
         <v>0</v>
@@ -11576,8 +11576,8 @@
       <c r="Y112" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z112" s="9" t="n">
-        <v>0</v>
+      <c r="Z112" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA112" s="10" t="n">
         <v>1</v>
@@ -11595,15 +11595,15 @@
         </is>
       </c>
       <c r="C113" s="4" t="n">
-        <v>28675639</v>
+        <v>7993552</v>
       </c>
       <c r="D113" s="4" t="inlineStr">
         <is>
-          <t>Toastmasters Club IITK #02</t>
+          <t>Toastmasters Club IITK #01</t>
         </is>
       </c>
       <c r="E113" s="5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F113" s="6" t="n">
         <v>10</v>
@@ -11617,10 +11617,10 @@
         </is>
       </c>
       <c r="I113" s="4" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="J113" s="4" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="K113" s="4" t="n">
         <v>0</v>
@@ -11652,14 +11652,14 @@
       <c r="R113" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S113" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="T113" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U113" s="10" t="n">
-        <v>1</v>
+      <c r="S113" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T113" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U113" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="V113" s="9" t="n">
         <v>0</v>
@@ -11668,7 +11668,7 @@
         <v>0</v>
       </c>
       <c r="X113" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Y113" s="9" t="n">
         <v>0</v>
@@ -11692,11 +11692,11 @@
         </is>
       </c>
       <c r="C114" s="4" t="n">
-        <v>28676264</v>
+        <v>28675639</v>
       </c>
       <c r="D114" s="4" t="inlineStr">
         <is>
-          <t>Toastmasters Club IITK #03</t>
+          <t>Toastmasters Club IITK #02</t>
         </is>
       </c>
       <c r="E114" s="5" t="n">
@@ -11789,15 +11789,15 @@
         </is>
       </c>
       <c r="C115" s="4" t="n">
-        <v>28677063</v>
+        <v>28676264</v>
       </c>
       <c r="D115" s="4" t="inlineStr">
         <is>
-          <t>Toastmasters Club IITK #04</t>
+          <t>Toastmasters Club IITK #03</t>
         </is>
       </c>
       <c r="E115" s="5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F115" s="6" t="n">
         <v>10</v>
@@ -11811,10 +11811,10 @@
         </is>
       </c>
       <c r="I115" s="4" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="J115" s="4" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="K115" s="4" t="n">
         <v>0</v>
@@ -11838,22 +11838,22 @@
         </is>
       </c>
       <c r="P115" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q115" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="Q115" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R115" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S115" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T115" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U115" s="9" t="n">
-        <v>0</v>
+      <c r="S115" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="T115" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U115" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V115" s="9" t="n">
         <v>0</v>
@@ -11862,7 +11862,7 @@
         <v>0</v>
       </c>
       <c r="X115" s="10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Y115" s="9" t="n">
         <v>0</v>
@@ -11886,15 +11886,15 @@
         </is>
       </c>
       <c r="C116" s="4" t="n">
-        <v>28677695</v>
+        <v>28677063</v>
       </c>
       <c r="D116" s="4" t="inlineStr">
         <is>
-          <t>Toastmasters Club IITK #05</t>
+          <t>Toastmasters Club IITK #04</t>
         </is>
       </c>
       <c r="E116" s="5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F116" s="6" t="n">
         <v>10</v>
@@ -11908,10 +11908,10 @@
         </is>
       </c>
       <c r="I116" s="4" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="J116" s="4" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="K116" s="4" t="n">
         <v>0</v>
@@ -11935,22 +11935,22 @@
         </is>
       </c>
       <c r="P116" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q116" s="10" t="n">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="Q116" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="R116" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S116" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="T116" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U116" s="10" t="n">
-        <v>1</v>
+      <c r="S116" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T116" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U116" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="V116" s="9" t="n">
         <v>0</v>
@@ -11959,7 +11959,7 @@
         <v>0</v>
       </c>
       <c r="X116" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Y116" s="9" t="n">
         <v>0</v>
@@ -11979,19 +11979,19 @@
       </c>
       <c r="B117" s="4" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>03</t>
         </is>
       </c>
       <c r="C117" s="4" t="n">
-        <v>7118202</v>
+        <v>28677695</v>
       </c>
       <c r="D117" s="4" t="inlineStr">
         <is>
-          <t>IMSUC Toastmasters Club</t>
+          <t>Toastmasters Club IITK #05</t>
         </is>
       </c>
       <c r="E117" s="5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F117" s="6" t="n">
         <v>10</v>
@@ -12005,10 +12005,10 @@
         </is>
       </c>
       <c r="I117" s="4" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="J117" s="4" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="K117" s="4" t="n">
         <v>0</v>
@@ -12019,11 +12019,11 @@
         </is>
       </c>
       <c r="M117" s="7" t="n">
-        <v>46387</v>
+        <v>46446</v>
       </c>
       <c r="N117" s="4" t="inlineStr">
         <is>
-          <t>Officer list on time</t>
+          <t>Officers trained Nov-Feb</t>
         </is>
       </c>
       <c r="O117" s="8" t="inlineStr">
@@ -12032,22 +12032,22 @@
         </is>
       </c>
       <c r="P117" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q117" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="Q117" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R117" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S117" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T117" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U117" s="9" t="n">
-        <v>0</v>
+      <c r="S117" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="T117" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U117" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V117" s="9" t="n">
         <v>0</v>
@@ -12055,8 +12055,8 @@
       <c r="W117" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X117" s="9" t="n">
-        <v>0</v>
+      <c r="X117" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y117" s="9" t="n">
         <v>0</v>
@@ -12064,8 +12064,8 @@
       <c r="Z117" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="AA117" s="9" t="n">
-        <v>0</v>
+      <c r="AA117" s="10" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="118">
@@ -12080,15 +12080,15 @@
         </is>
       </c>
       <c r="C118" s="4" t="n">
-        <v>28678966</v>
+        <v>7118202</v>
       </c>
       <c r="D118" s="4" t="inlineStr">
         <is>
-          <t>Infosys NCR Toastmasters Club</t>
+          <t>IMSUC Toastmasters Club</t>
         </is>
       </c>
       <c r="E118" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F118" s="6" t="n">
         <v>10</v>
@@ -12102,25 +12102,25 @@
         </is>
       </c>
       <c r="I118" s="4" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="J118" s="4" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="K118" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L118" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+      <c r="L118" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M118" s="7" t="n">
-        <v>46446</v>
+        <v>46387</v>
       </c>
       <c r="N118" s="4" t="inlineStr">
         <is>
-          <t>Officers trained Nov-Feb</t>
+          <t>Officer list on time</t>
         </is>
       </c>
       <c r="O118" s="8" t="inlineStr">
@@ -12152,17 +12152,17 @@
       <c r="W118" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X118" s="10" t="n">
-        <v>7</v>
+      <c r="X118" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Y118" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z118" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA118" s="10" t="n">
-        <v>1</v>
+      <c r="Z118" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA118" s="9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="119">
@@ -12177,15 +12177,15 @@
         </is>
       </c>
       <c r="C119" s="4" t="n">
-        <v>28676764</v>
+        <v>28678966</v>
       </c>
       <c r="D119" s="4" t="inlineStr">
         <is>
-          <t>Iris Toastmasters Club</t>
+          <t>Infosys NCR Toastmasters Club</t>
         </is>
       </c>
       <c r="E119" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F119" s="6" t="n">
         <v>10</v>
@@ -12199,10 +12199,10 @@
         </is>
       </c>
       <c r="I119" s="4" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="J119" s="4" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="K119" s="4" t="n">
         <v>0</v>
@@ -12255,8 +12255,8 @@
       <c r="Y119" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z119" s="9" t="n">
-        <v>0</v>
+      <c r="Z119" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA119" s="10" t="n">
         <v>1</v>
@@ -12274,15 +12274,15 @@
         </is>
       </c>
       <c r="C120" s="4" t="n">
-        <v>28677828</v>
+        <v>28676764</v>
       </c>
       <c r="D120" s="4" t="inlineStr">
         <is>
-          <t>IRIS Toastmasters Club II</t>
+          <t>Iris Toastmasters Club</t>
         </is>
       </c>
       <c r="E120" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F120" s="6" t="n">
         <v>10</v>
@@ -12296,10 +12296,10 @@
         </is>
       </c>
       <c r="I120" s="4" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J120" s="4" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="K120" s="4" t="n">
         <v>0</v>
@@ -12323,7 +12323,7 @@
         </is>
       </c>
       <c r="P120" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q120" s="9" t="n">
         <v>0</v>
@@ -12331,8 +12331,8 @@
       <c r="R120" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S120" s="9" t="n">
-        <v>0</v>
+      <c r="S120" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T120" s="9" t="n">
         <v>0</v>
@@ -12347,7 +12347,7 @@
         <v>0</v>
       </c>
       <c r="X120" s="10" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="Y120" s="9" t="n">
         <v>0</v>
@@ -12371,15 +12371,15 @@
         </is>
       </c>
       <c r="C121" s="4" t="n">
-        <v>4887204</v>
+        <v>28677828</v>
       </c>
       <c r="D121" s="4" t="inlineStr">
         <is>
-          <t>Noida ExpressWay Toastmasters Club</t>
+          <t>IRIS Toastmasters Club II</t>
         </is>
       </c>
       <c r="E121" s="5" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="F121" s="6" t="n">
         <v>10</v>
@@ -12393,13 +12393,13 @@
         </is>
       </c>
       <c r="I121" s="4" t="n">
-        <v>73</v>
+        <v>22</v>
       </c>
       <c r="J121" s="4" t="n">
-        <v>52</v>
+        <v>22</v>
       </c>
       <c r="K121" s="4" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="L121" s="4" t="inlineStr">
         <is>
@@ -12420,37 +12420,37 @@
         </is>
       </c>
       <c r="P121" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q121" s="10" t="n">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="Q121" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="R121" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S121" s="10" t="n">
-        <v>2</v>
+      <c r="S121" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="T121" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U121" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="V121" s="10" t="n">
+      <c r="U121" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V121" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W121" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X121" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W121" s="10" t="n">
-        <v>16</v>
-      </c>
-      <c r="X121" s="10" t="n">
-        <v>7</v>
-      </c>
       <c r="Y121" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z121" s="10" t="n">
-        <v>1</v>
+      <c r="Z121" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA121" s="10" t="n">
         <v>1</v>
@@ -12468,15 +12468,15 @@
         </is>
       </c>
       <c r="C122" s="4" t="n">
-        <v>28680880</v>
+        <v>4887204</v>
       </c>
       <c r="D122" s="4" t="inlineStr">
         <is>
-          <t>SpeakUp Noida Toastmasters Club</t>
+          <t>Noida ExpressWay Toastmasters Club</t>
         </is>
       </c>
       <c r="E122" s="5" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F122" s="6" t="n">
         <v>10</v>
@@ -12490,17 +12490,17 @@
         </is>
       </c>
       <c r="I122" s="4" t="n">
-        <v>5</v>
+        <v>73</v>
       </c>
       <c r="J122" s="4" t="n">
-        <v>20</v>
+        <v>52</v>
       </c>
       <c r="K122" s="4" t="n">
-        <v>-15</v>
-      </c>
-      <c r="L122" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>21</v>
+      </c>
+      <c r="L122" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M122" s="7" t="n">
@@ -12517,31 +12517,31 @@
         </is>
       </c>
       <c r="P122" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q122" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
+      </c>
+      <c r="Q122" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R122" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S122" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T122" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U122" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V122" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W122" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X122" s="9" t="n">
-        <v>0</v>
+      <c r="S122" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="T122" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U122" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="V122" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W122" s="10" t="n">
+        <v>16</v>
+      </c>
+      <c r="X122" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="Y122" s="9" t="n">
         <v>0</v>
@@ -12565,15 +12565,15 @@
         </is>
       </c>
       <c r="C123" s="4" t="n">
-        <v>28675384</v>
+        <v>28680880</v>
       </c>
       <c r="D123" s="4" t="inlineStr">
         <is>
-          <t>Young Voices Toastmasters Club</t>
+          <t>SpeakUp Noida Toastmasters Club</t>
         </is>
       </c>
       <c r="E123" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F123" s="6" t="n">
         <v>10</v>
@@ -12587,13 +12587,13 @@
         </is>
       </c>
       <c r="I123" s="4" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="J123" s="4" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="K123" s="4" t="n">
-        <v>1</v>
+        <v>-15</v>
       </c>
       <c r="L123" s="8" t="inlineStr">
         <is>
@@ -12632,19 +12632,19 @@
         <v>0</v>
       </c>
       <c r="V123" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W123" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X123" s="10" t="n">
-        <v>4</v>
+      <c r="X123" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Y123" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z123" s="9" t="n">
-        <v>0</v>
+      <c r="Z123" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA123" s="10" t="n">
         <v>1</v>
@@ -12653,24 +12653,24 @@
     <row r="124">
       <c r="A124" s="4" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>F</t>
         </is>
       </c>
       <c r="B124" s="4" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>04</t>
         </is>
       </c>
       <c r="C124" s="4" t="n">
-        <v>28676190</v>
+        <v>28675384</v>
       </c>
       <c r="D124" s="4" t="inlineStr">
         <is>
-          <t>BE@T Toastmasters Club</t>
+          <t>Young Voices Toastmasters Club</t>
         </is>
       </c>
       <c r="E124" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F124" s="6" t="n">
         <v>10</v>
@@ -12684,17 +12684,17 @@
         </is>
       </c>
       <c r="I124" s="4" t="n">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="J124" s="4" t="n">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="K124" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="L124" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>1</v>
+      </c>
+      <c r="L124" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M124" s="7" t="n">
@@ -12728,20 +12728,20 @@
       <c r="U124" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V124" s="10" t="n">
+      <c r="V124" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="W124" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X124" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W124" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="X124" s="10" t="n">
-        <v>6</v>
-      </c>
       <c r="Y124" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z124" s="10" t="n">
-        <v>1</v>
+      <c r="Z124" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA124" s="10" t="n">
         <v>1</v>
@@ -12759,15 +12759,15 @@
         </is>
       </c>
       <c r="C125" s="4" t="n">
-        <v>28678583</v>
+        <v>28676190</v>
       </c>
       <c r="D125" s="4" t="inlineStr">
         <is>
-          <t>Carelon Spartan Toastmasters Club</t>
+          <t>BE@T Toastmasters Club</t>
         </is>
       </c>
       <c r="E125" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F125" s="6" t="n">
         <v>10</v>
@@ -12781,13 +12781,13 @@
         </is>
       </c>
       <c r="I125" s="4" t="n">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="J125" s="4" t="n">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="K125" s="4" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L125" s="4" t="inlineStr">
         <is>
@@ -12810,14 +12810,14 @@
       <c r="P125" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Q125" s="10" t="n">
-        <v>2</v>
+      <c r="Q125" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="R125" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S125" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T125" s="9" t="n">
         <v>0</v>
@@ -12825,20 +12825,20 @@
       <c r="U125" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V125" s="9" t="n">
-        <v>0</v>
+      <c r="V125" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W125" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X125" s="10" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Y125" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z125" s="9" t="n">
-        <v>0</v>
+      <c r="Z125" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA125" s="10" t="n">
         <v>1</v>
@@ -12856,15 +12856,15 @@
         </is>
       </c>
       <c r="C126" s="4" t="n">
-        <v>4055055</v>
+        <v>28678583</v>
       </c>
       <c r="D126" s="4" t="inlineStr">
         <is>
-          <t>Eloquent Toastmasters Club</t>
+          <t>Carelon Spartan Toastmasters Club</t>
         </is>
       </c>
       <c r="E126" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F126" s="6" t="n">
         <v>10</v>
@@ -12878,13 +12878,13 @@
         </is>
       </c>
       <c r="I126" s="4" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="J126" s="4" t="n">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="K126" s="4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L126" s="4" t="inlineStr">
         <is>
@@ -12907,8 +12907,8 @@
       <c r="P126" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Q126" s="9" t="n">
-        <v>0</v>
+      <c r="Q126" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R126" s="9" t="n">
         <v>0</v>
@@ -12922,20 +12922,20 @@
       <c r="U126" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V126" s="10" t="n">
+      <c r="V126" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W126" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X126" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W126" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="X126" s="10" t="n">
-        <v>7</v>
-      </c>
       <c r="Y126" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z126" s="10" t="n">
-        <v>1</v>
+      <c r="Z126" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA126" s="10" t="n">
         <v>1</v>
@@ -12953,15 +12953,15 @@
         </is>
       </c>
       <c r="C127" s="4" t="n">
-        <v>5768974</v>
+        <v>4055055</v>
       </c>
       <c r="D127" s="4" t="inlineStr">
         <is>
-          <t>HSBC Toastmasters</t>
+          <t>Eloquent Toastmasters Club</t>
         </is>
       </c>
       <c r="E127" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F127" s="6" t="n">
         <v>10</v>
@@ -12975,17 +12975,17 @@
         </is>
       </c>
       <c r="I127" s="4" t="n">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="J127" s="4" t="n">
-        <v>8</v>
+        <v>35</v>
       </c>
       <c r="K127" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L127" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>5</v>
+      </c>
+      <c r="L127" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M127" s="7" t="n">
@@ -13011,7 +13011,7 @@
         <v>0</v>
       </c>
       <c r="S127" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T127" s="9" t="n">
         <v>0</v>
@@ -13019,20 +13019,20 @@
       <c r="U127" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V127" s="9" t="n">
-        <v>0</v>
+      <c r="V127" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W127" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X127" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="X127" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="Y127" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z127" s="9" t="n">
-        <v>0</v>
+      <c r="Z127" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA127" s="10" t="n">
         <v>1</v>
@@ -13046,15 +13046,15 @@
       </c>
       <c r="B128" s="4" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>01</t>
         </is>
       </c>
       <c r="C128" s="4" t="n">
-        <v>3781541</v>
+        <v>5768974</v>
       </c>
       <c r="D128" s="4" t="inlineStr">
         <is>
-          <t>Amex Gurgaon Toastmasters Club</t>
+          <t>HSBC Toastmasters</t>
         </is>
       </c>
       <c r="E128" s="5" t="n">
@@ -13147,15 +13147,15 @@
         </is>
       </c>
       <c r="C129" s="4" t="n">
-        <v>5168041</v>
+        <v>3781541</v>
       </c>
       <c r="D129" s="4" t="inlineStr">
         <is>
-          <t>Gurgaon Orators Toastmasters Club</t>
+          <t>Amex Gurgaon Toastmasters Club</t>
         </is>
       </c>
       <c r="E129" s="5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F129" s="6" t="n">
         <v>10</v>
@@ -13169,17 +13169,17 @@
         </is>
       </c>
       <c r="I129" s="4" t="n">
-        <v>47</v>
+        <v>8</v>
       </c>
       <c r="J129" s="4" t="n">
-        <v>37</v>
+        <v>8</v>
       </c>
       <c r="K129" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="L129" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>0</v>
+      </c>
+      <c r="L129" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M129" s="7" t="n">
@@ -13195,8 +13195,8 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P129" s="10" t="n">
-        <v>4</v>
+      <c r="P129" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Q129" s="9" t="n">
         <v>0</v>
@@ -13207,26 +13207,26 @@
       <c r="S129" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T129" s="10" t="n">
-        <v>1</v>
+      <c r="T129" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U129" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V129" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="W129" s="10" t="n">
-        <v>6</v>
-      </c>
-      <c r="X129" s="10" t="n">
-        <v>7</v>
+      <c r="V129" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W129" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X129" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Y129" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z129" s="10" t="n">
-        <v>1</v>
+      <c r="Z129" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA129" s="10" t="n">
         <v>1</v>
@@ -13244,15 +13244,15 @@
         </is>
       </c>
       <c r="C130" s="4" t="n">
-        <v>7901096</v>
+        <v>5168041</v>
       </c>
       <c r="D130" s="4" t="inlineStr">
         <is>
-          <t>Gurugram Professional Toastmasters</t>
+          <t>Gurgaon Orators Toastmasters Club</t>
         </is>
       </c>
       <c r="E130" s="5" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F130" s="6" t="n">
         <v>10</v>
@@ -13266,17 +13266,17 @@
         </is>
       </c>
       <c r="I130" s="4" t="n">
-        <v>19</v>
+        <v>47</v>
       </c>
       <c r="J130" s="4" t="n">
-        <v>17</v>
+        <v>37</v>
       </c>
       <c r="K130" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L130" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>10</v>
+      </c>
+      <c r="L130" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M130" s="7" t="n">
@@ -13292,8 +13292,8 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P130" s="9" t="n">
-        <v>0</v>
+      <c r="P130" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="Q130" s="9" t="n">
         <v>0</v>
@@ -13304,17 +13304,17 @@
       <c r="S130" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T130" s="9" t="n">
-        <v>0</v>
+      <c r="T130" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U130" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V130" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="W130" s="9" t="n">
-        <v>0</v>
+      <c r="V130" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W130" s="10" t="n">
+        <v>6</v>
       </c>
       <c r="X130" s="10" t="n">
         <v>7</v>
@@ -13341,15 +13341,15 @@
         </is>
       </c>
       <c r="C131" s="4" t="n">
-        <v>28678891</v>
+        <v>7901096</v>
       </c>
       <c r="D131" s="4" t="inlineStr">
         <is>
-          <t>Hatch India Toastmasters Club</t>
+          <t>Gurugram Professional Toastmasters</t>
         </is>
       </c>
       <c r="E131" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F131" s="6" t="n">
         <v>10</v>
@@ -13363,17 +13363,17 @@
         </is>
       </c>
       <c r="I131" s="4" t="n">
-        <v>40</v>
+        <v>19</v>
       </c>
       <c r="J131" s="4" t="n">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="K131" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L131" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>2</v>
+      </c>
+      <c r="L131" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M131" s="7" t="n">
@@ -13408,19 +13408,19 @@
         <v>0</v>
       </c>
       <c r="V131" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W131" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X131" s="10" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y131" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z131" s="9" t="n">
-        <v>0</v>
+      <c r="Z131" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA131" s="10" t="n">
         <v>1</v>
@@ -13438,11 +13438,11 @@
         </is>
       </c>
       <c r="C132" s="4" t="n">
-        <v>28678612</v>
+        <v>28678891</v>
       </c>
       <c r="D132" s="4" t="inlineStr">
         <is>
-          <t>Lummus Toastmasters Club</t>
+          <t>Hatch India Toastmasters Club</t>
         </is>
       </c>
       <c r="E132" s="5" t="n">
@@ -13460,10 +13460,10 @@
         </is>
       </c>
       <c r="I132" s="4" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="J132" s="4" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="K132" s="4" t="n">
         <v>0</v>
@@ -13474,11 +13474,11 @@
         </is>
       </c>
       <c r="M132" s="7" t="n">
-        <v>46387</v>
+        <v>46446</v>
       </c>
       <c r="N132" s="4" t="inlineStr">
         <is>
-          <t>Officer list on time</t>
+          <t>Officers trained Nov-Feb</t>
         </is>
       </c>
       <c r="O132" s="8" t="inlineStr">
@@ -13487,7 +13487,7 @@
         </is>
       </c>
       <c r="P132" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q132" s="9" t="n">
         <v>0</v>
@@ -13510,8 +13510,8 @@
       <c r="W132" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X132" s="9" t="n">
-        <v>2</v>
+      <c r="X132" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="Y132" s="9" t="n">
         <v>0</v>
@@ -13519,8 +13519,8 @@
       <c r="Z132" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="AA132" s="9" t="n">
-        <v>0</v>
+      <c r="AA132" s="10" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="133">
@@ -13535,11 +13535,11 @@
         </is>
       </c>
       <c r="C133" s="4" t="n">
-        <v>28679643</v>
+        <v>28678612</v>
       </c>
       <c r="D133" s="4" t="inlineStr">
         <is>
-          <t>Powergrid Toastmasters Club</t>
+          <t>Lummus Toastmasters Club</t>
         </is>
       </c>
       <c r="E133" s="5" t="n">
@@ -13557,25 +13557,25 @@
         </is>
       </c>
       <c r="I133" s="4" t="n">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="J133" s="4" t="n">
-        <v>39</v>
+        <v>25</v>
       </c>
       <c r="K133" s="4" t="n">
-        <v>-31</v>
-      </c>
-      <c r="L133" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>0</v>
+      </c>
+      <c r="L133" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M133" s="7" t="n">
-        <v>46446</v>
+        <v>46387</v>
       </c>
       <c r="N133" s="4" t="inlineStr">
         <is>
-          <t>Officers trained Nov-Feb</t>
+          <t>Officer list on time</t>
         </is>
       </c>
       <c r="O133" s="8" t="inlineStr">
@@ -13584,7 +13584,7 @@
         </is>
       </c>
       <c r="P133" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q133" s="9" t="n">
         <v>0</v>
@@ -13608,16 +13608,16 @@
         <v>0</v>
       </c>
       <c r="X133" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y133" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z133" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA133" s="10" t="n">
-        <v>1</v>
+      <c r="Z133" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA133" s="9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="134">
@@ -13628,15 +13628,15 @@
       </c>
       <c r="B134" s="4" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>02</t>
         </is>
       </c>
       <c r="C134" s="4" t="n">
-        <v>5949422</v>
+        <v>28679643</v>
       </c>
       <c r="D134" s="4" t="inlineStr">
         <is>
-          <t>Gurgaon Champions Toastmasters Club</t>
+          <t>Powergrid Toastmasters Club</t>
         </is>
       </c>
       <c r="E134" s="5" t="n">
@@ -13654,13 +13654,13 @@
         </is>
       </c>
       <c r="I134" s="4" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="J134" s="4" t="n">
-        <v>11</v>
+        <v>39</v>
       </c>
       <c r="K134" s="4" t="n">
-        <v>1</v>
+        <v>-31</v>
       </c>
       <c r="L134" s="8" t="inlineStr">
         <is>
@@ -13699,7 +13699,7 @@
         <v>0</v>
       </c>
       <c r="V134" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W134" s="9" t="n">
         <v>0</v>
@@ -13729,15 +13729,15 @@
         </is>
       </c>
       <c r="C135" s="4" t="n">
-        <v>3321031</v>
+        <v>5949422</v>
       </c>
       <c r="D135" s="4" t="inlineStr">
         <is>
-          <t>Millennium City Toastmasters Club</t>
+          <t>Gurgaon Champions Toastmasters Club</t>
         </is>
       </c>
       <c r="E135" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F135" s="6" t="n">
         <v>10</v>
@@ -13751,17 +13751,17 @@
         </is>
       </c>
       <c r="I135" s="4" t="n">
-        <v>48</v>
+        <v>12</v>
       </c>
       <c r="J135" s="4" t="n">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="K135" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="L135" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>1</v>
+      </c>
+      <c r="L135" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M135" s="7" t="n">
@@ -13778,10 +13778,10 @@
         </is>
       </c>
       <c r="P135" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q135" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R135" s="9" t="n">
         <v>0</v>
@@ -13795,14 +13795,14 @@
       <c r="U135" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V135" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="W135" s="10" t="n">
-        <v>6</v>
-      </c>
-      <c r="X135" s="10" t="n">
-        <v>7</v>
+      <c r="V135" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="W135" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X135" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Y135" s="9" t="n">
         <v>0</v>
@@ -13826,15 +13826,15 @@
         </is>
       </c>
       <c r="C136" s="4" t="n">
-        <v>28680288</v>
+        <v>3321031</v>
       </c>
       <c r="D136" s="4" t="inlineStr">
         <is>
-          <t>Oxane Partners Toastmasters Club - Leadership Circle</t>
+          <t>Millennium City Toastmasters Club</t>
         </is>
       </c>
       <c r="E136" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F136" s="6" t="n">
         <v>10</v>
@@ -13848,13 +13848,13 @@
         </is>
       </c>
       <c r="I136" s="4" t="n">
-        <v>22</v>
+        <v>48</v>
       </c>
       <c r="J136" s="4" t="n">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="K136" s="4" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L136" s="4" t="inlineStr">
         <is>
@@ -13875,10 +13875,10 @@
         </is>
       </c>
       <c r="P136" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q136" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R136" s="9" t="n">
         <v>0</v>
@@ -13892,20 +13892,20 @@
       <c r="U136" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V136" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W136" s="9" t="n">
-        <v>0</v>
+      <c r="V136" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W136" s="10" t="n">
+        <v>6</v>
       </c>
       <c r="X136" s="10" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="Y136" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z136" s="9" t="n">
-        <v>0</v>
+      <c r="Z136" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA136" s="10" t="n">
         <v>1</v>
@@ -13923,15 +13923,15 @@
         </is>
       </c>
       <c r="C137" s="4" t="n">
-        <v>28678659</v>
+        <v>28680288</v>
       </c>
       <c r="D137" s="4" t="inlineStr">
         <is>
-          <t>S&amp;P Global Toastmasters Club</t>
+          <t>Oxane Partners Toastmasters Club - Leadership Circle</t>
         </is>
       </c>
       <c r="E137" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F137" s="6" t="n">
         <v>10</v>
@@ -13945,17 +13945,17 @@
         </is>
       </c>
       <c r="I137" s="4" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="J137" s="4" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="K137" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L137" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>0</v>
+      </c>
+      <c r="L137" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M137" s="7" t="n">
@@ -13974,8 +13974,8 @@
       <c r="P137" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Q137" s="10" t="n">
-        <v>2</v>
+      <c r="Q137" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="R137" s="9" t="n">
         <v>0</v>
@@ -13990,19 +13990,19 @@
         <v>0</v>
       </c>
       <c r="V137" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="W137" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X137" s="10" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="Y137" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z137" s="10" t="n">
-        <v>1</v>
+      <c r="Z137" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA137" s="10" t="n">
         <v>1</v>
@@ -14020,15 +14020,15 @@
         </is>
       </c>
       <c r="C138" s="4" t="n">
-        <v>28677406</v>
+        <v>28678659</v>
       </c>
       <c r="D138" s="4" t="inlineStr">
         <is>
-          <t>Toastmasters Club at NAB India</t>
+          <t>S&amp;P Global Toastmasters Club</t>
         </is>
       </c>
       <c r="E138" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F138" s="6" t="n">
         <v>10</v>
@@ -14042,17 +14042,17 @@
         </is>
       </c>
       <c r="I138" s="4" t="n">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="J138" s="4" t="n">
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="K138" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L138" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>3</v>
+      </c>
+      <c r="L138" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M138" s="7" t="n">
@@ -14069,11 +14069,11 @@
         </is>
       </c>
       <c r="P138" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q138" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="Q138" s="9" t="n">
-        <v>0</v>
-      </c>
       <c r="R138" s="9" t="n">
         <v>0</v>
       </c>
@@ -14087,19 +14087,19 @@
         <v>0</v>
       </c>
       <c r="V138" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W138" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X138" s="10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y138" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z138" s="9" t="n">
-        <v>0</v>
+      <c r="Z138" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA138" s="10" t="n">
         <v>1</v>
@@ -14117,15 +14117,15 @@
         </is>
       </c>
       <c r="C139" s="4" t="n">
-        <v>28680808</v>
+        <v>28677406</v>
       </c>
       <c r="D139" s="4" t="inlineStr">
         <is>
-          <t>XLRI Xpressions Toastmasters Club</t>
+          <t>Toastmasters Club at NAB India</t>
         </is>
       </c>
       <c r="E139" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F139" s="6" t="n">
         <v>10</v>
@@ -14139,17 +14139,17 @@
         </is>
       </c>
       <c r="I139" s="4" t="n">
-        <v>12</v>
+        <v>40</v>
       </c>
       <c r="J139" s="4" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="K139" s="4" t="n">
-        <v>-8</v>
-      </c>
-      <c r="L139" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>0</v>
+      </c>
+      <c r="L139" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M139" s="7" t="n">
@@ -14166,7 +14166,7 @@
         </is>
       </c>
       <c r="P139" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q139" s="9" t="n">
         <v>0</v>
@@ -14189,14 +14189,14 @@
       <c r="W139" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X139" s="9" t="n">
-        <v>0</v>
+      <c r="X139" s="10" t="n">
+        <v>6</v>
       </c>
       <c r="Y139" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z139" s="10" t="n">
-        <v>1</v>
+      <c r="Z139" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA139" s="10" t="n">
         <v>1</v>
@@ -14210,15 +14210,15 @@
       </c>
       <c r="B140" s="4" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>03</t>
         </is>
       </c>
       <c r="C140" s="4" t="n">
-        <v>28675941</v>
+        <v>28680808</v>
       </c>
       <c r="D140" s="4" t="inlineStr">
         <is>
-          <t>AtkinsRealis Jewels Toastmasters Club</t>
+          <t>XLRI Xpressions Toastmasters Club</t>
         </is>
       </c>
       <c r="E140" s="5" t="n">
@@ -14236,17 +14236,17 @@
         </is>
       </c>
       <c r="I140" s="4" t="n">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="J140" s="4" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="K140" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L140" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-8</v>
+      </c>
+      <c r="L140" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M140" s="7" t="n">
@@ -14272,10 +14272,10 @@
         <v>0</v>
       </c>
       <c r="S140" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="T140" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="T140" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U140" s="9" t="n">
         <v>0</v>
@@ -14292,8 +14292,8 @@
       <c r="Y140" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z140" s="9" t="n">
-        <v>0</v>
+      <c r="Z140" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA140" s="10" t="n">
         <v>1</v>
@@ -14311,15 +14311,15 @@
         </is>
       </c>
       <c r="C141" s="4" t="n">
-        <v>1407110</v>
+        <v>28675941</v>
       </c>
       <c r="D141" s="4" t="inlineStr">
         <is>
-          <t>Blue Quest</t>
+          <t>AtkinsRealis Jewels Toastmasters Club</t>
         </is>
       </c>
       <c r="E141" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F141" s="6" t="n">
         <v>10</v>
@@ -14333,17 +14333,17 @@
         </is>
       </c>
       <c r="I141" s="4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="J141" s="4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="K141" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L141" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="L141" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M141" s="7" t="n">
@@ -14369,10 +14369,10 @@
         <v>0</v>
       </c>
       <c r="S141" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T141" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="T141" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U141" s="9" t="n">
         <v>0</v>
@@ -14383,8 +14383,8 @@
       <c r="W141" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X141" s="10" t="n">
-        <v>4</v>
+      <c r="X141" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Y141" s="9" t="n">
         <v>0</v>
@@ -14408,11 +14408,11 @@
         </is>
       </c>
       <c r="C142" s="4" t="n">
-        <v>3719774</v>
+        <v>1407110</v>
       </c>
       <c r="D142" s="4" t="inlineStr">
         <is>
-          <t>McDermott Speakers Toastmasters Club</t>
+          <t>Blue Quest</t>
         </is>
       </c>
       <c r="E142" s="5" t="n">
@@ -14430,17 +14430,17 @@
         </is>
       </c>
       <c r="I142" s="4" t="n">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="J142" s="4" t="n">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="K142" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L142" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+      <c r="L142" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M142" s="7" t="n">
@@ -14457,7 +14457,7 @@
         </is>
       </c>
       <c r="P142" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q142" s="9" t="n">
         <v>0</v>
@@ -14466,7 +14466,7 @@
         <v>0</v>
       </c>
       <c r="S142" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T142" s="9" t="n">
         <v>0</v>
@@ -14505,15 +14505,15 @@
         </is>
       </c>
       <c r="C143" s="4" t="n">
-        <v>6462252</v>
+        <v>3719774</v>
       </c>
       <c r="D143" s="4" t="inlineStr">
         <is>
-          <t>Move Mountains Toastmasters Club</t>
+          <t>McDermott Speakers Toastmasters Club</t>
         </is>
       </c>
       <c r="E143" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F143" s="6" t="n">
         <v>10</v>
@@ -14527,13 +14527,13 @@
         </is>
       </c>
       <c r="I143" s="4" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="J143" s="4" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="K143" s="4" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="L143" s="4" t="inlineStr">
         <is>
@@ -14554,7 +14554,7 @@
         </is>
       </c>
       <c r="P143" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q143" s="9" t="n">
         <v>0</v>
@@ -14565,26 +14565,26 @@
       <c r="S143" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="T143" s="10" t="n">
-        <v>1</v>
+      <c r="T143" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U143" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V143" s="10" t="n">
+      <c r="V143" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W143" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X143" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W143" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="X143" s="10" t="n">
-        <v>5</v>
-      </c>
       <c r="Y143" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z143" s="10" t="n">
-        <v>1</v>
+      <c r="Z143" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA143" s="10" t="n">
         <v>1</v>
@@ -14602,15 +14602,15 @@
         </is>
       </c>
       <c r="C144" s="4" t="n">
-        <v>28676033</v>
+        <v>6462252</v>
       </c>
       <c r="D144" s="4" t="inlineStr">
         <is>
-          <t>THE VANGUARDS</t>
+          <t>Move Mountains Toastmasters Club</t>
         </is>
       </c>
       <c r="E144" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F144" s="6" t="n">
         <v>10</v>
@@ -14624,13 +14624,13 @@
         </is>
       </c>
       <c r="I144" s="4" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J144" s="4" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="K144" s="4" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="L144" s="4" t="inlineStr">
         <is>
@@ -14638,11 +14638,11 @@
         </is>
       </c>
       <c r="M144" s="7" t="n">
-        <v>46387</v>
+        <v>46446</v>
       </c>
       <c r="N144" s="4" t="inlineStr">
         <is>
-          <t>Officer list on time</t>
+          <t>Officers trained Nov-Feb</t>
         </is>
       </c>
       <c r="O144" s="8" t="inlineStr">
@@ -14660,10 +14660,10 @@
         <v>0</v>
       </c>
       <c r="S144" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T144" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="T144" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U144" s="9" t="n">
         <v>0</v>
@@ -14671,43 +14671,43 @@
       <c r="V144" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W144" s="10" t="n">
+      <c r="W144" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="X144" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="X144" s="9" t="n">
-        <v>1</v>
-      </c>
       <c r="Y144" s="9" t="n">
         <v>0</v>
       </c>
       <c r="Z144" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="AA144" s="9" t="n">
-        <v>0</v>
+      <c r="AA144" s="10" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="4" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>G</t>
         </is>
       </c>
       <c r="B145" s="4" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>04</t>
         </is>
       </c>
       <c r="C145" s="4" t="n">
-        <v>7661270</v>
+        <v>28676033</v>
       </c>
       <c r="D145" s="4" t="inlineStr">
         <is>
-          <t>Bright Beginning Toastmasters Club</t>
+          <t>THE VANGUARDS</t>
         </is>
       </c>
       <c r="E145" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F145" s="6" t="n">
         <v>10</v>
@@ -14721,25 +14721,25 @@
         </is>
       </c>
       <c r="I145" s="4" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="J145" s="4" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="K145" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L145" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>9</v>
+      </c>
+      <c r="L145" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M145" s="7" t="n">
-        <v>46446</v>
+        <v>46387</v>
       </c>
       <c r="N145" s="4" t="inlineStr">
         <is>
-          <t>Officers trained Nov-Feb</t>
+          <t>Officer list on time</t>
         </is>
       </c>
       <c r="O145" s="8" t="inlineStr">
@@ -14748,10 +14748,10 @@
         </is>
       </c>
       <c r="P145" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q145" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R145" s="9" t="n">
         <v>0</v>
@@ -14765,23 +14765,23 @@
       <c r="U145" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V145" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W145" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X145" s="10" t="n">
+      <c r="V145" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W145" s="10" t="n">
         <v>5</v>
       </c>
+      <c r="X145" s="9" t="n">
+        <v>1</v>
+      </c>
       <c r="Y145" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z145" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA145" s="10" t="n">
-        <v>1</v>
+      <c r="Z145" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA145" s="9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="146">
@@ -14796,15 +14796,15 @@
         </is>
       </c>
       <c r="C146" s="4" t="n">
-        <v>5517955</v>
+        <v>7661270</v>
       </c>
       <c r="D146" s="4" t="inlineStr">
         <is>
-          <t>Faridabad Orators Toastmasters Club</t>
+          <t>Bright Beginning Toastmasters Club</t>
         </is>
       </c>
       <c r="E146" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F146" s="6" t="n">
         <v>10</v>
@@ -14818,17 +14818,17 @@
         </is>
       </c>
       <c r="I146" s="4" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="J146" s="4" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="K146" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L146" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+      <c r="L146" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M146" s="7" t="n">
@@ -14845,10 +14845,10 @@
         </is>
       </c>
       <c r="P146" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q146" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R146" s="9" t="n">
         <v>0</v>
@@ -14856,11 +14856,11 @@
       <c r="S146" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T146" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U146" s="10" t="n">
-        <v>1</v>
+      <c r="T146" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U146" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="V146" s="9" t="n">
         <v>0</v>
@@ -14874,8 +14874,8 @@
       <c r="Y146" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z146" s="10" t="n">
-        <v>1</v>
+      <c r="Z146" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA146" s="10" t="n">
         <v>1</v>
@@ -14893,11 +14893,11 @@
         </is>
       </c>
       <c r="C147" s="4" t="n">
-        <v>1867633</v>
+        <v>5517955</v>
       </c>
       <c r="D147" s="4" t="inlineStr">
         <is>
-          <t>Faridabad Toastmasters Club</t>
+          <t>Faridabad Orators Toastmasters Club</t>
         </is>
       </c>
       <c r="E147" s="5" t="n">
@@ -14915,13 +14915,13 @@
         </is>
       </c>
       <c r="I147" s="4" t="n">
-        <v>39</v>
+        <v>20</v>
       </c>
       <c r="J147" s="4" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="K147" s="4" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="L147" s="4" t="inlineStr">
         <is>
@@ -14942,31 +14942,31 @@
         </is>
       </c>
       <c r="P147" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q147" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R147" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S147" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="T147" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U147" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V147" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="W147" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T147" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U147" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="V147" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W147" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X147" s="10" t="n">
         <v>5</v>
-      </c>
-      <c r="X147" s="10" t="n">
-        <v>7</v>
       </c>
       <c r="Y147" s="9" t="n">
         <v>0</v>
@@ -14990,15 +14990,15 @@
         </is>
       </c>
       <c r="C148" s="4" t="n">
-        <v>28679608</v>
+        <v>1867633</v>
       </c>
       <c r="D148" s="4" t="inlineStr">
         <is>
-          <t>Moody's India Toastmasters Club</t>
+          <t>Faridabad Toastmasters Club</t>
         </is>
       </c>
       <c r="E148" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F148" s="6" t="n">
         <v>10</v>
@@ -15012,13 +15012,13 @@
         </is>
       </c>
       <c r="I148" s="4" t="n">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="J148" s="4" t="n">
-        <v>51</v>
+        <v>30</v>
       </c>
       <c r="K148" s="4" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="L148" s="4" t="inlineStr">
         <is>
@@ -15039,16 +15039,16 @@
         </is>
       </c>
       <c r="P148" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q148" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R148" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S148" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T148" s="9" t="n">
         <v>0</v>
@@ -15056,20 +15056,20 @@
       <c r="U148" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V148" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W148" s="9" t="n">
-        <v>0</v>
+      <c r="V148" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W148" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="X148" s="10" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="Y148" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z148" s="9" t="n">
-        <v>0</v>
+      <c r="Z148" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA148" s="10" t="n">
         <v>1</v>
@@ -15087,11 +15087,11 @@
         </is>
       </c>
       <c r="C149" s="4" t="n">
-        <v>28679776</v>
+        <v>28679608</v>
       </c>
       <c r="D149" s="4" t="inlineStr">
         <is>
-          <t>Zuari Toastmasters Club</t>
+          <t>Moody's India Toastmasters Club</t>
         </is>
       </c>
       <c r="E149" s="5" t="n">
@@ -15109,17 +15109,17 @@
         </is>
       </c>
       <c r="I149" s="4" t="n">
-        <v>8</v>
+        <v>51</v>
       </c>
       <c r="J149" s="4" t="n">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="K149" s="4" t="n">
-        <v>-12</v>
-      </c>
-      <c r="L149" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>0</v>
+      </c>
+      <c r="L149" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M149" s="7" t="n">
@@ -15180,19 +15180,19 @@
       </c>
       <c r="B150" s="4" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>01</t>
         </is>
       </c>
       <c r="C150" s="4" t="n">
-        <v>28677400</v>
+        <v>28679776</v>
       </c>
       <c r="D150" s="4" t="inlineStr">
         <is>
-          <t>Carrier Toastmasters Club</t>
+          <t>Zuari Toastmasters Club</t>
         </is>
       </c>
       <c r="E150" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F150" s="6" t="n">
         <v>10</v>
@@ -15206,13 +15206,13 @@
         </is>
       </c>
       <c r="I150" s="4" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="J150" s="4" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="K150" s="4" t="n">
-        <v>1</v>
+        <v>-12</v>
       </c>
       <c r="L150" s="8" t="inlineStr">
         <is>
@@ -15251,7 +15251,7 @@
         <v>0</v>
       </c>
       <c r="V150" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W150" s="9" t="n">
         <v>0</v>
@@ -15262,8 +15262,8 @@
       <c r="Y150" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z150" s="10" t="n">
-        <v>1</v>
+      <c r="Z150" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA150" s="10" t="n">
         <v>1</v>
@@ -15281,15 +15281,15 @@
         </is>
       </c>
       <c r="C151" s="4" t="n">
-        <v>1200975</v>
+        <v>28677400</v>
       </c>
       <c r="D151" s="4" t="inlineStr">
         <is>
-          <t>Gurgaon Toastmasters Club</t>
+          <t>Carrier Toastmasters Club</t>
         </is>
       </c>
       <c r="E151" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F151" s="6" t="n">
         <v>10</v>
@@ -15303,17 +15303,17 @@
         </is>
       </c>
       <c r="I151" s="4" t="n">
-        <v>59</v>
+        <v>14</v>
       </c>
       <c r="J151" s="4" t="n">
-        <v>52</v>
+        <v>13</v>
       </c>
       <c r="K151" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="L151" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>1</v>
+      </c>
+      <c r="L151" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M151" s="7" t="n">
@@ -15339,22 +15339,22 @@
         <v>0</v>
       </c>
       <c r="S151" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="T151" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="T151" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U151" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V151" s="10" t="n">
+      <c r="V151" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="W151" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X151" s="10" t="n">
         <v>4</v>
-      </c>
-      <c r="W151" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="X151" s="10" t="n">
-        <v>7</v>
       </c>
       <c r="Y151" s="9" t="n">
         <v>0</v>
@@ -15378,15 +15378,15 @@
         </is>
       </c>
       <c r="C152" s="4" t="n">
-        <v>28678186</v>
+        <v>1200975</v>
       </c>
       <c r="D152" s="4" t="inlineStr">
         <is>
-          <t>Gurugram Dronacharya Toastmasters Club</t>
+          <t>Gurgaon Toastmasters Club</t>
         </is>
       </c>
       <c r="E152" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F152" s="6" t="n">
         <v>10</v>
@@ -15400,13 +15400,13 @@
         </is>
       </c>
       <c r="I152" s="4" t="n">
-        <v>20</v>
+        <v>59</v>
       </c>
       <c r="J152" s="4" t="n">
-        <v>14</v>
+        <v>52</v>
       </c>
       <c r="K152" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L152" s="4" t="inlineStr">
         <is>
@@ -15430,16 +15430,16 @@
         <v>0</v>
       </c>
       <c r="Q152" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R152" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S152" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T152" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="T152" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U152" s="9" t="n">
         <v>0</v>
@@ -15448,10 +15448,10 @@
         <v>4</v>
       </c>
       <c r="W152" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X152" s="10" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="Y152" s="9" t="n">
         <v>0</v>
@@ -15475,11 +15475,11 @@
         </is>
       </c>
       <c r="C153" s="4" t="n">
-        <v>28678197</v>
+        <v>28678186</v>
       </c>
       <c r="D153" s="4" t="inlineStr">
         <is>
-          <t>Leaders Stories Toastmasters Club</t>
+          <t>Gurugram Dronacharya Toastmasters Club</t>
         </is>
       </c>
       <c r="E153" s="5" t="n">
@@ -15497,13 +15497,13 @@
         </is>
       </c>
       <c r="I153" s="4" t="n">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="J153" s="4" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="K153" s="4" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="L153" s="4" t="inlineStr">
         <is>
@@ -15524,10 +15524,10 @@
         </is>
       </c>
       <c r="P153" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q153" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R153" s="9" t="n">
         <v>0</v>
@@ -15535,20 +15535,20 @@
       <c r="S153" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T153" s="10" t="n">
-        <v>1</v>
+      <c r="T153" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U153" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V153" s="9" t="n">
-        <v>1</v>
+      <c r="V153" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W153" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X153" s="10" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="Y153" s="9" t="n">
         <v>0</v>
@@ -15572,15 +15572,15 @@
         </is>
       </c>
       <c r="C154" s="4" t="n">
-        <v>7391076</v>
+        <v>28678197</v>
       </c>
       <c r="D154" s="4" t="inlineStr">
         <is>
-          <t>Orange India Toastmasters</t>
+          <t>Leaders Stories Toastmasters Club</t>
         </is>
       </c>
       <c r="E154" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F154" s="6" t="n">
         <v>10</v>
@@ -15594,17 +15594,17 @@
         </is>
       </c>
       <c r="I154" s="4" t="n">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="J154" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K154" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L154" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>18</v>
+      </c>
+      <c r="L154" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M154" s="7" t="n">
@@ -15621,7 +15621,7 @@
         </is>
       </c>
       <c r="P154" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q154" s="9" t="n">
         <v>0</v>
@@ -15632,26 +15632,26 @@
       <c r="S154" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T154" s="9" t="n">
-        <v>0</v>
+      <c r="T154" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U154" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V154" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W154" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X154" s="9" t="n">
-        <v>0</v>
+      <c r="X154" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="Y154" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z154" s="9" t="n">
-        <v>0</v>
+      <c r="Z154" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA154" s="10" t="n">
         <v>1</v>
@@ -15669,15 +15669,15 @@
         </is>
       </c>
       <c r="C155" s="4" t="n">
-        <v>6672640</v>
+        <v>7391076</v>
       </c>
       <c r="D155" s="4" t="inlineStr">
         <is>
-          <t>Siemens Tales and Tellers</t>
+          <t>Orange India Toastmasters</t>
         </is>
       </c>
       <c r="E155" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F155" s="6" t="n">
         <v>10</v>
@@ -15691,17 +15691,17 @@
         </is>
       </c>
       <c r="I155" s="4" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="J155" s="4" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="K155" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L155" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+      <c r="L155" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M155" s="7" t="n">
@@ -15741,14 +15741,14 @@
       <c r="W155" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X155" s="10" t="n">
-        <v>4</v>
+      <c r="X155" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Y155" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z155" s="10" t="n">
-        <v>1</v>
+      <c r="Z155" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA155" s="10" t="n">
         <v>1</v>
@@ -15762,19 +15762,19 @@
       </c>
       <c r="B156" s="4" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>02</t>
         </is>
       </c>
       <c r="C156" s="4" t="n">
-        <v>28676069</v>
+        <v>6672640</v>
       </c>
       <c r="D156" s="4" t="inlineStr">
         <is>
-          <t>New Gurugram Toastmasters Club</t>
+          <t>Siemens Tales and Tellers</t>
         </is>
       </c>
       <c r="E156" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F156" s="6" t="n">
         <v>10</v>
@@ -15788,13 +15788,13 @@
         </is>
       </c>
       <c r="I156" s="4" t="n">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="J156" s="4" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="K156" s="4" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L156" s="4" t="inlineStr">
         <is>
@@ -15815,7 +15815,7 @@
         </is>
       </c>
       <c r="P156" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q156" s="9" t="n">
         <v>0</v>
@@ -15824,22 +15824,22 @@
         <v>0</v>
       </c>
       <c r="S156" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="T156" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="T156" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U156" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V156" s="10" t="n">
+      <c r="V156" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W156" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X156" s="10" t="n">
         <v>4</v>
-      </c>
-      <c r="W156" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X156" s="10" t="n">
-        <v>7</v>
       </c>
       <c r="Y156" s="9" t="n">
         <v>0</v>
@@ -15863,15 +15863,15 @@
         </is>
       </c>
       <c r="C157" s="4" t="n">
-        <v>1345936</v>
+        <v>28676069</v>
       </c>
       <c r="D157" s="4" t="inlineStr">
         <is>
-          <t>TCS Maitree Gurgaon Toastmasters</t>
+          <t>New Gurugram Toastmasters Club</t>
         </is>
       </c>
       <c r="E157" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F157" s="6" t="n">
         <v>10</v>
@@ -15885,17 +15885,17 @@
         </is>
       </c>
       <c r="I157" s="4" t="n">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="J157" s="4" t="n">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="K157" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L157" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>4</v>
+      </c>
+      <c r="L157" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M157" s="7" t="n">
@@ -15912,7 +15912,7 @@
         </is>
       </c>
       <c r="P157" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q157" s="9" t="n">
         <v>0</v>
@@ -15921,28 +15921,28 @@
         <v>0</v>
       </c>
       <c r="S157" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T157" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="T157" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U157" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V157" s="9" t="n">
-        <v>1</v>
+      <c r="V157" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W157" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X157" s="10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y157" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z157" s="9" t="n">
-        <v>0</v>
+      <c r="Z157" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA157" s="10" t="n">
         <v>1</v>
@@ -15960,15 +15960,15 @@
         </is>
       </c>
       <c r="C158" s="4" t="n">
-        <v>5539557</v>
+        <v>1345936</v>
       </c>
       <c r="D158" s="4" t="inlineStr">
         <is>
-          <t>The Pangram's Toastmasters Club</t>
+          <t>TCS Maitree Gurgaon Toastmasters</t>
         </is>
       </c>
       <c r="E158" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F158" s="6" t="n">
         <v>10</v>
@@ -15982,17 +15982,17 @@
         </is>
       </c>
       <c r="I158" s="4" t="n">
-        <v>39</v>
+        <v>10</v>
       </c>
       <c r="J158" s="4" t="n">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="K158" s="4" t="n">
-        <v>11</v>
-      </c>
-      <c r="L158" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>1</v>
+      </c>
+      <c r="L158" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M158" s="7" t="n">
@@ -16020,20 +16020,20 @@
       <c r="S158" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T158" s="10" t="n">
-        <v>1</v>
+      <c r="T158" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U158" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V158" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="W158" s="10" t="n">
-        <v>7</v>
+      <c r="V158" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="W158" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="X158" s="10" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y158" s="9" t="n">
         <v>0</v>
@@ -16057,15 +16057,15 @@
         </is>
       </c>
       <c r="C159" s="4" t="n">
-        <v>4238711</v>
+        <v>5539557</v>
       </c>
       <c r="D159" s="4" t="inlineStr">
         <is>
-          <t>Turning Point Toastmasters</t>
+          <t>The Pangram's Toastmasters Club</t>
         </is>
       </c>
       <c r="E159" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F159" s="6" t="n">
         <v>10</v>
@@ -16079,13 +16079,13 @@
         </is>
       </c>
       <c r="I159" s="4" t="n">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="J159" s="4" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="K159" s="4" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="L159" s="4" t="inlineStr">
         <is>
@@ -16106,7 +16106,7 @@
         </is>
       </c>
       <c r="P159" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q159" s="9" t="n">
         <v>1</v>
@@ -16117,8 +16117,8 @@
       <c r="S159" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T159" s="9" t="n">
-        <v>0</v>
+      <c r="T159" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U159" s="9" t="n">
         <v>0</v>
@@ -16127,7 +16127,7 @@
         <v>4</v>
       </c>
       <c r="W159" s="10" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="X159" s="10" t="n">
         <v>7</v>
@@ -16150,19 +16150,19 @@
       </c>
       <c r="B160" s="4" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>03</t>
         </is>
       </c>
       <c r="C160" s="4" t="n">
-        <v>28678501</v>
+        <v>4238711</v>
       </c>
       <c r="D160" s="4" t="inlineStr">
         <is>
-          <t>Toast the Most - GGN Club A</t>
+          <t>Turning Point Toastmasters</t>
         </is>
       </c>
       <c r="E160" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F160" s="6" t="n">
         <v>10</v>
@@ -16176,13 +16176,13 @@
         </is>
       </c>
       <c r="I160" s="4" t="n">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="J160" s="4" t="n">
-        <v>41</v>
+        <v>21</v>
       </c>
       <c r="K160" s="4" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="L160" s="4" t="inlineStr">
         <is>
@@ -16203,7 +16203,7 @@
         </is>
       </c>
       <c r="P160" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q160" s="9" t="n">
         <v>1</v>
@@ -16220,11 +16220,11 @@
       <c r="U160" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V160" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W160" s="9" t="n">
-        <v>0</v>
+      <c r="V160" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W160" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="X160" s="10" t="n">
         <v>7</v>
@@ -16251,11 +16251,11 @@
         </is>
       </c>
       <c r="C161" s="4" t="n">
-        <v>28678502</v>
+        <v>28678501</v>
       </c>
       <c r="D161" s="4" t="inlineStr">
         <is>
-          <t>Toast the Most - GGN Club B</t>
+          <t>Toast the Most - GGN Club A</t>
         </is>
       </c>
       <c r="E161" s="5" t="n">
@@ -16273,10 +16273,10 @@
         </is>
       </c>
       <c r="I161" s="4" t="n">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="J161" s="4" t="n">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="K161" s="4" t="n">
         <v>0</v>
@@ -16303,7 +16303,7 @@
         <v>0</v>
       </c>
       <c r="Q161" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R161" s="9" t="n">
         <v>0</v>
@@ -16324,7 +16324,7 @@
         <v>0</v>
       </c>
       <c r="X161" s="10" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y161" s="9" t="n">
         <v>0</v>
@@ -16348,15 +16348,15 @@
         </is>
       </c>
       <c r="C162" s="4" t="n">
-        <v>28676260</v>
+        <v>28678502</v>
       </c>
       <c r="D162" s="4" t="inlineStr">
         <is>
-          <t>Toastmasters at Gartner India</t>
+          <t>Toast the Most - GGN Club B</t>
         </is>
       </c>
       <c r="E162" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F162" s="6" t="n">
         <v>10</v>
@@ -16370,17 +16370,17 @@
         </is>
       </c>
       <c r="I162" s="4" t="n">
-        <v>10</v>
+        <v>34</v>
       </c>
       <c r="J162" s="4" t="n">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="K162" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L162" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>0</v>
+      </c>
+      <c r="L162" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M162" s="7" t="n">
@@ -16415,19 +16415,19 @@
         <v>0</v>
       </c>
       <c r="V162" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W162" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X162" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Y162" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z162" s="9" t="n">
-        <v>0</v>
+      <c r="Z162" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA162" s="10" t="n">
         <v>1</v>
@@ -16445,11 +16445,11 @@
         </is>
       </c>
       <c r="C163" s="4" t="n">
-        <v>28678892</v>
+        <v>28676260</v>
       </c>
       <c r="D163" s="4" t="inlineStr">
         <is>
-          <t>Toastmasters BSC Gurgaon</t>
+          <t>Toastmasters at Gartner India</t>
         </is>
       </c>
       <c r="E163" s="5" t="n">
@@ -16467,13 +16467,13 @@
         </is>
       </c>
       <c r="I163" s="4" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="J163" s="4" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="K163" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L163" s="8" t="inlineStr">
         <is>
@@ -16494,7 +16494,7 @@
         </is>
       </c>
       <c r="P163" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q163" s="9" t="n">
         <v>0</v>
@@ -16512,13 +16512,13 @@
         <v>0</v>
       </c>
       <c r="V163" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W163" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X163" s="9" t="n">
-        <v>2</v>
+      <c r="X163" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y163" s="9" t="n">
         <v>0</v>
@@ -16542,11 +16542,11 @@
         </is>
       </c>
       <c r="C164" s="4" t="n">
-        <v>7428610</v>
+        <v>28678892</v>
       </c>
       <c r="D164" s="4" t="inlineStr">
         <is>
-          <t>Xceedance Tikri Toastmasters</t>
+          <t>Toastmasters BSC Gurgaon</t>
         </is>
       </c>
       <c r="E164" s="5" t="n">
@@ -16564,17 +16564,17 @@
         </is>
       </c>
       <c r="I164" s="4" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="J164" s="4" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="K164" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L164" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+      <c r="L164" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M164" s="7" t="n">
@@ -16615,7 +16615,7 @@
         <v>0</v>
       </c>
       <c r="X164" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y164" s="9" t="n">
         <v>0</v>
@@ -16627,8 +16627,105 @@
         <v>1</v>
       </c>
     </row>
+    <row r="165">
+      <c r="A165" s="4" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="B165" s="4" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="C165" s="4" t="n">
+        <v>7428610</v>
+      </c>
+      <c r="D165" s="4" t="inlineStr">
+        <is>
+          <t>Xceedance Tikri Toastmasters</t>
+        </is>
+      </c>
+      <c r="E165" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F165" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="G165" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="H165" s="4" t="inlineStr">
+        <is>
+          <t>Smedley</t>
+        </is>
+      </c>
+      <c r="I165" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="J165" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="K165" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L165" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="M165" s="7" t="n">
+        <v>46446</v>
+      </c>
+      <c r="N165" s="4" t="inlineStr">
+        <is>
+          <t>Officers trained Nov-Feb</t>
+        </is>
+      </c>
+      <c r="O165" s="8" t="inlineStr">
+        <is>
+          <t>not yet</t>
+        </is>
+      </c>
+      <c r="P165" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q165" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R165" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S165" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T165" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U165" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V165" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W165" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X165" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y165" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z165" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA165" s="10" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AA164"/>
+  <autoFilter ref="A1:AA165"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -16748,7 +16845,7 @@
         <v>6</v>
       </c>
       <c r="D3" t="n">
-        <v>1.33</v>
+        <v>1.67</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -16781,7 +16878,7 @@
         <v>5</v>
       </c>
       <c r="D4" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -16814,7 +16911,7 @@
         <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -16847,13 +16944,13 @@
         <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>2.6</v>
+        <v>3</v>
       </c>
       <c r="E6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -16979,7 +17076,7 @@
         <v>5</v>
       </c>
       <c r="D10" t="n">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
       <c r="E10" t="n">
         <v>1</v>
@@ -17012,7 +17109,7 @@
         <v>5</v>
       </c>
       <c r="D11" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -17045,7 +17142,7 @@
         <v>6</v>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -17177,7 +17274,7 @@
         <v>5</v>
       </c>
       <c r="D16" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -17210,7 +17307,7 @@
         <v>5</v>
       </c>
       <c r="D17" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -17243,7 +17340,7 @@
         <v>6</v>
       </c>
       <c r="D18" t="n">
-        <v>1.17</v>
+        <v>1.33</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -17273,16 +17370,16 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D19" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -17342,7 +17439,7 @@
         <v>4</v>
       </c>
       <c r="D21" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="E21" t="n">
         <v>1</v>
@@ -17408,7 +17505,7 @@
         <v>5</v>
       </c>
       <c r="D23" t="n">
-        <v>2.4</v>
+        <v>2.8</v>
       </c>
       <c r="E23" t="n">
         <v>1</v>
@@ -17507,7 +17604,7 @@
         <v>7</v>
       </c>
       <c r="D26" t="n">
-        <v>1.29</v>
+        <v>1.57</v>
       </c>
       <c r="E26" t="n">
         <v>1</v>
@@ -17606,7 +17703,7 @@
         <v>6</v>
       </c>
       <c r="D29" t="n">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>
@@ -17738,7 +17835,7 @@
         <v>4</v>
       </c>
       <c r="D33" t="n">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="E33" t="n">
         <v>0</v>
@@ -17771,7 +17868,7 @@
         <v>5</v>
       </c>
       <c r="D34" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="E34" t="n">
         <v>0</v>

--- a/docs/d/224/inyear.xlsx
+++ b/docs/d/224/inyear.xlsx
@@ -12,7 +12,7 @@
     <sheet name="By Area" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Club Health'!$A$1:$AA$165</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Club Health'!$A$1:$AA$167</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'By Area'!$A$1:$I$34</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 03-Oct-2026. Built 2026-10-04 12:23 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:33 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>269 days remain until 30 June 2027, when these scores become final.</t>
+          <t>262 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (88 days) - 18 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (81 days) - 18 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (147 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (140 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (178 days) - 74 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (171 days) - 74 clubs short</t>
         </is>
       </c>
     </row>
@@ -647,7 +647,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA165"/>
+  <dimension ref="A1:AA167"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -850,13 +850,13 @@
         </is>
       </c>
       <c r="I2" s="4" t="n">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="J2" s="4" t="n">
         <v>37</v>
       </c>
       <c r="K2" s="4" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="L2" s="4" t="inlineStr">
         <is>
@@ -947,17 +947,17 @@
         </is>
       </c>
       <c r="I3" s="4" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="J3" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K3" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="L3" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>0</v>
+      </c>
+      <c r="L3" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M3" s="7" t="n">
@@ -1432,13 +1432,13 @@
         </is>
       </c>
       <c r="I8" s="4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J8" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L8" s="8" t="inlineStr">
         <is>
@@ -1477,7 +1477,7 @@
         <v>0</v>
       </c>
       <c r="V8" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W8" s="9" t="n">
         <v>0</v>
@@ -1529,13 +1529,13 @@
         </is>
       </c>
       <c r="I9" s="4" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="J9" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L9" s="8" t="inlineStr">
         <is>
@@ -1626,13 +1626,13 @@
         </is>
       </c>
       <c r="I10" s="4" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="J10" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
@@ -1917,13 +1917,13 @@
         </is>
       </c>
       <c r="I13" s="4" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="J13" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>1</v>
+        <v>-5</v>
       </c>
       <c r="L13" s="8" t="inlineStr">
         <is>
@@ -2014,13 +2014,13 @@
         </is>
       </c>
       <c r="I14" s="4" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="J14" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="L14" s="8" t="inlineStr">
         <is>
@@ -2111,13 +2111,13 @@
         </is>
       </c>
       <c r="I15" s="4" t="n">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="J15" s="4" t="n">
         <v>31</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>1</v>
+        <v>-10</v>
       </c>
       <c r="L15" s="4" t="inlineStr">
         <is>
@@ -2194,7 +2194,7 @@
         </is>
       </c>
       <c r="E16" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F16" s="6" t="n">
         <v>10</v>
@@ -2208,13 +2208,13 @@
         </is>
       </c>
       <c r="I16" s="4" t="n">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="J16" s="4" t="n">
         <v>33</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="L16" s="4" t="inlineStr">
         <is>
@@ -2252,11 +2252,11 @@
       <c r="U16" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V16" s="9" t="n">
-        <v>0</v>
+      <c r="V16" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W16" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X16" s="10" t="n">
         <v>7</v>
@@ -2305,17 +2305,17 @@
         </is>
       </c>
       <c r="I17" s="4" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="J17" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-10</v>
+      </c>
+      <c r="L17" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M17" s="7" t="n">
@@ -2402,13 +2402,13 @@
         </is>
       </c>
       <c r="I18" s="4" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J18" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L18" s="4" t="inlineStr">
         <is>
@@ -2447,7 +2447,7 @@
         <v>0</v>
       </c>
       <c r="V18" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W18" s="9" t="n">
         <v>0</v>
@@ -2499,13 +2499,13 @@
         </is>
       </c>
       <c r="I19" s="4" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="J19" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>0</v>
+        <v>-9</v>
       </c>
       <c r="L19" s="8" t="inlineStr">
         <is>
@@ -2596,13 +2596,13 @@
         </is>
       </c>
       <c r="I20" s="4" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J20" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L20" s="8" t="inlineStr">
         <is>
@@ -2641,7 +2641,7 @@
         <v>0</v>
       </c>
       <c r="V20" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W20" s="9" t="n">
         <v>0</v>
@@ -2693,17 +2693,17 @@
         </is>
       </c>
       <c r="I21" s="4" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="J21" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-21</v>
+      </c>
+      <c r="L21" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M21" s="7" t="n">
@@ -2790,13 +2790,13 @@
         </is>
       </c>
       <c r="I22" s="4" t="n">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="J22" s="4" t="n">
         <v>38</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>7</v>
+        <v>-6</v>
       </c>
       <c r="L22" s="4" t="inlineStr">
         <is>
@@ -2873,7 +2873,7 @@
         </is>
       </c>
       <c r="E23" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F23" s="6" t="n">
         <v>10</v>
@@ -2887,13 +2887,13 @@
         </is>
       </c>
       <c r="I23" s="4" t="n">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="J23" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>7</v>
+        <v>-2</v>
       </c>
       <c r="L23" s="4" t="inlineStr">
         <is>
@@ -2934,8 +2934,8 @@
       <c r="V23" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W23" s="9" t="n">
-        <v>3</v>
+      <c r="W23" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="X23" s="10" t="n">
         <v>6</v>
@@ -2970,7 +2970,7 @@
         </is>
       </c>
       <c r="E24" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F24" s="6" t="n">
         <v>10</v>
@@ -2984,13 +2984,13 @@
         </is>
       </c>
       <c r="I24" s="4" t="n">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="J24" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>7</v>
+        <v>-7</v>
       </c>
       <c r="L24" s="4" t="inlineStr">
         <is>
@@ -3031,8 +3031,8 @@
       <c r="V24" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W24" s="9" t="n">
-        <v>3</v>
+      <c r="W24" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="X24" s="10" t="n">
         <v>7</v>
@@ -3081,13 +3081,13 @@
         </is>
       </c>
       <c r="I25" s="4" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="J25" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>2</v>
+        <v>-2</v>
       </c>
       <c r="L25" s="8" t="inlineStr">
         <is>
@@ -3126,7 +3126,7 @@
         <v>0</v>
       </c>
       <c r="V25" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W25" s="9" t="n">
         <v>0</v>
@@ -3178,13 +3178,13 @@
         </is>
       </c>
       <c r="I26" s="4" t="n">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="J26" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>8</v>
+        <v>-5</v>
       </c>
       <c r="L26" s="4" t="inlineStr">
         <is>
@@ -3275,13 +3275,13 @@
         </is>
       </c>
       <c r="I27" s="4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J27" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L27" s="8" t="inlineStr">
         <is>
@@ -3320,7 +3320,7 @@
         <v>0</v>
       </c>
       <c r="V27" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W27" s="9" t="n">
         <v>0</v>
@@ -3372,17 +3372,17 @@
         </is>
       </c>
       <c r="I28" s="4" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="J28" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L28" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-13</v>
+      </c>
+      <c r="L28" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M28" s="7" t="n">
@@ -3469,17 +3469,17 @@
         </is>
       </c>
       <c r="I29" s="4" t="n">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="J29" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="L29" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-10</v>
+      </c>
+      <c r="L29" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M29" s="7" t="n">
@@ -3566,13 +3566,13 @@
         </is>
       </c>
       <c r="I30" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J30" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L30" s="8" t="inlineStr">
         <is>
@@ -3663,13 +3663,13 @@
         </is>
       </c>
       <c r="I31" s="4" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J31" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="L31" s="8" t="inlineStr">
         <is>
@@ -3760,17 +3760,17 @@
         </is>
       </c>
       <c r="I32" s="4" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J32" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L32" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-3</v>
+      </c>
+      <c r="L32" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M32" s="7" t="n">
@@ -3805,7 +3805,7 @@
         <v>0</v>
       </c>
       <c r="V32" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W32" s="9" t="n">
         <v>0</v>
@@ -3857,13 +3857,13 @@
         </is>
       </c>
       <c r="I33" s="4" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="J33" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="L33" s="8" t="inlineStr">
         <is>
@@ -3902,7 +3902,7 @@
         <v>0</v>
       </c>
       <c r="V33" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W33" s="9" t="n">
         <v>0</v>
@@ -3954,17 +3954,17 @@
         </is>
       </c>
       <c r="I34" s="4" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="J34" s="4" t="n">
         <v>24</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L34" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-24</v>
+      </c>
+      <c r="L34" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M34" s="7" t="n">
@@ -4051,17 +4051,17 @@
         </is>
       </c>
       <c r="I35" s="4" t="n">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="J35" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L35" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-10</v>
+      </c>
+      <c r="L35" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M35" s="7" t="n">
@@ -4148,13 +4148,13 @@
         </is>
       </c>
       <c r="I36" s="4" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="J36" s="4" t="n">
         <v>5</v>
       </c>
       <c r="K36" s="4" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="L36" s="4" t="inlineStr">
         <is>
@@ -4231,7 +4231,7 @@
         </is>
       </c>
       <c r="E37" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F37" s="6" t="n">
         <v>10</v>
@@ -4245,17 +4245,17 @@
         </is>
       </c>
       <c r="I37" s="4" t="n">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="J37" s="4" t="n">
         <v>28</v>
       </c>
       <c r="K37" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L37" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-14</v>
+      </c>
+      <c r="L37" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M37" s="7" t="n">
@@ -4280,8 +4280,8 @@
       <c r="R37" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S37" s="9" t="n">
-        <v>1</v>
+      <c r="S37" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T37" s="9" t="n">
         <v>0</v>
@@ -4342,13 +4342,13 @@
         </is>
       </c>
       <c r="I38" s="4" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="J38" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K38" s="4" t="n">
-        <v>1</v>
+        <v>-5</v>
       </c>
       <c r="L38" s="8" t="inlineStr">
         <is>
@@ -4387,7 +4387,7 @@
         <v>0</v>
       </c>
       <c r="V38" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W38" s="9" t="n">
         <v>0</v>
@@ -4439,13 +4439,13 @@
         </is>
       </c>
       <c r="I39" s="4" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="J39" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K39" s="4" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="L39" s="8" t="inlineStr">
         <is>
@@ -4536,13 +4536,13 @@
         </is>
       </c>
       <c r="I40" s="4" t="n">
-        <v>55</v>
+        <v>30</v>
       </c>
       <c r="J40" s="4" t="n">
         <v>44</v>
       </c>
       <c r="K40" s="4" t="n">
-        <v>11</v>
+        <v>-14</v>
       </c>
       <c r="L40" s="4" t="inlineStr">
         <is>
@@ -4572,7 +4572,7 @@
         <v>0</v>
       </c>
       <c r="S40" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T40" s="10" t="n">
         <v>1</v>
@@ -4584,7 +4584,7 @@
         <v>4</v>
       </c>
       <c r="W40" s="10" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="X40" s="10" t="n">
         <v>6</v>
@@ -4633,13 +4633,13 @@
         </is>
       </c>
       <c r="I41" s="4" t="n">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="J41" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K41" s="4" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="L41" s="4" t="inlineStr">
         <is>
@@ -4681,7 +4681,7 @@
         <v>4</v>
       </c>
       <c r="W41" s="10" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="X41" s="10" t="n">
         <v>6</v>
@@ -4730,17 +4730,17 @@
         </is>
       </c>
       <c r="I42" s="4" t="n">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="J42" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K42" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L42" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-16</v>
+      </c>
+      <c r="L42" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M42" s="7" t="n">
@@ -4827,13 +4827,13 @@
         </is>
       </c>
       <c r="I43" s="4" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="J43" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K43" s="4" t="n">
-        <v>0</v>
+        <v>-9</v>
       </c>
       <c r="L43" s="8" t="inlineStr">
         <is>
@@ -4924,13 +4924,13 @@
         </is>
       </c>
       <c r="I44" s="4" t="n">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="J44" s="4" t="n">
         <v>33</v>
       </c>
       <c r="K44" s="4" t="n">
-        <v>0</v>
+        <v>-13</v>
       </c>
       <c r="L44" s="4" t="inlineStr">
         <is>
@@ -4969,7 +4969,7 @@
         <v>0</v>
       </c>
       <c r="V44" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W44" s="9" t="n">
         <v>0</v>
@@ -5021,13 +5021,13 @@
         </is>
       </c>
       <c r="I45" s="4" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="J45" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K45" s="4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L45" s="4" t="inlineStr">
         <is>
@@ -5066,7 +5066,7 @@
         <v>0</v>
       </c>
       <c r="V45" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W45" s="9" t="n">
         <v>0</v>
@@ -5118,13 +5118,13 @@
         </is>
       </c>
       <c r="I46" s="4" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J46" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K46" s="4" t="n">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="L46" s="8" t="inlineStr">
         <is>
@@ -5215,13 +5215,13 @@
         </is>
       </c>
       <c r="I47" s="4" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="J47" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K47" s="4" t="n">
-        <v>0</v>
+        <v>-19</v>
       </c>
       <c r="L47" s="8" t="inlineStr">
         <is>
@@ -5409,13 +5409,13 @@
         </is>
       </c>
       <c r="I49" s="4" t="n">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="J49" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K49" s="4" t="n">
-        <v>8</v>
+        <v>-5</v>
       </c>
       <c r="L49" s="4" t="inlineStr">
         <is>
@@ -5457,7 +5457,7 @@
         <v>4</v>
       </c>
       <c r="W49" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="X49" s="10" t="n">
         <v>7</v>
@@ -5506,13 +5506,13 @@
         </is>
       </c>
       <c r="I50" s="4" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J50" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K50" s="4" t="n">
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="L50" s="8" t="inlineStr">
         <is>
@@ -5603,13 +5603,13 @@
         </is>
       </c>
       <c r="I51" s="4" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="J51" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K51" s="4" t="n">
-        <v>1</v>
+        <v>-7</v>
       </c>
       <c r="L51" s="8" t="inlineStr">
         <is>
@@ -5700,17 +5700,17 @@
         </is>
       </c>
       <c r="I52" s="4" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="J52" s="4" t="n">
         <v>0</v>
       </c>
       <c r="K52" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L52" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>7</v>
+      </c>
+      <c r="L52" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M52" s="7" t="n">
@@ -5745,7 +5745,7 @@
         <v>0</v>
       </c>
       <c r="V52" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W52" s="9" t="n">
         <v>0</v>
@@ -5783,7 +5783,7 @@
         </is>
       </c>
       <c r="E53" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F53" s="6" t="n">
         <v>10</v>
@@ -5797,13 +5797,13 @@
         </is>
       </c>
       <c r="I53" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J53" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K53" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L53" s="8" t="inlineStr">
         <is>
@@ -5841,11 +5841,11 @@
       <c r="U53" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V53" s="9" t="n">
-        <v>0</v>
+      <c r="V53" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W53" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X53" s="10" t="n">
         <v>7</v>
@@ -5880,7 +5880,7 @@
         </is>
       </c>
       <c r="E54" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F54" s="6" t="n">
         <v>10</v>
@@ -5894,13 +5894,13 @@
         </is>
       </c>
       <c r="I54" s="4" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="J54" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K54" s="4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L54" s="4" t="inlineStr">
         <is>
@@ -5938,11 +5938,11 @@
       <c r="U54" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V54" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W54" s="9" t="n">
-        <v>0</v>
+      <c r="V54" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W54" s="10" t="n">
+        <v>8</v>
       </c>
       <c r="X54" s="10" t="n">
         <v>7</v>
@@ -6088,17 +6088,17 @@
         </is>
       </c>
       <c r="I56" s="4" t="n">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="J56" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K56" s="4" t="n">
-        <v>13</v>
-      </c>
-      <c r="L56" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-7</v>
+      </c>
+      <c r="L56" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M56" s="7" t="n">
@@ -6185,13 +6185,13 @@
         </is>
       </c>
       <c r="I57" s="4" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="J57" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K57" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L57" s="8" t="inlineStr">
         <is>
@@ -6282,13 +6282,13 @@
         </is>
       </c>
       <c r="I58" s="4" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="J58" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K58" s="4" t="n">
-        <v>1</v>
+        <v>-4</v>
       </c>
       <c r="L58" s="8" t="inlineStr">
         <is>
@@ -6379,13 +6379,13 @@
         </is>
       </c>
       <c r="I59" s="4" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="J59" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K59" s="4" t="n">
-        <v>1</v>
+        <v>-5</v>
       </c>
       <c r="L59" s="8" t="inlineStr">
         <is>
@@ -6424,7 +6424,7 @@
         <v>0</v>
       </c>
       <c r="V59" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W59" s="9" t="n">
         <v>0</v>
@@ -6476,17 +6476,17 @@
         </is>
       </c>
       <c r="I60" s="4" t="n">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="J60" s="4" t="n">
         <v>24</v>
       </c>
       <c r="K60" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L60" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-23</v>
+      </c>
+      <c r="L60" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M60" s="7" t="n">
@@ -6573,13 +6573,13 @@
         </is>
       </c>
       <c r="I61" s="4" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="J61" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K61" s="4" t="n">
-        <v>1</v>
+        <v>-3</v>
       </c>
       <c r="L61" s="8" t="inlineStr">
         <is>
@@ -6670,13 +6670,13 @@
         </is>
       </c>
       <c r="I62" s="4" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="J62" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K62" s="4" t="n">
-        <v>0</v>
+        <v>-11</v>
       </c>
       <c r="L62" s="8" t="inlineStr">
         <is>
@@ -6767,13 +6767,13 @@
         </is>
       </c>
       <c r="I63" s="4" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="J63" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K63" s="4" t="n">
-        <v>4</v>
+        <v>-4</v>
       </c>
       <c r="L63" s="8" t="inlineStr">
         <is>
@@ -6815,7 +6815,7 @@
         <v>4</v>
       </c>
       <c r="W63" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X63" s="10" t="n">
         <v>7</v>
@@ -6864,17 +6864,17 @@
         </is>
       </c>
       <c r="I64" s="4" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="J64" s="4" t="n">
         <v>51</v>
       </c>
       <c r="K64" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L64" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-51</v>
+      </c>
+      <c r="L64" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M64" s="7" t="n">
@@ -7106,7 +7106,7 @@
         <v>4</v>
       </c>
       <c r="W66" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X66" s="10" t="n">
         <v>7</v>
@@ -7155,13 +7155,13 @@
         </is>
       </c>
       <c r="I67" s="4" t="n">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="J67" s="4" t="n">
         <v>33</v>
       </c>
       <c r="K67" s="4" t="n">
-        <v>15</v>
+        <v>-5</v>
       </c>
       <c r="L67" s="4" t="inlineStr">
         <is>
@@ -7252,17 +7252,17 @@
         </is>
       </c>
       <c r="I68" s="4" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="J68" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K68" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L68" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-10</v>
+      </c>
+      <c r="L68" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M68" s="7" t="n">
@@ -7335,7 +7335,7 @@
         </is>
       </c>
       <c r="E69" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F69" s="6" t="n">
         <v>10</v>
@@ -7349,13 +7349,13 @@
         </is>
       </c>
       <c r="I69" s="4" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="J69" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K69" s="4" t="n">
-        <v>2</v>
+        <v>-2</v>
       </c>
       <c r="L69" s="8" t="inlineStr">
         <is>
@@ -7376,7 +7376,7 @@
         </is>
       </c>
       <c r="P69" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q69" s="9" t="n">
         <v>0</v>
@@ -7393,8 +7393,8 @@
       <c r="U69" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V69" s="9" t="n">
-        <v>2</v>
+      <c r="V69" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W69" s="9" t="n">
         <v>0</v>
@@ -7446,17 +7446,17 @@
         </is>
       </c>
       <c r="I70" s="4" t="n">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="J70" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K70" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L70" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-7</v>
+      </c>
+      <c r="L70" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M70" s="7" t="n">
@@ -7491,7 +7491,7 @@
         <v>1</v>
       </c>
       <c r="V70" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W70" s="9" t="n">
         <v>0</v>
@@ -7543,17 +7543,17 @@
         </is>
       </c>
       <c r="I71" s="4" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="J71" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K71" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L71" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-17</v>
+      </c>
+      <c r="L71" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M71" s="7" t="n">
@@ -7640,13 +7640,13 @@
         </is>
       </c>
       <c r="I72" s="4" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J72" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K72" s="4" t="n">
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="L72" s="8" t="inlineStr">
         <is>
@@ -7737,13 +7737,13 @@
         </is>
       </c>
       <c r="I73" s="4" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="J73" s="4" t="n">
         <v>0</v>
       </c>
       <c r="K73" s="4" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="L73" s="4" t="inlineStr">
         <is>
@@ -7773,7 +7773,7 @@
         <v>0</v>
       </c>
       <c r="S73" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T73" s="9" t="n">
         <v>0</v>
@@ -7834,13 +7834,13 @@
         </is>
       </c>
       <c r="I74" s="4" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="J74" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K74" s="4" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="L74" s="4" t="inlineStr">
         <is>
@@ -7917,7 +7917,7 @@
         </is>
       </c>
       <c r="E75" s="5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F75" s="6" t="n">
         <v>10</v>
@@ -7931,13 +7931,13 @@
         </is>
       </c>
       <c r="I75" s="4" t="n">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="J75" s="4" t="n">
         <v>30</v>
       </c>
       <c r="K75" s="4" t="n">
-        <v>1</v>
+        <v>-3</v>
       </c>
       <c r="L75" s="4" t="inlineStr">
         <is>
@@ -7975,11 +7975,11 @@
       <c r="U75" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V75" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="W75" s="9" t="n">
-        <v>0</v>
+      <c r="V75" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W75" s="10" t="n">
+        <v>6</v>
       </c>
       <c r="X75" s="10" t="n">
         <v>7</v>
@@ -8014,7 +8014,7 @@
         </is>
       </c>
       <c r="E76" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F76" s="6" t="n">
         <v>10</v>
@@ -8028,17 +8028,17 @@
         </is>
       </c>
       <c r="I76" s="4" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="J76" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K76" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="L76" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-2</v>
+      </c>
+      <c r="L76" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M76" s="7" t="n">
@@ -8075,8 +8075,8 @@
       <c r="V76" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W76" s="9" t="n">
-        <v>1</v>
+      <c r="W76" s="10" t="n">
+        <v>8</v>
       </c>
       <c r="X76" s="10" t="n">
         <v>4</v>
@@ -8125,13 +8125,13 @@
         </is>
       </c>
       <c r="I77" s="4" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J77" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K77" s="4" t="n">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="L77" s="8" t="inlineStr">
         <is>
@@ -8208,7 +8208,7 @@
         </is>
       </c>
       <c r="E78" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F78" s="6" t="n">
         <v>10</v>
@@ -8258,7 +8258,7 @@
         <v>0</v>
       </c>
       <c r="S78" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T78" s="10" t="n">
         <v>1</v>
@@ -8266,11 +8266,11 @@
       <c r="U78" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V78" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="W78" s="9" t="n">
-        <v>0</v>
+      <c r="V78" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W78" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="X78" s="10" t="n">
         <v>6</v>
@@ -8416,17 +8416,17 @@
         </is>
       </c>
       <c r="I80" s="4" t="n">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="J80" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K80" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="L80" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-4</v>
+      </c>
+      <c r="L80" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M80" s="7" t="n">
@@ -8499,7 +8499,7 @@
         </is>
       </c>
       <c r="E81" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F81" s="6" t="n">
         <v>10</v>
@@ -8513,13 +8513,13 @@
         </is>
       </c>
       <c r="I81" s="4" t="n">
-        <v>43</v>
+        <v>23</v>
       </c>
       <c r="J81" s="4" t="n">
         <v>37</v>
       </c>
       <c r="K81" s="4" t="n">
-        <v>6</v>
+        <v>-14</v>
       </c>
       <c r="L81" s="4" t="inlineStr">
         <is>
@@ -8540,7 +8540,7 @@
         </is>
       </c>
       <c r="P81" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q81" s="9" t="n">
         <v>0</v>
@@ -8560,8 +8560,8 @@
       <c r="V81" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W81" s="9" t="n">
-        <v>2</v>
+      <c r="W81" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="X81" s="10" t="n">
         <v>6</v>
@@ -8610,13 +8610,13 @@
         </is>
       </c>
       <c r="I82" s="4" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="J82" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K82" s="4" t="n">
-        <v>0</v>
+        <v>-11</v>
       </c>
       <c r="L82" s="8" t="inlineStr">
         <is>
@@ -8901,13 +8901,13 @@
         </is>
       </c>
       <c r="I85" s="4" t="n">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="J85" s="4" t="n">
         <v>29</v>
       </c>
       <c r="K85" s="4" t="n">
-        <v>3</v>
+        <v>-8</v>
       </c>
       <c r="L85" s="4" t="inlineStr">
         <is>
@@ -8998,17 +8998,17 @@
         </is>
       </c>
       <c r="I86" s="4" t="n">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="J86" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K86" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="L86" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-5</v>
+      </c>
+      <c r="L86" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M86" s="7" t="n">
@@ -9046,7 +9046,7 @@
         <v>4</v>
       </c>
       <c r="W86" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X86" s="10" t="n">
         <v>4</v>
@@ -9095,13 +9095,13 @@
         </is>
       </c>
       <c r="I87" s="4" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="J87" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K87" s="4" t="n">
-        <v>2</v>
+        <v>-7</v>
       </c>
       <c r="L87" s="8" t="inlineStr">
         <is>
@@ -9192,13 +9192,13 @@
         </is>
       </c>
       <c r="I88" s="4" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="J88" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K88" s="4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L88" s="8" t="inlineStr">
         <is>
@@ -9222,7 +9222,7 @@
         <v>0</v>
       </c>
       <c r="Q88" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R88" s="9" t="n">
         <v>0</v>
@@ -9289,13 +9289,13 @@
         </is>
       </c>
       <c r="I89" s="4" t="n">
-        <v>58</v>
+        <v>32</v>
       </c>
       <c r="J89" s="4" t="n">
         <v>43</v>
       </c>
       <c r="K89" s="4" t="n">
-        <v>15</v>
+        <v>-11</v>
       </c>
       <c r="L89" s="4" t="inlineStr">
         <is>
@@ -9337,7 +9337,7 @@
         <v>4</v>
       </c>
       <c r="W89" s="10" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="X89" s="10" t="n">
         <v>7</v>
@@ -9386,17 +9386,17 @@
         </is>
       </c>
       <c r="I90" s="4" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="J90" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K90" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="L90" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>1</v>
+      </c>
+      <c r="L90" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M90" s="7" t="n">
@@ -9413,7 +9413,7 @@
         </is>
       </c>
       <c r="P90" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q90" s="9" t="n">
         <v>0</v>
@@ -9434,7 +9434,7 @@
         <v>4</v>
       </c>
       <c r="W90" s="10" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="X90" s="10" t="n">
         <v>4</v>
@@ -9483,17 +9483,17 @@
         </is>
       </c>
       <c r="I91" s="4" t="n">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="J91" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K91" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="L91" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-16</v>
+      </c>
+      <c r="L91" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M91" s="7" t="n">
@@ -9558,15 +9558,15 @@
         </is>
       </c>
       <c r="C92" s="4" t="n">
-        <v>7827937</v>
+        <v>28681049</v>
       </c>
       <c r="D92" s="4" t="inlineStr">
         <is>
-          <t>Toastmasters Club of Storytellers</t>
+          <t>SpeakEasy IIFTD Toastmasters Club</t>
         </is>
       </c>
       <c r="E92" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F92" s="6" t="n">
         <v>10</v>
@@ -9580,17 +9580,17 @@
         </is>
       </c>
       <c r="I92" s="4" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="J92" s="4" t="n">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="K92" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="L92" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>0</v>
+      </c>
+      <c r="L92" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M92" s="7" t="n">
@@ -9610,7 +9610,7 @@
         <v>0</v>
       </c>
       <c r="Q92" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R92" s="9" t="n">
         <v>0</v>
@@ -9624,14 +9624,14 @@
       <c r="U92" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V92" s="10" t="n">
-        <v>4</v>
+      <c r="V92" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="W92" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X92" s="10" t="n">
-        <v>5</v>
+      <c r="X92" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Y92" s="9" t="n">
         <v>0</v>
@@ -9651,19 +9651,19 @@
       </c>
       <c r="B93" s="4" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>02</t>
         </is>
       </c>
       <c r="C93" s="4" t="n">
-        <v>4892008</v>
+        <v>7827937</v>
       </c>
       <c r="D93" s="4" t="inlineStr">
         <is>
-          <t>Delhi One Toastmasters</t>
+          <t>Toastmasters Club of Storytellers</t>
         </is>
       </c>
       <c r="E93" s="5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F93" s="6" t="n">
         <v>10</v>
@@ -9677,17 +9677,17 @@
         </is>
       </c>
       <c r="I93" s="4" t="n">
-        <v>39</v>
+        <v>10</v>
       </c>
       <c r="J93" s="4" t="n">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="K93" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="L93" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-1</v>
+      </c>
+      <c r="L93" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M93" s="7" t="n">
@@ -9704,16 +9704,16 @@
         </is>
       </c>
       <c r="P93" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q93" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R93" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S93" s="10" t="n">
-        <v>2</v>
+      <c r="S93" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="T93" s="9" t="n">
         <v>0</v>
@@ -9724,11 +9724,11 @@
       <c r="V93" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W93" s="10" t="n">
-        <v>4</v>
+      <c r="W93" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="X93" s="10" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Y93" s="9" t="n">
         <v>0</v>
@@ -9752,15 +9752,15 @@
         </is>
       </c>
       <c r="C94" s="4" t="n">
-        <v>858173</v>
+        <v>4892008</v>
       </c>
       <c r="D94" s="4" t="inlineStr">
         <is>
-          <t>Invictus Toastmasters</t>
+          <t>Delhi One Toastmasters</t>
         </is>
       </c>
       <c r="E94" s="5" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F94" s="6" t="n">
         <v>10</v>
@@ -9774,17 +9774,17 @@
         </is>
       </c>
       <c r="I94" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="J94" s="4" t="n">
         <v>31</v>
       </c>
-      <c r="J94" s="4" t="n">
-        <v>27</v>
-      </c>
       <c r="K94" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="L94" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-14</v>
+      </c>
+      <c r="L94" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M94" s="7" t="n">
@@ -9803,29 +9803,29 @@
       <c r="P94" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="Q94" s="10" t="n">
+      <c r="Q94" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R94" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S94" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="R94" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="S94" s="10" t="n">
-        <v>5</v>
-      </c>
-      <c r="T94" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U94" s="10" t="n">
-        <v>3</v>
+      <c r="T94" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U94" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="V94" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W94" s="9" t="n">
-        <v>0</v>
+      <c r="W94" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="X94" s="10" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y94" s="9" t="n">
         <v>0</v>
@@ -9849,15 +9849,15 @@
         </is>
       </c>
       <c r="C95" s="4" t="n">
-        <v>5749303</v>
+        <v>858173</v>
       </c>
       <c r="D95" s="4" t="inlineStr">
         <is>
-          <t>North Delhi Toastmasters Club</t>
+          <t>Invictus Toastmasters</t>
         </is>
       </c>
       <c r="E95" s="5" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F95" s="6" t="n">
         <v>10</v>
@@ -9871,17 +9871,17 @@
         </is>
       </c>
       <c r="I95" s="4" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="J95" s="4" t="n">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="K95" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L95" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>-6</v>
+      </c>
+      <c r="L95" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M95" s="7" t="n">
@@ -9903,32 +9903,32 @@
       <c r="Q95" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="R95" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S95" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="T95" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U95" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V95" s="9" t="n">
-        <v>1</v>
+      <c r="R95" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="S95" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T95" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U95" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="V95" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W95" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X95" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Y95" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z95" s="9" t="n">
-        <v>0</v>
+      <c r="Z95" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA95" s="10" t="n">
         <v>1</v>
@@ -9946,15 +9946,15 @@
         </is>
       </c>
       <c r="C96" s="4" t="n">
-        <v>3936</v>
+        <v>5749303</v>
       </c>
       <c r="D96" s="4" t="inlineStr">
         <is>
-          <t>Toastmasters Club of New Delhi</t>
+          <t>North Delhi Toastmasters Club</t>
         </is>
       </c>
       <c r="E96" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F96" s="6" t="n">
         <v>10</v>
@@ -9968,17 +9968,17 @@
         </is>
       </c>
       <c r="I96" s="4" t="n">
-        <v>49</v>
+        <v>3</v>
       </c>
       <c r="J96" s="4" t="n">
-        <v>44</v>
+        <v>13</v>
       </c>
       <c r="K96" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="L96" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-10</v>
+      </c>
+      <c r="L96" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M96" s="7" t="n">
@@ -9995,16 +9995,16 @@
         </is>
       </c>
       <c r="P96" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q96" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
+      </c>
+      <c r="Q96" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R96" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S96" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T96" s="9" t="n">
         <v>0</v>
@@ -10012,20 +10012,20 @@
       <c r="U96" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V96" s="10" t="n">
+      <c r="V96" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="W96" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X96" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W96" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="X96" s="10" t="n">
-        <v>7</v>
-      </c>
       <c r="Y96" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z96" s="10" t="n">
-        <v>1</v>
+      <c r="Z96" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA96" s="10" t="n">
         <v>1</v>
@@ -10039,19 +10039,19 @@
       </c>
       <c r="B97" s="4" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>03</t>
         </is>
       </c>
       <c r="C97" s="4" t="n">
-        <v>2959367</v>
+        <v>3936</v>
       </c>
       <c r="D97" s="4" t="inlineStr">
         <is>
-          <t>Leaders Connect Toastmasters Club</t>
+          <t>Toastmasters Club of New Delhi</t>
         </is>
       </c>
       <c r="E97" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F97" s="6" t="n">
         <v>10</v>
@@ -10065,17 +10065,17 @@
         </is>
       </c>
       <c r="I97" s="4" t="n">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="J97" s="4" t="n">
-        <v>14</v>
+        <v>44</v>
       </c>
       <c r="K97" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L97" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>-15</v>
+      </c>
+      <c r="L97" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M97" s="7" t="n">
@@ -10092,7 +10092,7 @@
         </is>
       </c>
       <c r="P97" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q97" s="9" t="n">
         <v>0</v>
@@ -10101,7 +10101,7 @@
         <v>0</v>
       </c>
       <c r="S97" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T97" s="9" t="n">
         <v>0</v>
@@ -10109,20 +10109,20 @@
       <c r="U97" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V97" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="W97" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X97" s="9" t="n">
-        <v>1</v>
+      <c r="V97" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W97" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="X97" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="Y97" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z97" s="9" t="n">
-        <v>0</v>
+      <c r="Z97" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA97" s="10" t="n">
         <v>1</v>
@@ -10140,39 +10140,39 @@
         </is>
       </c>
       <c r="C98" s="4" t="n">
-        <v>7878891</v>
+        <v>2959367</v>
       </c>
       <c r="D98" s="4" t="inlineStr">
         <is>
-          <t>Step Up Dwarka Toastmasters Club</t>
+          <t>Leaders Connect Toastmasters Club</t>
         </is>
       </c>
       <c r="E98" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F98" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="G98" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="H98" s="4" t="inlineStr">
+        <is>
+          <t>Smedley</t>
+        </is>
+      </c>
+      <c r="I98" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="F98" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="G98" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="H98" s="4" t="inlineStr">
-        <is>
-          <t>Smedley</t>
-        </is>
-      </c>
-      <c r="I98" s="4" t="n">
-        <v>31</v>
-      </c>
       <c r="J98" s="4" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="K98" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="L98" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-11</v>
+      </c>
+      <c r="L98" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M98" s="7" t="n">
@@ -10189,10 +10189,10 @@
         </is>
       </c>
       <c r="P98" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q98" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R98" s="9" t="n">
         <v>0</v>
@@ -10209,17 +10209,17 @@
       <c r="V98" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W98" s="10" t="n">
-        <v>5</v>
-      </c>
-      <c r="X98" s="10" t="n">
-        <v>4</v>
+      <c r="W98" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X98" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="Y98" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z98" s="10" t="n">
-        <v>1</v>
+      <c r="Z98" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA98" s="10" t="n">
         <v>1</v>
@@ -10237,15 +10237,15 @@
         </is>
       </c>
       <c r="C99" s="4" t="n">
-        <v>996285</v>
+        <v>7878891</v>
       </c>
       <c r="D99" s="4" t="inlineStr">
         <is>
-          <t>Toastmasters Club of Dwarka</t>
+          <t>Step Up Dwarka Toastmasters Club</t>
         </is>
       </c>
       <c r="E99" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F99" s="6" t="n">
         <v>10</v>
@@ -10262,10 +10262,10 @@
         <v>25</v>
       </c>
       <c r="J99" s="4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K99" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L99" s="4" t="inlineStr">
         <is>
@@ -10289,7 +10289,7 @@
         <v>1</v>
       </c>
       <c r="Q99" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R99" s="9" t="n">
         <v>0</v>
@@ -10306,11 +10306,11 @@
       <c r="V99" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W99" s="9" t="n">
-        <v>0</v>
+      <c r="W99" s="10" t="n">
+        <v>9</v>
       </c>
       <c r="X99" s="10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Y99" s="9" t="n">
         <v>0</v>
@@ -10334,15 +10334,15 @@
         </is>
       </c>
       <c r="C100" s="4" t="n">
-        <v>1574616</v>
+        <v>996285</v>
       </c>
       <c r="D100" s="4" t="inlineStr">
         <is>
-          <t>Toastmasters Club of West Delhi</t>
+          <t>Toastmasters Club of Dwarka</t>
         </is>
       </c>
       <c r="E100" s="5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F100" s="6" t="n">
         <v>10</v>
@@ -10356,17 +10356,17 @@
         </is>
       </c>
       <c r="I100" s="4" t="n">
-        <v>43</v>
+        <v>11</v>
       </c>
       <c r="J100" s="4" t="n">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="K100" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="L100" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-10</v>
+      </c>
+      <c r="L100" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M100" s="7" t="n">
@@ -10394,8 +10394,8 @@
       <c r="S100" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T100" s="10" t="n">
-        <v>1</v>
+      <c r="T100" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U100" s="9" t="n">
         <v>0</v>
@@ -10403,11 +10403,11 @@
       <c r="V100" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W100" s="10" t="n">
-        <v>6</v>
+      <c r="W100" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="X100" s="10" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Y100" s="9" t="n">
         <v>0</v>
@@ -10422,24 +10422,24 @@
     <row r="101">
       <c r="A101" s="4" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>E</t>
         </is>
       </c>
       <c r="B101" s="4" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>04</t>
         </is>
       </c>
       <c r="C101" s="4" t="n">
-        <v>6044728</v>
+        <v>1574616</v>
       </c>
       <c r="D101" s="4" t="inlineStr">
         <is>
-          <t>Lucknow Toastmasters Club</t>
+          <t>Toastmasters Club of West Delhi</t>
         </is>
       </c>
       <c r="E101" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F101" s="6" t="n">
         <v>10</v>
@@ -10453,13 +10453,13 @@
         </is>
       </c>
       <c r="I101" s="4" t="n">
-        <v>41</v>
+        <v>28</v>
       </c>
       <c r="J101" s="4" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="K101" s="4" t="n">
-        <v>10</v>
+        <v>-5</v>
       </c>
       <c r="L101" s="4" t="inlineStr">
         <is>
@@ -10480,7 +10480,7 @@
         </is>
       </c>
       <c r="P101" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q101" s="9" t="n">
         <v>0</v>
@@ -10491,8 +10491,8 @@
       <c r="S101" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T101" s="9" t="n">
-        <v>0</v>
+      <c r="T101" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U101" s="9" t="n">
         <v>0</v>
@@ -10501,7 +10501,7 @@
         <v>4</v>
       </c>
       <c r="W101" s="10" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="X101" s="10" t="n">
         <v>7</v>
@@ -10528,15 +10528,15 @@
         </is>
       </c>
       <c r="C102" s="4" t="n">
-        <v>28679131</v>
+        <v>6044728</v>
       </c>
       <c r="D102" s="4" t="inlineStr">
         <is>
-          <t>Renukoot Toastmasters Club</t>
+          <t>Lucknow Toastmasters Club</t>
         </is>
       </c>
       <c r="E102" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F102" s="6" t="n">
         <v>10</v>
@@ -10550,10 +10550,10 @@
         </is>
       </c>
       <c r="I102" s="4" t="n">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="J102" s="4" t="n">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="K102" s="4" t="n">
         <v>0</v>
@@ -10577,7 +10577,7 @@
         </is>
       </c>
       <c r="P102" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q102" s="9" t="n">
         <v>0</v>
@@ -10594,20 +10594,20 @@
       <c r="U102" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V102" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W102" s="9" t="n">
-        <v>0</v>
+      <c r="V102" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W102" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="X102" s="10" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="Y102" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z102" s="9" t="n">
-        <v>0</v>
+      <c r="Z102" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA102" s="10" t="n">
         <v>1</v>
@@ -10625,15 +10625,15 @@
         </is>
       </c>
       <c r="C103" s="4" t="n">
-        <v>28677670</v>
+        <v>28679131</v>
       </c>
       <c r="D103" s="4" t="inlineStr">
         <is>
-          <t>SRMS Toastmasters Club</t>
+          <t>Renukoot Toastmasters Club</t>
         </is>
       </c>
       <c r="E103" s="5" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F103" s="6" t="n">
         <v>10</v>
@@ -10647,13 +10647,13 @@
         </is>
       </c>
       <c r="I103" s="4" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="J103" s="4" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="K103" s="4" t="n">
-        <v>0</v>
+        <v>-23</v>
       </c>
       <c r="L103" s="8" t="inlineStr">
         <is>
@@ -10673,32 +10673,32 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P103" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q103" s="10" t="n">
+      <c r="P103" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="R103" s="10" t="n">
+      <c r="Q103" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R103" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S103" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T103" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U103" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V103" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W103" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X103" s="10" t="n">
         <v>4</v>
-      </c>
-      <c r="S103" s="10" t="n">
-        <v>6</v>
-      </c>
-      <c r="T103" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U103" s="10" t="n">
-        <v>10</v>
-      </c>
-      <c r="V103" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W103" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X103" s="10" t="n">
-        <v>7</v>
       </c>
       <c r="Y103" s="9" t="n">
         <v>0</v>
@@ -10722,15 +10722,15 @@
         </is>
       </c>
       <c r="C104" s="4" t="n">
-        <v>7870082</v>
+        <v>28677670</v>
       </c>
       <c r="D104" s="4" t="inlineStr">
         <is>
-          <t>Toastmasters Club of Lucknow</t>
+          <t>SRMS Toastmasters Club</t>
         </is>
       </c>
       <c r="E104" s="5" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="F104" s="6" t="n">
         <v>10</v>
@@ -10747,10 +10747,10 @@
         <v>21</v>
       </c>
       <c r="J104" s="4" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="K104" s="4" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L104" s="4" t="inlineStr">
         <is>
@@ -10770,29 +10770,29 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P104" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q104" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="R104" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S104" s="9" t="n">
-        <v>0</v>
+      <c r="P104" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q104" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="R104" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="S104" s="10" t="n">
+        <v>6</v>
       </c>
       <c r="T104" s="10" t="n">
         <v>1</v>
       </c>
       <c r="U104" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="V104" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W104" s="9" t="n">
-        <v>0</v>
+        <v>10</v>
+      </c>
+      <c r="V104" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W104" s="10" t="n">
+        <v>11</v>
       </c>
       <c r="X104" s="10" t="n">
         <v>7</v>
@@ -10800,8 +10800,8 @@
       <c r="Y104" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z104" s="10" t="n">
-        <v>1</v>
+      <c r="Z104" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA104" s="10" t="n">
         <v>1</v>
@@ -10819,15 +10819,15 @@
         </is>
       </c>
       <c r="C105" s="4" t="n">
-        <v>28676433</v>
+        <v>7870082</v>
       </c>
       <c r="D105" s="4" t="inlineStr">
         <is>
-          <t>UGI Toastmasters Club</t>
+          <t>Toastmasters Club of Lucknow</t>
         </is>
       </c>
       <c r="E105" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F105" s="6" t="n">
         <v>10</v>
@@ -10841,17 +10841,17 @@
         </is>
       </c>
       <c r="I105" s="4" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="J105" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K105" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L105" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-12</v>
+      </c>
+      <c r="L105" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M105" s="7" t="n">
@@ -10868,22 +10868,22 @@
         </is>
       </c>
       <c r="P105" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q105" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q105" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R105" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S105" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T105" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U105" s="10" t="n">
         <v>2</v>
-      </c>
-      <c r="R105" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S105" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="T105" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U105" s="9" t="n">
-        <v>0</v>
       </c>
       <c r="V105" s="9" t="n">
         <v>0</v>
@@ -10912,19 +10912,19 @@
       </c>
       <c r="B106" s="4" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>01</t>
         </is>
       </c>
       <c r="C106" s="4" t="n">
-        <v>28677813</v>
+        <v>28676433</v>
       </c>
       <c r="D106" s="4" t="inlineStr">
         <is>
-          <t>Idemia Toastmasters Club</t>
+          <t>UGI Toastmasters Club</t>
         </is>
       </c>
       <c r="E106" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F106" s="6" t="n">
         <v>10</v>
@@ -10938,17 +10938,17 @@
         </is>
       </c>
       <c r="I106" s="4" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="J106" s="4" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="K106" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L106" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-4</v>
+      </c>
+      <c r="L106" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M106" s="7" t="n">
@@ -10965,16 +10965,16 @@
         </is>
       </c>
       <c r="P106" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q106" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="Q106" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R106" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S106" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T106" s="9" t="n">
         <v>0</v>
@@ -10982,20 +10982,20 @@
       <c r="U106" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V106" s="9" t="n">
-        <v>0</v>
+      <c r="V106" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W106" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X106" s="10" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="Y106" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z106" s="9" t="n">
-        <v>0</v>
+      <c r="Z106" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA106" s="10" t="n">
         <v>1</v>
@@ -11013,11 +11013,11 @@
         </is>
       </c>
       <c r="C107" s="4" t="n">
-        <v>28679641</v>
+        <v>28677813</v>
       </c>
       <c r="D107" s="4" t="inlineStr">
         <is>
-          <t>Optimus Toastmasters Club</t>
+          <t>Idemia Toastmasters Club</t>
         </is>
       </c>
       <c r="E107" s="5" t="n">
@@ -11035,17 +11035,17 @@
         </is>
       </c>
       <c r="I107" s="4" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="J107" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K107" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L107" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-21</v>
+      </c>
+      <c r="L107" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M107" s="7" t="n">
@@ -11086,7 +11086,7 @@
         <v>0</v>
       </c>
       <c r="X107" s="10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Y107" s="9" t="n">
         <v>0</v>
@@ -11110,11 +11110,11 @@
         </is>
       </c>
       <c r="C108" s="4" t="n">
-        <v>28679152</v>
+        <v>28679641</v>
       </c>
       <c r="D108" s="4" t="inlineStr">
         <is>
-          <t>UKG Toastmasters Noida #1</t>
+          <t>Optimus Toastmasters Club</t>
         </is>
       </c>
       <c r="E108" s="5" t="n">
@@ -11132,13 +11132,13 @@
         </is>
       </c>
       <c r="I108" s="4" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="J108" s="4" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="K108" s="4" t="n">
-        <v>0</v>
+        <v>-21</v>
       </c>
       <c r="L108" s="8" t="inlineStr">
         <is>
@@ -11146,11 +11146,11 @@
         </is>
       </c>
       <c r="M108" s="7" t="n">
-        <v>46387</v>
+        <v>46446</v>
       </c>
       <c r="N108" s="4" t="inlineStr">
         <is>
-          <t>Officer list on time</t>
+          <t>Officers trained Nov-Feb</t>
         </is>
       </c>
       <c r="O108" s="8" t="inlineStr">
@@ -11183,7 +11183,7 @@
         <v>0</v>
       </c>
       <c r="X108" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Y108" s="9" t="n">
         <v>0</v>
@@ -11191,8 +11191,8 @@
       <c r="Z108" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="AA108" s="9" t="n">
-        <v>0</v>
+      <c r="AA108" s="10" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="109">
@@ -11207,11 +11207,11 @@
         </is>
       </c>
       <c r="C109" s="4" t="n">
-        <v>28679153</v>
+        <v>28679152</v>
       </c>
       <c r="D109" s="4" t="inlineStr">
         <is>
-          <t>UKG Toastmasters Noida #2</t>
+          <t>UKG Toastmasters Noida #1</t>
         </is>
       </c>
       <c r="E109" s="5" t="n">
@@ -11229,13 +11229,13 @@
         </is>
       </c>
       <c r="I109" s="4" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="J109" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K109" s="4" t="n">
-        <v>0</v>
+        <v>-12</v>
       </c>
       <c r="L109" s="8" t="inlineStr">
         <is>
@@ -11256,7 +11256,7 @@
         </is>
       </c>
       <c r="P109" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q109" s="9" t="n">
         <v>0</v>
@@ -11280,7 +11280,7 @@
         <v>0</v>
       </c>
       <c r="X109" s="10" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Y109" s="9" t="n">
         <v>0</v>
@@ -11304,11 +11304,11 @@
         </is>
       </c>
       <c r="C110" s="4" t="n">
-        <v>28679312</v>
+        <v>28679153</v>
       </c>
       <c r="D110" s="4" t="inlineStr">
         <is>
-          <t>UKG Toastmasters Noida #3</t>
+          <t>UKG Toastmasters Noida #2</t>
         </is>
       </c>
       <c r="E110" s="5" t="n">
@@ -11329,10 +11329,10 @@
         <v>0</v>
       </c>
       <c r="J110" s="4" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="K110" s="4" t="n">
-        <v>0</v>
+        <v>-12</v>
       </c>
       <c r="L110" s="8" t="inlineStr">
         <is>
@@ -11353,7 +11353,7 @@
         </is>
       </c>
       <c r="P110" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q110" s="9" t="n">
         <v>0</v>
@@ -11376,8 +11376,8 @@
       <c r="W110" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X110" s="9" t="n">
-        <v>0</v>
+      <c r="X110" s="10" t="n">
+        <v>6</v>
       </c>
       <c r="Y110" s="9" t="n">
         <v>0</v>
@@ -11401,11 +11401,11 @@
         </is>
       </c>
       <c r="C111" s="4" t="n">
-        <v>28679313</v>
+        <v>28679312</v>
       </c>
       <c r="D111" s="4" t="inlineStr">
         <is>
-          <t>UKG Toastmasters Noida #4</t>
+          <t>UKG Toastmasters Noida #3</t>
         </is>
       </c>
       <c r="E111" s="5" t="n">
@@ -11423,10 +11423,10 @@
         </is>
       </c>
       <c r="I111" s="4" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="J111" s="4" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="K111" s="4" t="n">
         <v>0</v>
@@ -11474,7 +11474,7 @@
         <v>0</v>
       </c>
       <c r="X111" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Y111" s="9" t="n">
         <v>0</v>
@@ -11494,19 +11494,19 @@
       </c>
       <c r="B112" s="4" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>02</t>
         </is>
       </c>
       <c r="C112" s="4" t="n">
-        <v>5972216</v>
+        <v>28679313</v>
       </c>
       <c r="D112" s="4" t="inlineStr">
         <is>
-          <t>Kanpur Toastmasters Club</t>
+          <t>UKG Toastmasters Noida #4</t>
         </is>
       </c>
       <c r="E112" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F112" s="6" t="n">
         <v>10</v>
@@ -11520,25 +11520,25 @@
         </is>
       </c>
       <c r="I112" s="4" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="J112" s="4" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="K112" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="L112" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-9</v>
+      </c>
+      <c r="L112" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M112" s="7" t="n">
-        <v>46446</v>
+        <v>46387</v>
       </c>
       <c r="N112" s="4" t="inlineStr">
         <is>
-          <t>Officers trained Nov-Feb</t>
+          <t>Officer list on time</t>
         </is>
       </c>
       <c r="O112" s="8" t="inlineStr">
@@ -11564,23 +11564,23 @@
       <c r="U112" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V112" s="10" t="n">
-        <v>4</v>
+      <c r="V112" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="W112" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X112" s="10" t="n">
-        <v>5</v>
+      <c r="X112" s="9" t="n">
+        <v>3</v>
       </c>
       <c r="Y112" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z112" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA112" s="10" t="n">
-        <v>1</v>
+      <c r="Z112" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA112" s="9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="113">
@@ -11595,15 +11595,15 @@
         </is>
       </c>
       <c r="C113" s="4" t="n">
-        <v>7993552</v>
+        <v>5972216</v>
       </c>
       <c r="D113" s="4" t="inlineStr">
         <is>
-          <t>Toastmasters Club IITK #01</t>
+          <t>Kanpur Toastmasters Club</t>
         </is>
       </c>
       <c r="E113" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F113" s="6" t="n">
         <v>10</v>
@@ -11617,13 +11617,13 @@
         </is>
       </c>
       <c r="I113" s="4" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="J113" s="4" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="K113" s="4" t="n">
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="L113" s="8" t="inlineStr">
         <is>
@@ -11644,10 +11644,10 @@
         </is>
       </c>
       <c r="P113" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q113" s="10" t="n">
-        <v>2</v>
+        <v>0</v>
+      </c>
+      <c r="Q113" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="R113" s="9" t="n">
         <v>0</v>
@@ -11661,8 +11661,8 @@
       <c r="U113" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V113" s="9" t="n">
-        <v>0</v>
+      <c r="V113" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W113" s="9" t="n">
         <v>0</v>
@@ -11673,8 +11673,8 @@
       <c r="Y113" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z113" s="9" t="n">
-        <v>0</v>
+      <c r="Z113" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA113" s="10" t="n">
         <v>1</v>
@@ -11692,15 +11692,15 @@
         </is>
       </c>
       <c r="C114" s="4" t="n">
-        <v>28675639</v>
+        <v>7993552</v>
       </c>
       <c r="D114" s="4" t="inlineStr">
         <is>
-          <t>Toastmasters Club IITK #02</t>
+          <t>Toastmasters Club IITK #01</t>
         </is>
       </c>
       <c r="E114" s="5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F114" s="6" t="n">
         <v>10</v>
@@ -11714,13 +11714,13 @@
         </is>
       </c>
       <c r="I114" s="4" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="J114" s="4" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="K114" s="4" t="n">
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="L114" s="8" t="inlineStr">
         <is>
@@ -11749,14 +11749,14 @@
       <c r="R114" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S114" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="T114" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U114" s="10" t="n">
-        <v>1</v>
+      <c r="S114" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T114" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U114" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="V114" s="9" t="n">
         <v>0</v>
@@ -11765,7 +11765,7 @@
         <v>0</v>
       </c>
       <c r="X114" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Y114" s="9" t="n">
         <v>0</v>
@@ -11789,11 +11789,11 @@
         </is>
       </c>
       <c r="C115" s="4" t="n">
-        <v>28676264</v>
+        <v>28675639</v>
       </c>
       <c r="D115" s="4" t="inlineStr">
         <is>
-          <t>Toastmasters Club IITK #03</t>
+          <t>Toastmasters Club IITK #02</t>
         </is>
       </c>
       <c r="E115" s="5" t="n">
@@ -11811,13 +11811,13 @@
         </is>
       </c>
       <c r="I115" s="4" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="J115" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K115" s="4" t="n">
-        <v>0</v>
+        <v>-11</v>
       </c>
       <c r="L115" s="8" t="inlineStr">
         <is>
@@ -11886,15 +11886,15 @@
         </is>
       </c>
       <c r="C116" s="4" t="n">
-        <v>28677063</v>
+        <v>28676264</v>
       </c>
       <c r="D116" s="4" t="inlineStr">
         <is>
-          <t>Toastmasters Club IITK #04</t>
+          <t>Toastmasters Club IITK #03</t>
         </is>
       </c>
       <c r="E116" s="5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F116" s="6" t="n">
         <v>10</v>
@@ -11908,13 +11908,13 @@
         </is>
       </c>
       <c r="I116" s="4" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="J116" s="4" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="K116" s="4" t="n">
-        <v>0</v>
+        <v>-11</v>
       </c>
       <c r="L116" s="8" t="inlineStr">
         <is>
@@ -11935,22 +11935,22 @@
         </is>
       </c>
       <c r="P116" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q116" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="Q116" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R116" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S116" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T116" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U116" s="9" t="n">
-        <v>0</v>
+      <c r="S116" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="T116" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U116" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V116" s="9" t="n">
         <v>0</v>
@@ -11959,7 +11959,7 @@
         <v>0</v>
       </c>
       <c r="X116" s="10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Y116" s="9" t="n">
         <v>0</v>
@@ -11983,15 +11983,15 @@
         </is>
       </c>
       <c r="C117" s="4" t="n">
-        <v>28677695</v>
+        <v>28677063</v>
       </c>
       <c r="D117" s="4" t="inlineStr">
         <is>
-          <t>Toastmasters Club IITK #05</t>
+          <t>Toastmasters Club IITK #04</t>
         </is>
       </c>
       <c r="E117" s="5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F117" s="6" t="n">
         <v>10</v>
@@ -12005,13 +12005,13 @@
         </is>
       </c>
       <c r="I117" s="4" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="J117" s="4" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="K117" s="4" t="n">
-        <v>0</v>
+        <v>-14</v>
       </c>
       <c r="L117" s="8" t="inlineStr">
         <is>
@@ -12032,22 +12032,22 @@
         </is>
       </c>
       <c r="P117" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q117" s="10" t="n">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="Q117" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="R117" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S117" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="T117" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U117" s="10" t="n">
-        <v>1</v>
+      <c r="S117" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T117" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U117" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="V117" s="9" t="n">
         <v>0</v>
@@ -12056,7 +12056,7 @@
         <v>0</v>
       </c>
       <c r="X117" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Y117" s="9" t="n">
         <v>0</v>
@@ -12076,19 +12076,19 @@
       </c>
       <c r="B118" s="4" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>03</t>
         </is>
       </c>
       <c r="C118" s="4" t="n">
-        <v>7118202</v>
+        <v>28677695</v>
       </c>
       <c r="D118" s="4" t="inlineStr">
         <is>
-          <t>IMSUC Toastmasters Club</t>
+          <t>Toastmasters Club IITK #05</t>
         </is>
       </c>
       <c r="E118" s="5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F118" s="6" t="n">
         <v>10</v>
@@ -12102,13 +12102,13 @@
         </is>
       </c>
       <c r="I118" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J118" s="4" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="K118" s="4" t="n">
-        <v>0</v>
+        <v>-11</v>
       </c>
       <c r="L118" s="8" t="inlineStr">
         <is>
@@ -12116,11 +12116,11 @@
         </is>
       </c>
       <c r="M118" s="7" t="n">
-        <v>46387</v>
+        <v>46446</v>
       </c>
       <c r="N118" s="4" t="inlineStr">
         <is>
-          <t>Officer list on time</t>
+          <t>Officers trained Nov-Feb</t>
         </is>
       </c>
       <c r="O118" s="8" t="inlineStr">
@@ -12129,22 +12129,22 @@
         </is>
       </c>
       <c r="P118" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q118" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="Q118" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R118" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S118" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T118" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U118" s="9" t="n">
-        <v>0</v>
+      <c r="S118" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="T118" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U118" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V118" s="9" t="n">
         <v>0</v>
@@ -12152,8 +12152,8 @@
       <c r="W118" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X118" s="9" t="n">
-        <v>0</v>
+      <c r="X118" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y118" s="9" t="n">
         <v>0</v>
@@ -12161,8 +12161,8 @@
       <c r="Z118" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="AA118" s="9" t="n">
-        <v>0</v>
+      <c r="AA118" s="10" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="119">
@@ -12177,15 +12177,15 @@
         </is>
       </c>
       <c r="C119" s="4" t="n">
-        <v>28678966</v>
+        <v>7118202</v>
       </c>
       <c r="D119" s="4" t="inlineStr">
         <is>
-          <t>Infosys NCR Toastmasters Club</t>
+          <t>IMSUC Toastmasters Club</t>
         </is>
       </c>
       <c r="E119" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F119" s="6" t="n">
         <v>10</v>
@@ -12199,25 +12199,25 @@
         </is>
       </c>
       <c r="I119" s="4" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J119" s="4" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="K119" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L119" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-1</v>
+      </c>
+      <c r="L119" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M119" s="7" t="n">
-        <v>46446</v>
+        <v>46387</v>
       </c>
       <c r="N119" s="4" t="inlineStr">
         <is>
-          <t>Officers trained Nov-Feb</t>
+          <t>Officer list on time</t>
         </is>
       </c>
       <c r="O119" s="8" t="inlineStr">
@@ -12249,17 +12249,17 @@
       <c r="W119" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X119" s="10" t="n">
-        <v>7</v>
+      <c r="X119" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Y119" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z119" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA119" s="10" t="n">
-        <v>1</v>
+      <c r="Z119" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA119" s="9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="120">
@@ -12274,11 +12274,11 @@
         </is>
       </c>
       <c r="C120" s="4" t="n">
-        <v>28676764</v>
+        <v>28678966</v>
       </c>
       <c r="D120" s="4" t="inlineStr">
         <is>
-          <t>Iris Toastmasters Club</t>
+          <t>Infosys NCR Toastmasters Club</t>
         </is>
       </c>
       <c r="E120" s="5" t="n">
@@ -12296,17 +12296,17 @@
         </is>
       </c>
       <c r="I120" s="4" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="J120" s="4" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="K120" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L120" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-3</v>
+      </c>
+      <c r="L120" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M120" s="7" t="n">
@@ -12331,8 +12331,8 @@
       <c r="R120" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S120" s="10" t="n">
-        <v>2</v>
+      <c r="S120" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="T120" s="9" t="n">
         <v>0</v>
@@ -12341,7 +12341,7 @@
         <v>0</v>
       </c>
       <c r="V120" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W120" s="9" t="n">
         <v>0</v>
@@ -12352,8 +12352,8 @@
       <c r="Y120" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z120" s="9" t="n">
-        <v>0</v>
+      <c r="Z120" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA120" s="10" t="n">
         <v>1</v>
@@ -12371,11 +12371,11 @@
         </is>
       </c>
       <c r="C121" s="4" t="n">
-        <v>28677828</v>
+        <v>28676764</v>
       </c>
       <c r="D121" s="4" t="inlineStr">
         <is>
-          <t>IRIS Toastmasters Club II</t>
+          <t>Iris Toastmasters Club</t>
         </is>
       </c>
       <c r="E121" s="5" t="n">
@@ -12393,17 +12393,17 @@
         </is>
       </c>
       <c r="I121" s="4" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="J121" s="4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K121" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L121" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-23</v>
+      </c>
+      <c r="L121" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M121" s="7" t="n">
@@ -12420,7 +12420,7 @@
         </is>
       </c>
       <c r="P121" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q121" s="9" t="n">
         <v>0</v>
@@ -12428,11 +12428,11 @@
       <c r="R121" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S121" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T121" s="10" t="n">
-        <v>1</v>
+      <c r="S121" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="T121" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U121" s="9" t="n">
         <v>0</v>
@@ -12444,7 +12444,7 @@
         <v>0</v>
       </c>
       <c r="X121" s="10" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="Y121" s="9" t="n">
         <v>0</v>
@@ -12468,15 +12468,15 @@
         </is>
       </c>
       <c r="C122" s="4" t="n">
-        <v>4887204</v>
+        <v>28677828</v>
       </c>
       <c r="D122" s="4" t="inlineStr">
         <is>
-          <t>Noida ExpressWay Toastmasters Club</t>
+          <t>IRIS Toastmasters Club II</t>
         </is>
       </c>
       <c r="E122" s="5" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="F122" s="6" t="n">
         <v>10</v>
@@ -12490,17 +12490,17 @@
         </is>
       </c>
       <c r="I122" s="4" t="n">
-        <v>73</v>
+        <v>0</v>
       </c>
       <c r="J122" s="4" t="n">
-        <v>52</v>
+        <v>22</v>
       </c>
       <c r="K122" s="4" t="n">
-        <v>21</v>
-      </c>
-      <c r="L122" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-22</v>
+      </c>
+      <c r="L122" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M122" s="7" t="n">
@@ -12517,37 +12517,37 @@
         </is>
       </c>
       <c r="P122" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q122" s="10" t="n">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="Q122" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="R122" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S122" s="10" t="n">
-        <v>2</v>
+      <c r="S122" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="T122" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U122" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="V122" s="10" t="n">
+      <c r="U122" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V122" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W122" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X122" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W122" s="10" t="n">
-        <v>16</v>
-      </c>
-      <c r="X122" s="10" t="n">
-        <v>7</v>
-      </c>
       <c r="Y122" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z122" s="10" t="n">
-        <v>1</v>
+      <c r="Z122" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA122" s="10" t="n">
         <v>1</v>
@@ -12565,15 +12565,15 @@
         </is>
       </c>
       <c r="C123" s="4" t="n">
-        <v>28680880</v>
+        <v>4887204</v>
       </c>
       <c r="D123" s="4" t="inlineStr">
         <is>
-          <t>SpeakUp Noida Toastmasters Club</t>
+          <t>Noida ExpressWay Toastmasters Club</t>
         </is>
       </c>
       <c r="E123" s="5" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F123" s="6" t="n">
         <v>10</v>
@@ -12587,17 +12587,17 @@
         </is>
       </c>
       <c r="I123" s="4" t="n">
-        <v>5</v>
+        <v>53</v>
       </c>
       <c r="J123" s="4" t="n">
-        <v>20</v>
+        <v>52</v>
       </c>
       <c r="K123" s="4" t="n">
-        <v>-15</v>
-      </c>
-      <c r="L123" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>1</v>
+      </c>
+      <c r="L123" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M123" s="7" t="n">
@@ -12614,31 +12614,31 @@
         </is>
       </c>
       <c r="P123" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q123" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
+      </c>
+      <c r="Q123" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R123" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S123" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T123" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U123" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V123" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W123" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X123" s="9" t="n">
-        <v>0</v>
+      <c r="S123" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="T123" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U123" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="V123" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W123" s="10" t="n">
+        <v>17</v>
+      </c>
+      <c r="X123" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="Y123" s="9" t="n">
         <v>0</v>
@@ -12662,15 +12662,15 @@
         </is>
       </c>
       <c r="C124" s="4" t="n">
-        <v>28675384</v>
+        <v>28680880</v>
       </c>
       <c r="D124" s="4" t="inlineStr">
         <is>
-          <t>Young Voices Toastmasters Club</t>
+          <t>SpeakUp Noida Toastmasters Club</t>
         </is>
       </c>
       <c r="E124" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F124" s="6" t="n">
         <v>10</v>
@@ -12684,13 +12684,13 @@
         </is>
       </c>
       <c r="I124" s="4" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="J124" s="4" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="K124" s="4" t="n">
-        <v>1</v>
+        <v>-10</v>
       </c>
       <c r="L124" s="8" t="inlineStr">
         <is>
@@ -12729,19 +12729,19 @@
         <v>0</v>
       </c>
       <c r="V124" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W124" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X124" s="10" t="n">
-        <v>4</v>
+      <c r="X124" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Y124" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z124" s="9" t="n">
-        <v>0</v>
+      <c r="Z124" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA124" s="10" t="n">
         <v>1</v>
@@ -12750,24 +12750,24 @@
     <row r="125">
       <c r="A125" s="4" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>F</t>
         </is>
       </c>
       <c r="B125" s="4" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>04</t>
         </is>
       </c>
       <c r="C125" s="4" t="n">
-        <v>28676190</v>
+        <v>28675384</v>
       </c>
       <c r="D125" s="4" t="inlineStr">
         <is>
-          <t>BE@T Toastmasters Club</t>
+          <t>Young Voices Toastmasters Club</t>
         </is>
       </c>
       <c r="E125" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F125" s="6" t="n">
         <v>10</v>
@@ -12781,17 +12781,17 @@
         </is>
       </c>
       <c r="I125" s="4" t="n">
-        <v>32</v>
+        <v>7</v>
       </c>
       <c r="J125" s="4" t="n">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="K125" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="L125" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-4</v>
+      </c>
+      <c r="L125" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M125" s="7" t="n">
@@ -12825,20 +12825,20 @@
       <c r="U125" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V125" s="10" t="n">
+      <c r="V125" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="W125" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X125" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W125" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="X125" s="10" t="n">
-        <v>6</v>
-      </c>
       <c r="Y125" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z125" s="10" t="n">
-        <v>1</v>
+      <c r="Z125" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA125" s="10" t="n">
         <v>1</v>
@@ -12856,15 +12856,15 @@
         </is>
       </c>
       <c r="C126" s="4" t="n">
-        <v>28678583</v>
+        <v>28676190</v>
       </c>
       <c r="D126" s="4" t="inlineStr">
         <is>
-          <t>Carelon Spartan Toastmasters Club</t>
+          <t>BE@T Toastmasters Club</t>
         </is>
       </c>
       <c r="E126" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F126" s="6" t="n">
         <v>10</v>
@@ -12878,17 +12878,17 @@
         </is>
       </c>
       <c r="I126" s="4" t="n">
-        <v>41</v>
+        <v>18</v>
       </c>
       <c r="J126" s="4" t="n">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="K126" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L126" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-9</v>
+      </c>
+      <c r="L126" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M126" s="7" t="n">
@@ -12907,14 +12907,14 @@
       <c r="P126" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Q126" s="10" t="n">
-        <v>2</v>
+      <c r="Q126" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="R126" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S126" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T126" s="9" t="n">
         <v>0</v>
@@ -12922,20 +12922,20 @@
       <c r="U126" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V126" s="9" t="n">
-        <v>0</v>
+      <c r="V126" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W126" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X126" s="10" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Y126" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z126" s="9" t="n">
-        <v>0</v>
+      <c r="Z126" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA126" s="10" t="n">
         <v>1</v>
@@ -12953,11 +12953,11 @@
         </is>
       </c>
       <c r="C127" s="4" t="n">
-        <v>4055055</v>
+        <v>28678583</v>
       </c>
       <c r="D127" s="4" t="inlineStr">
         <is>
-          <t>Eloquent Toastmasters Club</t>
+          <t>Carelon Spartan Toastmasters Club</t>
         </is>
       </c>
       <c r="E127" s="5" t="n">
@@ -12975,13 +12975,13 @@
         </is>
       </c>
       <c r="I127" s="4" t="n">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="J127" s="4" t="n">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="K127" s="4" t="n">
-        <v>5</v>
+        <v>-15</v>
       </c>
       <c r="L127" s="4" t="inlineStr">
         <is>
@@ -13004,8 +13004,8 @@
       <c r="P127" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Q127" s="9" t="n">
-        <v>0</v>
+      <c r="Q127" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R127" s="9" t="n">
         <v>0</v>
@@ -13026,13 +13026,13 @@
         <v>1</v>
       </c>
       <c r="X127" s="10" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="Y127" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z127" s="10" t="n">
-        <v>1</v>
+      <c r="Z127" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA127" s="10" t="n">
         <v>1</v>
@@ -13050,15 +13050,15 @@
         </is>
       </c>
       <c r="C128" s="4" t="n">
-        <v>5768974</v>
+        <v>4055055</v>
       </c>
       <c r="D128" s="4" t="inlineStr">
         <is>
-          <t>HSBC Toastmasters</t>
+          <t>Eloquent Toastmasters Club</t>
         </is>
       </c>
       <c r="E128" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F128" s="6" t="n">
         <v>10</v>
@@ -13072,17 +13072,17 @@
         </is>
       </c>
       <c r="I128" s="4" t="n">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="J128" s="4" t="n">
-        <v>8</v>
+        <v>35</v>
       </c>
       <c r="K128" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L128" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>-11</v>
+      </c>
+      <c r="L128" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M128" s="7" t="n">
@@ -13108,7 +13108,7 @@
         <v>0</v>
       </c>
       <c r="S128" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T128" s="9" t="n">
         <v>0</v>
@@ -13116,20 +13116,20 @@
       <c r="U128" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V128" s="9" t="n">
-        <v>0</v>
+      <c r="V128" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W128" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X128" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="X128" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="Y128" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z128" s="9" t="n">
-        <v>0</v>
+      <c r="Z128" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA128" s="10" t="n">
         <v>1</v>
@@ -13143,15 +13143,15 @@
       </c>
       <c r="B129" s="4" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>01</t>
         </is>
       </c>
       <c r="C129" s="4" t="n">
-        <v>3781541</v>
+        <v>5768974</v>
       </c>
       <c r="D129" s="4" t="inlineStr">
         <is>
-          <t>Amex Gurgaon Toastmasters Club</t>
+          <t>HSBC Toastmasters</t>
         </is>
       </c>
       <c r="E129" s="5" t="n">
@@ -13244,15 +13244,15 @@
         </is>
       </c>
       <c r="C130" s="4" t="n">
-        <v>5168041</v>
+        <v>3781541</v>
       </c>
       <c r="D130" s="4" t="inlineStr">
         <is>
-          <t>Gurgaon Orators Toastmasters Club</t>
+          <t>Amex Gurgaon Toastmasters Club</t>
         </is>
       </c>
       <c r="E130" s="5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F130" s="6" t="n">
         <v>10</v>
@@ -13266,17 +13266,17 @@
         </is>
       </c>
       <c r="I130" s="4" t="n">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="J130" s="4" t="n">
-        <v>37</v>
+        <v>8</v>
       </c>
       <c r="K130" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="L130" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-8</v>
+      </c>
+      <c r="L130" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M130" s="7" t="n">
@@ -13292,8 +13292,8 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P130" s="10" t="n">
-        <v>5</v>
+      <c r="P130" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Q130" s="9" t="n">
         <v>0</v>
@@ -13304,26 +13304,26 @@
       <c r="S130" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T130" s="10" t="n">
-        <v>1</v>
+      <c r="T130" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U130" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V130" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="W130" s="10" t="n">
-        <v>6</v>
-      </c>
-      <c r="X130" s="10" t="n">
-        <v>7</v>
+      <c r="V130" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W130" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X130" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Y130" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z130" s="10" t="n">
-        <v>1</v>
+      <c r="Z130" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA130" s="10" t="n">
         <v>1</v>
@@ -13341,15 +13341,15 @@
         </is>
       </c>
       <c r="C131" s="4" t="n">
-        <v>7901096</v>
+        <v>5168041</v>
       </c>
       <c r="D131" s="4" t="inlineStr">
         <is>
-          <t>Gurugram Professional Toastmasters</t>
+          <t>Gurgaon Orators Toastmasters Club</t>
         </is>
       </c>
       <c r="E131" s="5" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F131" s="6" t="n">
         <v>10</v>
@@ -13363,17 +13363,17 @@
         </is>
       </c>
       <c r="I131" s="4" t="n">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="J131" s="4" t="n">
-        <v>17</v>
+        <v>37</v>
       </c>
       <c r="K131" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L131" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>-7</v>
+      </c>
+      <c r="L131" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M131" s="7" t="n">
@@ -13389,8 +13389,8 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P131" s="9" t="n">
-        <v>0</v>
+      <c r="P131" s="10" t="n">
+        <v>8</v>
       </c>
       <c r="Q131" s="9" t="n">
         <v>0</v>
@@ -13401,17 +13401,17 @@
       <c r="S131" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T131" s="9" t="n">
-        <v>0</v>
+      <c r="T131" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U131" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V131" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="W131" s="9" t="n">
-        <v>0</v>
+      <c r="V131" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W131" s="10" t="n">
+        <v>8</v>
       </c>
       <c r="X131" s="10" t="n">
         <v>7</v>
@@ -13438,15 +13438,15 @@
         </is>
       </c>
       <c r="C132" s="4" t="n">
-        <v>28678891</v>
+        <v>7901096</v>
       </c>
       <c r="D132" s="4" t="inlineStr">
         <is>
-          <t>Hatch India Toastmasters Club</t>
+          <t>Gurugram Professional Toastmasters</t>
         </is>
       </c>
       <c r="E132" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F132" s="6" t="n">
         <v>10</v>
@@ -13460,17 +13460,17 @@
         </is>
       </c>
       <c r="I132" s="4" t="n">
-        <v>40</v>
+        <v>13</v>
       </c>
       <c r="J132" s="4" t="n">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="K132" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L132" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-4</v>
+      </c>
+      <c r="L132" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M132" s="7" t="n">
@@ -13505,19 +13505,19 @@
         <v>0</v>
       </c>
       <c r="V132" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W132" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X132" s="10" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y132" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z132" s="9" t="n">
-        <v>0</v>
+      <c r="Z132" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA132" s="10" t="n">
         <v>1</v>
@@ -13535,11 +13535,11 @@
         </is>
       </c>
       <c r="C133" s="4" t="n">
-        <v>28678612</v>
+        <v>28678891</v>
       </c>
       <c r="D133" s="4" t="inlineStr">
         <is>
-          <t>Lummus Toastmasters Club</t>
+          <t>Hatch India Toastmasters Club</t>
         </is>
       </c>
       <c r="E133" s="5" t="n">
@@ -13557,25 +13557,25 @@
         </is>
       </c>
       <c r="I133" s="4" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="J133" s="4" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="K133" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L133" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-40</v>
+      </c>
+      <c r="L133" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M133" s="7" t="n">
-        <v>46387</v>
+        <v>46446</v>
       </c>
       <c r="N133" s="4" t="inlineStr">
         <is>
-          <t>Officer list on time</t>
+          <t>Officers trained Nov-Feb</t>
         </is>
       </c>
       <c r="O133" s="8" t="inlineStr">
@@ -13584,7 +13584,7 @@
         </is>
       </c>
       <c r="P133" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q133" s="9" t="n">
         <v>0</v>
@@ -13607,17 +13607,17 @@
       <c r="W133" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X133" s="9" t="n">
-        <v>2</v>
+      <c r="X133" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="Y133" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z133" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA133" s="9" t="n">
-        <v>0</v>
+      <c r="Z133" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA133" s="10" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="134">
@@ -13632,15 +13632,15 @@
         </is>
       </c>
       <c r="C134" s="4" t="n">
-        <v>28679643</v>
+        <v>28678612</v>
       </c>
       <c r="D134" s="4" t="inlineStr">
         <is>
-          <t>Powergrid Toastmasters Club</t>
+          <t>Lummus Toastmasters Club</t>
         </is>
       </c>
       <c r="E134" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F134" s="6" t="n">
         <v>10</v>
@@ -13654,13 +13654,13 @@
         </is>
       </c>
       <c r="I134" s="4" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="J134" s="4" t="n">
-        <v>39</v>
+        <v>25</v>
       </c>
       <c r="K134" s="4" t="n">
-        <v>-31</v>
+        <v>-6</v>
       </c>
       <c r="L134" s="8" t="inlineStr">
         <is>
@@ -13668,11 +13668,11 @@
         </is>
       </c>
       <c r="M134" s="7" t="n">
-        <v>46446</v>
+        <v>46387</v>
       </c>
       <c r="N134" s="4" t="inlineStr">
         <is>
-          <t>Officers trained Nov-Feb</t>
+          <t>Officer list on time</t>
         </is>
       </c>
       <c r="O134" s="8" t="inlineStr">
@@ -13681,7 +13681,7 @@
         </is>
       </c>
       <c r="P134" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q134" s="9" t="n">
         <v>0</v>
@@ -13698,23 +13698,23 @@
       <c r="U134" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V134" s="9" t="n">
-        <v>0</v>
+      <c r="V134" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W134" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X134" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y134" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z134" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA134" s="10" t="n">
-        <v>1</v>
+      <c r="Z134" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA134" s="9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="135">
@@ -13725,19 +13725,19 @@
       </c>
       <c r="B135" s="4" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>02</t>
         </is>
       </c>
       <c r="C135" s="4" t="n">
-        <v>5949422</v>
+        <v>28679643</v>
       </c>
       <c r="D135" s="4" t="inlineStr">
         <is>
-          <t>Gurgaon Champions Toastmasters Club</t>
+          <t>Powergrid Toastmasters Club</t>
         </is>
       </c>
       <c r="E135" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F135" s="6" t="n">
         <v>10</v>
@@ -13751,13 +13751,13 @@
         </is>
       </c>
       <c r="I135" s="4" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="J135" s="4" t="n">
-        <v>11</v>
+        <v>39</v>
       </c>
       <c r="K135" s="4" t="n">
-        <v>1</v>
+        <v>-39</v>
       </c>
       <c r="L135" s="8" t="inlineStr">
         <is>
@@ -13796,7 +13796,7 @@
         <v>0</v>
       </c>
       <c r="V135" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W135" s="9" t="n">
         <v>0</v>
@@ -13807,8 +13807,8 @@
       <c r="Y135" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z135" s="10" t="n">
-        <v>1</v>
+      <c r="Z135" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA135" s="10" t="n">
         <v>1</v>
@@ -13826,15 +13826,15 @@
         </is>
       </c>
       <c r="C136" s="4" t="n">
-        <v>3321031</v>
+        <v>5949422</v>
       </c>
       <c r="D136" s="4" t="inlineStr">
         <is>
-          <t>Millennium City Toastmasters Club</t>
+          <t>Gurgaon Champions Toastmasters Club</t>
         </is>
       </c>
       <c r="E136" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F136" s="6" t="n">
         <v>10</v>
@@ -13848,17 +13848,17 @@
         </is>
       </c>
       <c r="I136" s="4" t="n">
-        <v>48</v>
+        <v>8</v>
       </c>
       <c r="J136" s="4" t="n">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="K136" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="L136" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-3</v>
+      </c>
+      <c r="L136" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M136" s="7" t="n">
@@ -13875,10 +13875,10 @@
         </is>
       </c>
       <c r="P136" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q136" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R136" s="9" t="n">
         <v>0</v>
@@ -13892,14 +13892,14 @@
       <c r="U136" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V136" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="W136" s="10" t="n">
-        <v>6</v>
-      </c>
-      <c r="X136" s="10" t="n">
-        <v>7</v>
+      <c r="V136" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="W136" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X136" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Y136" s="9" t="n">
         <v>0</v>
@@ -13923,15 +13923,15 @@
         </is>
       </c>
       <c r="C137" s="4" t="n">
-        <v>28680288</v>
+        <v>3321031</v>
       </c>
       <c r="D137" s="4" t="inlineStr">
         <is>
-          <t>Oxane Partners Toastmasters Club - Leadership Circle</t>
+          <t>Millennium City Toastmasters Club</t>
         </is>
       </c>
       <c r="E137" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F137" s="6" t="n">
         <v>10</v>
@@ -13945,13 +13945,13 @@
         </is>
       </c>
       <c r="I137" s="4" t="n">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="J137" s="4" t="n">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="K137" s="4" t="n">
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="L137" s="4" t="inlineStr">
         <is>
@@ -13972,10 +13972,10 @@
         </is>
       </c>
       <c r="P137" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q137" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R137" s="9" t="n">
         <v>0</v>
@@ -13989,20 +13989,20 @@
       <c r="U137" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V137" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W137" s="9" t="n">
-        <v>0</v>
+      <c r="V137" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W137" s="10" t="n">
+        <v>11</v>
       </c>
       <c r="X137" s="10" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="Y137" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z137" s="9" t="n">
-        <v>0</v>
+      <c r="Z137" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA137" s="10" t="n">
         <v>1</v>
@@ -14020,15 +14020,15 @@
         </is>
       </c>
       <c r="C138" s="4" t="n">
-        <v>28678659</v>
+        <v>28680288</v>
       </c>
       <c r="D138" s="4" t="inlineStr">
         <is>
-          <t>S&amp;P Global Toastmasters Club</t>
+          <t>Oxane Partners Toastmasters Club - Leadership Circle</t>
         </is>
       </c>
       <c r="E138" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F138" s="6" t="n">
         <v>10</v>
@@ -14042,17 +14042,17 @@
         </is>
       </c>
       <c r="I138" s="4" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="J138" s="4" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="K138" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L138" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>0</v>
+      </c>
+      <c r="L138" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M138" s="7" t="n">
@@ -14071,8 +14071,8 @@
       <c r="P138" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Q138" s="10" t="n">
-        <v>2</v>
+      <c r="Q138" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="R138" s="9" t="n">
         <v>0</v>
@@ -14087,19 +14087,19 @@
         <v>0</v>
       </c>
       <c r="V138" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="W138" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X138" s="10" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="Y138" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z138" s="10" t="n">
-        <v>1</v>
+      <c r="Z138" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA138" s="10" t="n">
         <v>1</v>
@@ -14117,15 +14117,15 @@
         </is>
       </c>
       <c r="C139" s="4" t="n">
-        <v>28677406</v>
+        <v>28678659</v>
       </c>
       <c r="D139" s="4" t="inlineStr">
         <is>
-          <t>Toastmasters Club at NAB India</t>
+          <t>S&amp;P Global Toastmasters Club</t>
         </is>
       </c>
       <c r="E139" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F139" s="6" t="n">
         <v>10</v>
@@ -14139,17 +14139,17 @@
         </is>
       </c>
       <c r="I139" s="4" t="n">
-        <v>40</v>
+        <v>14</v>
       </c>
       <c r="J139" s="4" t="n">
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="K139" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L139" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>2</v>
+      </c>
+      <c r="L139" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M139" s="7" t="n">
@@ -14166,11 +14166,11 @@
         </is>
       </c>
       <c r="P139" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q139" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="Q139" s="9" t="n">
-        <v>0</v>
-      </c>
       <c r="R139" s="9" t="n">
         <v>0</v>
       </c>
@@ -14184,19 +14184,19 @@
         <v>0</v>
       </c>
       <c r="V139" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W139" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X139" s="10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y139" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z139" s="9" t="n">
-        <v>0</v>
+      <c r="Z139" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA139" s="10" t="n">
         <v>1</v>
@@ -14214,15 +14214,15 @@
         </is>
       </c>
       <c r="C140" s="4" t="n">
-        <v>28680808</v>
+        <v>28677406</v>
       </c>
       <c r="D140" s="4" t="inlineStr">
         <is>
-          <t>XLRI Xpressions Toastmasters Club</t>
+          <t>Toastmasters Club at NAB India</t>
         </is>
       </c>
       <c r="E140" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F140" s="6" t="n">
         <v>10</v>
@@ -14236,13 +14236,13 @@
         </is>
       </c>
       <c r="I140" s="4" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="J140" s="4" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="K140" s="4" t="n">
-        <v>-8</v>
+        <v>-40</v>
       </c>
       <c r="L140" s="8" t="inlineStr">
         <is>
@@ -14263,7 +14263,7 @@
         </is>
       </c>
       <c r="P140" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q140" s="9" t="n">
         <v>0</v>
@@ -14286,14 +14286,14 @@
       <c r="W140" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X140" s="9" t="n">
-        <v>0</v>
+      <c r="X140" s="10" t="n">
+        <v>6</v>
       </c>
       <c r="Y140" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z140" s="10" t="n">
-        <v>1</v>
+      <c r="Z140" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA140" s="10" t="n">
         <v>1</v>
@@ -14307,15 +14307,15 @@
       </c>
       <c r="B141" s="4" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>03</t>
         </is>
       </c>
       <c r="C141" s="4" t="n">
-        <v>28675941</v>
+        <v>28680808</v>
       </c>
       <c r="D141" s="4" t="inlineStr">
         <is>
-          <t>AtkinsRealis Jewels Toastmasters Club</t>
+          <t>XLRI Xpressions Toastmasters Club</t>
         </is>
       </c>
       <c r="E141" s="5" t="n">
@@ -14333,10 +14333,10 @@
         </is>
       </c>
       <c r="I141" s="4" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="J141" s="4" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="K141" s="4" t="n">
         <v>0</v>
@@ -14369,10 +14369,10 @@
         <v>0</v>
       </c>
       <c r="S141" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="T141" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="T141" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U141" s="9" t="n">
         <v>0</v>
@@ -14389,8 +14389,8 @@
       <c r="Y141" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z141" s="9" t="n">
-        <v>0</v>
+      <c r="Z141" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA141" s="10" t="n">
         <v>1</v>
@@ -14408,15 +14408,15 @@
         </is>
       </c>
       <c r="C142" s="4" t="n">
-        <v>1407110</v>
+        <v>28675941</v>
       </c>
       <c r="D142" s="4" t="inlineStr">
         <is>
-          <t>Blue Quest</t>
+          <t>AtkinsRealis Jewels Toastmasters Club</t>
         </is>
       </c>
       <c r="E142" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F142" s="6" t="n">
         <v>10</v>
@@ -14430,13 +14430,13 @@
         </is>
       </c>
       <c r="I142" s="4" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J142" s="4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="K142" s="4" t="n">
-        <v>0</v>
+        <v>-25</v>
       </c>
       <c r="L142" s="8" t="inlineStr">
         <is>
@@ -14466,10 +14466,10 @@
         <v>0</v>
       </c>
       <c r="S142" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T142" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="T142" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U142" s="9" t="n">
         <v>0</v>
@@ -14480,8 +14480,8 @@
       <c r="W142" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X142" s="10" t="n">
-        <v>4</v>
+      <c r="X142" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Y142" s="9" t="n">
         <v>0</v>
@@ -14505,11 +14505,11 @@
         </is>
       </c>
       <c r="C143" s="4" t="n">
-        <v>3719774</v>
+        <v>1407110</v>
       </c>
       <c r="D143" s="4" t="inlineStr">
         <is>
-          <t>McDermott Speakers Toastmasters Club</t>
+          <t>Blue Quest</t>
         </is>
       </c>
       <c r="E143" s="5" t="n">
@@ -14527,17 +14527,17 @@
         </is>
       </c>
       <c r="I143" s="4" t="n">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="J143" s="4" t="n">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="K143" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L143" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-6</v>
+      </c>
+      <c r="L143" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M143" s="7" t="n">
@@ -14554,7 +14554,7 @@
         </is>
       </c>
       <c r="P143" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q143" s="9" t="n">
         <v>0</v>
@@ -14563,7 +14563,7 @@
         <v>0</v>
       </c>
       <c r="S143" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T143" s="9" t="n">
         <v>0</v>
@@ -14602,15 +14602,15 @@
         </is>
       </c>
       <c r="C144" s="4" t="n">
-        <v>6462252</v>
+        <v>3719774</v>
       </c>
       <c r="D144" s="4" t="inlineStr">
         <is>
-          <t>Move Mountains Toastmasters Club</t>
+          <t>McDermott Speakers Toastmasters Club</t>
         </is>
       </c>
       <c r="E144" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F144" s="6" t="n">
         <v>10</v>
@@ -14624,13 +14624,13 @@
         </is>
       </c>
       <c r="I144" s="4" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J144" s="4" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="K144" s="4" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="L144" s="4" t="inlineStr">
         <is>
@@ -14651,7 +14651,7 @@
         </is>
       </c>
       <c r="P144" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q144" s="9" t="n">
         <v>0</v>
@@ -14662,8 +14662,8 @@
       <c r="S144" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="T144" s="10" t="n">
-        <v>1</v>
+      <c r="T144" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U144" s="9" t="n">
         <v>0</v>
@@ -14672,16 +14672,16 @@
         <v>4</v>
       </c>
       <c r="W144" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X144" s="10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Y144" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z144" s="10" t="n">
-        <v>1</v>
+      <c r="Z144" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA144" s="10" t="n">
         <v>1</v>
@@ -14699,15 +14699,15 @@
         </is>
       </c>
       <c r="C145" s="4" t="n">
-        <v>28676033</v>
+        <v>6462252</v>
       </c>
       <c r="D145" s="4" t="inlineStr">
         <is>
-          <t>THE VANGUARDS</t>
+          <t>Move Mountains Toastmasters Club</t>
         </is>
       </c>
       <c r="E145" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F145" s="6" t="n">
         <v>10</v>
@@ -14721,25 +14721,25 @@
         </is>
       </c>
       <c r="I145" s="4" t="n">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="J145" s="4" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="K145" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="L145" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-9</v>
+      </c>
+      <c r="L145" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M145" s="7" t="n">
-        <v>46387</v>
+        <v>46446</v>
       </c>
       <c r="N145" s="4" t="inlineStr">
         <is>
-          <t>Officer list on time</t>
+          <t>Officers trained Nov-Feb</t>
         </is>
       </c>
       <c r="O145" s="8" t="inlineStr">
@@ -14757,10 +14757,10 @@
         <v>0</v>
       </c>
       <c r="S145" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T145" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="T145" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U145" s="9" t="n">
         <v>0</v>
@@ -14768,43 +14768,43 @@
       <c r="V145" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W145" s="10" t="n">
+      <c r="W145" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="X145" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="X145" s="9" t="n">
-        <v>1</v>
-      </c>
       <c r="Y145" s="9" t="n">
         <v>0</v>
       </c>
       <c r="Z145" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="AA145" s="9" t="n">
-        <v>0</v>
+      <c r="AA145" s="10" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="4" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>G</t>
         </is>
       </c>
       <c r="B146" s="4" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>04</t>
         </is>
       </c>
       <c r="C146" s="4" t="n">
-        <v>7661270</v>
+        <v>28676033</v>
       </c>
       <c r="D146" s="4" t="inlineStr">
         <is>
-          <t>Bright Beginning Toastmasters Club</t>
+          <t>THE VANGUARDS</t>
         </is>
       </c>
       <c r="E146" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F146" s="6" t="n">
         <v>10</v>
@@ -14818,25 +14818,25 @@
         </is>
       </c>
       <c r="I146" s="4" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="J146" s="4" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="K146" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L146" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>8</v>
+      </c>
+      <c r="L146" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M146" s="7" t="n">
-        <v>46446</v>
+        <v>46387</v>
       </c>
       <c r="N146" s="4" t="inlineStr">
         <is>
-          <t>Officers trained Nov-Feb</t>
+          <t>Officer list on time</t>
         </is>
       </c>
       <c r="O146" s="8" t="inlineStr">
@@ -14845,10 +14845,10 @@
         </is>
       </c>
       <c r="P146" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q146" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R146" s="9" t="n">
         <v>0</v>
@@ -14862,23 +14862,23 @@
       <c r="U146" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V146" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W146" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X146" s="10" t="n">
+      <c r="V146" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W146" s="10" t="n">
         <v>5</v>
       </c>
+      <c r="X146" s="9" t="n">
+        <v>1</v>
+      </c>
       <c r="Y146" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z146" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA146" s="10" t="n">
-        <v>1</v>
+      <c r="Z146" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA146" s="9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="147">
@@ -14893,15 +14893,15 @@
         </is>
       </c>
       <c r="C147" s="4" t="n">
-        <v>5517955</v>
+        <v>7661270</v>
       </c>
       <c r="D147" s="4" t="inlineStr">
         <is>
-          <t>Faridabad Orators Toastmasters Club</t>
+          <t>Bright Beginning Toastmasters Club</t>
         </is>
       </c>
       <c r="E147" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F147" s="6" t="n">
         <v>10</v>
@@ -14915,17 +14915,17 @@
         </is>
       </c>
       <c r="I147" s="4" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="J147" s="4" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="K147" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L147" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-9</v>
+      </c>
+      <c r="L147" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M147" s="7" t="n">
@@ -14942,10 +14942,10 @@
         </is>
       </c>
       <c r="P147" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q147" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R147" s="9" t="n">
         <v>0</v>
@@ -14953,11 +14953,11 @@
       <c r="S147" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T147" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U147" s="10" t="n">
-        <v>1</v>
+      <c r="T147" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U147" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="V147" s="9" t="n">
         <v>0</v>
@@ -14971,8 +14971,8 @@
       <c r="Y147" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z147" s="10" t="n">
-        <v>1</v>
+      <c r="Z147" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA147" s="10" t="n">
         <v>1</v>
@@ -14990,11 +14990,11 @@
         </is>
       </c>
       <c r="C148" s="4" t="n">
-        <v>1867633</v>
+        <v>5517955</v>
       </c>
       <c r="D148" s="4" t="inlineStr">
         <is>
-          <t>Faridabad Toastmasters Club</t>
+          <t>Faridabad Orators Toastmasters Club</t>
         </is>
       </c>
       <c r="E148" s="5" t="n">
@@ -15012,17 +15012,17 @@
         </is>
       </c>
       <c r="I148" s="4" t="n">
-        <v>39</v>
+        <v>16</v>
       </c>
       <c r="J148" s="4" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="K148" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="L148" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-4</v>
+      </c>
+      <c r="L148" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M148" s="7" t="n">
@@ -15039,31 +15039,31 @@
         </is>
       </c>
       <c r="P148" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q148" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R148" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S148" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="T148" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U148" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V148" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="W148" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T148" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U148" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="V148" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="W148" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X148" s="10" t="n">
         <v>5</v>
-      </c>
-      <c r="X148" s="10" t="n">
-        <v>7</v>
       </c>
       <c r="Y148" s="9" t="n">
         <v>0</v>
@@ -15087,15 +15087,15 @@
         </is>
       </c>
       <c r="C149" s="4" t="n">
-        <v>28679608</v>
+        <v>1867633</v>
       </c>
       <c r="D149" s="4" t="inlineStr">
         <is>
-          <t>Moody's India Toastmasters Club</t>
+          <t>Faridabad Toastmasters Club</t>
         </is>
       </c>
       <c r="E149" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F149" s="6" t="n">
         <v>10</v>
@@ -15109,13 +15109,13 @@
         </is>
       </c>
       <c r="I149" s="4" t="n">
-        <v>51</v>
+        <v>24</v>
       </c>
       <c r="J149" s="4" t="n">
-        <v>51</v>
+        <v>30</v>
       </c>
       <c r="K149" s="4" t="n">
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="L149" s="4" t="inlineStr">
         <is>
@@ -15136,16 +15136,16 @@
         </is>
       </c>
       <c r="P149" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q149" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R149" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S149" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T149" s="9" t="n">
         <v>0</v>
@@ -15153,20 +15153,20 @@
       <c r="U149" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V149" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W149" s="9" t="n">
-        <v>0</v>
+      <c r="V149" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W149" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="X149" s="10" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="Y149" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z149" s="9" t="n">
-        <v>0</v>
+      <c r="Z149" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA149" s="10" t="n">
         <v>1</v>
@@ -15184,15 +15184,15 @@
         </is>
       </c>
       <c r="C150" s="4" t="n">
-        <v>28679776</v>
+        <v>28679608</v>
       </c>
       <c r="D150" s="4" t="inlineStr">
         <is>
-          <t>Zuari Toastmasters Club</t>
+          <t>Moody's India Toastmasters Club</t>
         </is>
       </c>
       <c r="E150" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F150" s="6" t="n">
         <v>10</v>
@@ -15206,13 +15206,13 @@
         </is>
       </c>
       <c r="I150" s="4" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="J150" s="4" t="n">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="K150" s="4" t="n">
-        <v>-12</v>
+        <v>-37</v>
       </c>
       <c r="L150" s="8" t="inlineStr">
         <is>
@@ -15262,8 +15262,8 @@
       <c r="Y150" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z150" s="9" t="n">
-        <v>0</v>
+      <c r="Z150" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA150" s="10" t="n">
         <v>1</v>
@@ -15277,19 +15277,19 @@
       </c>
       <c r="B151" s="4" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>01</t>
         </is>
       </c>
       <c r="C151" s="4" t="n">
-        <v>28677400</v>
+        <v>28679776</v>
       </c>
       <c r="D151" s="4" t="inlineStr">
         <is>
-          <t>Carrier Toastmasters Club</t>
+          <t>Zuari Toastmasters Club</t>
         </is>
       </c>
       <c r="E151" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F151" s="6" t="n">
         <v>10</v>
@@ -15303,13 +15303,13 @@
         </is>
       </c>
       <c r="I151" s="4" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="J151" s="4" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="K151" s="4" t="n">
-        <v>1</v>
+        <v>-20</v>
       </c>
       <c r="L151" s="8" t="inlineStr">
         <is>
@@ -15348,7 +15348,7 @@
         <v>0</v>
       </c>
       <c r="V151" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W151" s="9" t="n">
         <v>0</v>
@@ -15359,8 +15359,8 @@
       <c r="Y151" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z151" s="10" t="n">
-        <v>1</v>
+      <c r="Z151" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA151" s="10" t="n">
         <v>1</v>
@@ -15378,15 +15378,15 @@
         </is>
       </c>
       <c r="C152" s="4" t="n">
-        <v>1200975</v>
+        <v>28677400</v>
       </c>
       <c r="D152" s="4" t="inlineStr">
         <is>
-          <t>Gurgaon Toastmasters Club</t>
+          <t>Carrier Toastmasters Club</t>
         </is>
       </c>
       <c r="E152" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F152" s="6" t="n">
         <v>10</v>
@@ -15400,17 +15400,17 @@
         </is>
       </c>
       <c r="I152" s="4" t="n">
-        <v>59</v>
+        <v>6</v>
       </c>
       <c r="J152" s="4" t="n">
-        <v>52</v>
+        <v>13</v>
       </c>
       <c r="K152" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="L152" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-7</v>
+      </c>
+      <c r="L152" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M152" s="7" t="n">
@@ -15436,28 +15436,28 @@
         <v>0</v>
       </c>
       <c r="S152" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="T152" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="T152" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U152" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V152" s="10" t="n">
+      <c r="V152" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="W152" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X152" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W152" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="X152" s="10" t="n">
-        <v>7</v>
-      </c>
       <c r="Y152" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z152" s="10" t="n">
-        <v>1</v>
+      <c r="Z152" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA152" s="10" t="n">
         <v>1</v>
@@ -15475,15 +15475,15 @@
         </is>
       </c>
       <c r="C153" s="4" t="n">
-        <v>28678186</v>
+        <v>1200975</v>
       </c>
       <c r="D153" s="4" t="inlineStr">
         <is>
-          <t>Gurugram Dronacharya Toastmasters Club</t>
+          <t>Gurgaon Toastmasters Club</t>
         </is>
       </c>
       <c r="E153" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F153" s="6" t="n">
         <v>10</v>
@@ -15497,13 +15497,13 @@
         </is>
       </c>
       <c r="I153" s="4" t="n">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="J153" s="4" t="n">
-        <v>14</v>
+        <v>52</v>
       </c>
       <c r="K153" s="4" t="n">
-        <v>6</v>
+        <v>-14</v>
       </c>
       <c r="L153" s="4" t="inlineStr">
         <is>
@@ -15527,16 +15527,16 @@
         <v>0</v>
       </c>
       <c r="Q153" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R153" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S153" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T153" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="T153" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U153" s="9" t="n">
         <v>0</v>
@@ -15545,10 +15545,10 @@
         <v>4</v>
       </c>
       <c r="W153" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X153" s="10" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="Y153" s="9" t="n">
         <v>0</v>
@@ -15572,11 +15572,11 @@
         </is>
       </c>
       <c r="C154" s="4" t="n">
-        <v>28678197</v>
+        <v>28678186</v>
       </c>
       <c r="D154" s="4" t="inlineStr">
         <is>
-          <t>Leaders Stories Toastmasters Club</t>
+          <t>Gurugram Dronacharya Toastmasters Club</t>
         </is>
       </c>
       <c r="E154" s="5" t="n">
@@ -15594,17 +15594,17 @@
         </is>
       </c>
       <c r="I154" s="4" t="n">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="J154" s="4" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="K154" s="4" t="n">
-        <v>18</v>
-      </c>
-      <c r="L154" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-2</v>
+      </c>
+      <c r="L154" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M154" s="7" t="n">
@@ -15621,10 +15621,10 @@
         </is>
       </c>
       <c r="P154" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q154" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R154" s="9" t="n">
         <v>0</v>
@@ -15632,20 +15632,20 @@
       <c r="S154" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T154" s="10" t="n">
-        <v>1</v>
+      <c r="T154" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U154" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V154" s="9" t="n">
-        <v>1</v>
+      <c r="V154" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W154" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X154" s="10" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="Y154" s="9" t="n">
         <v>0</v>
@@ -15669,15 +15669,15 @@
         </is>
       </c>
       <c r="C155" s="4" t="n">
-        <v>7391076</v>
+        <v>28678197</v>
       </c>
       <c r="D155" s="4" t="inlineStr">
         <is>
-          <t>Orange India Toastmasters</t>
+          <t>Leaders Stories Toastmasters Club</t>
         </is>
       </c>
       <c r="E155" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F155" s="6" t="n">
         <v>10</v>
@@ -15691,13 +15691,13 @@
         </is>
       </c>
       <c r="I155" s="4" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="J155" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K155" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L155" s="8" t="inlineStr">
         <is>
@@ -15718,7 +15718,7 @@
         </is>
       </c>
       <c r="P155" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q155" s="9" t="n">
         <v>0</v>
@@ -15729,26 +15729,26 @@
       <c r="S155" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T155" s="9" t="n">
-        <v>0</v>
+      <c r="T155" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U155" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V155" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W155" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X155" s="9" t="n">
-        <v>0</v>
+      <c r="X155" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="Y155" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z155" s="9" t="n">
-        <v>0</v>
+      <c r="Z155" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA155" s="10" t="n">
         <v>1</v>
@@ -15766,15 +15766,15 @@
         </is>
       </c>
       <c r="C156" s="4" t="n">
-        <v>6672640</v>
+        <v>7391076</v>
       </c>
       <c r="D156" s="4" t="inlineStr">
         <is>
-          <t>Siemens Tales and Tellers</t>
+          <t>Orange India Toastmasters</t>
         </is>
       </c>
       <c r="E156" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F156" s="6" t="n">
         <v>10</v>
@@ -15788,17 +15788,17 @@
         </is>
       </c>
       <c r="I156" s="4" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="J156" s="4" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="K156" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L156" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-4</v>
+      </c>
+      <c r="L156" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M156" s="7" t="n">
@@ -15838,14 +15838,14 @@
       <c r="W156" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X156" s="10" t="n">
-        <v>4</v>
+      <c r="X156" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Y156" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z156" s="10" t="n">
-        <v>1</v>
+      <c r="Z156" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA156" s="10" t="n">
         <v>1</v>
@@ -15859,19 +15859,19 @@
       </c>
       <c r="B157" s="4" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>02</t>
         </is>
       </c>
       <c r="C157" s="4" t="n">
-        <v>28676069</v>
+        <v>6672640</v>
       </c>
       <c r="D157" s="4" t="inlineStr">
         <is>
-          <t>New Gurugram Toastmasters Club</t>
+          <t>Siemens Tales and Tellers</t>
         </is>
       </c>
       <c r="E157" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F157" s="6" t="n">
         <v>10</v>
@@ -15885,17 +15885,17 @@
         </is>
       </c>
       <c r="I157" s="4" t="n">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="J157" s="4" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="K157" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="L157" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-2</v>
+      </c>
+      <c r="L157" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M157" s="7" t="n">
@@ -15912,7 +15912,7 @@
         </is>
       </c>
       <c r="P157" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q157" s="9" t="n">
         <v>0</v>
@@ -15921,10 +15921,10 @@
         <v>0</v>
       </c>
       <c r="S157" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="T157" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="T157" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U157" s="9" t="n">
         <v>0</v>
@@ -15936,7 +15936,7 @@
         <v>0</v>
       </c>
       <c r="X157" s="10" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="Y157" s="9" t="n">
         <v>0</v>
@@ -15960,15 +15960,15 @@
         </is>
       </c>
       <c r="C158" s="4" t="n">
-        <v>1345936</v>
+        <v>28681042</v>
       </c>
       <c r="D158" s="4" t="inlineStr">
         <is>
-          <t>TCS Maitree Gurgaon Toastmasters</t>
+          <t>Beyond Language Toastmasters Club</t>
         </is>
       </c>
       <c r="E158" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F158" s="6" t="n">
         <v>10</v>
@@ -15982,17 +15982,17 @@
         </is>
       </c>
       <c r="I158" s="4" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="J158" s="4" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="K158" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L158" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>0</v>
+      </c>
+      <c r="L158" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M158" s="7" t="n">
@@ -16027,19 +16027,19 @@
         <v>0</v>
       </c>
       <c r="V158" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W158" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X158" s="10" t="n">
-        <v>6</v>
+      <c r="X158" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Y158" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z158" s="9" t="n">
-        <v>0</v>
+      <c r="Z158" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="AA158" s="10" t="n">
         <v>1</v>
@@ -16057,15 +16057,15 @@
         </is>
       </c>
       <c r="C159" s="4" t="n">
-        <v>5539557</v>
+        <v>28676069</v>
       </c>
       <c r="D159" s="4" t="inlineStr">
         <is>
-          <t>The Pangram's Toastmasters Club</t>
+          <t>New Gurugram Toastmasters Club</t>
         </is>
       </c>
       <c r="E159" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F159" s="6" t="n">
         <v>10</v>
@@ -16079,17 +16079,17 @@
         </is>
       </c>
       <c r="I159" s="4" t="n">
-        <v>39</v>
+        <v>12</v>
       </c>
       <c r="J159" s="4" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="K159" s="4" t="n">
-        <v>11</v>
-      </c>
-      <c r="L159" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-13</v>
+      </c>
+      <c r="L159" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M159" s="7" t="n">
@@ -16106,16 +16106,16 @@
         </is>
       </c>
       <c r="P159" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q159" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R159" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S159" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T159" s="10" t="n">
         <v>1</v>
@@ -16126,8 +16126,8 @@
       <c r="V159" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W159" s="10" t="n">
-        <v>7</v>
+      <c r="W159" s="9" t="n">
+        <v>2</v>
       </c>
       <c r="X159" s="10" t="n">
         <v>7</v>
@@ -16154,15 +16154,15 @@
         </is>
       </c>
       <c r="C160" s="4" t="n">
-        <v>4238711</v>
+        <v>1345936</v>
       </c>
       <c r="D160" s="4" t="inlineStr">
         <is>
-          <t>Turning Point Toastmasters</t>
+          <t>TCS Maitree Gurgaon Toastmasters</t>
         </is>
       </c>
       <c r="E160" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F160" s="6" t="n">
         <v>10</v>
@@ -16176,17 +16176,17 @@
         </is>
       </c>
       <c r="I160" s="4" t="n">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="J160" s="4" t="n">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="K160" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="L160" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-5</v>
+      </c>
+      <c r="L160" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M160" s="7" t="n">
@@ -16203,10 +16203,10 @@
         </is>
       </c>
       <c r="P160" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q160" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R160" s="9" t="n">
         <v>0</v>
@@ -16220,20 +16220,20 @@
       <c r="U160" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V160" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="W160" s="10" t="n">
-        <v>5</v>
+      <c r="V160" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="W160" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="X160" s="10" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y160" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z160" s="10" t="n">
-        <v>1</v>
+      <c r="Z160" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA160" s="10" t="n">
         <v>1</v>
@@ -16247,19 +16247,19 @@
       </c>
       <c r="B161" s="4" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>03</t>
         </is>
       </c>
       <c r="C161" s="4" t="n">
-        <v>28678501</v>
+        <v>5539557</v>
       </c>
       <c r="D161" s="4" t="inlineStr">
         <is>
-          <t>Toast the Most - GGN Club A</t>
+          <t>The Pangram's Toastmasters Club</t>
         </is>
       </c>
       <c r="E161" s="5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F161" s="6" t="n">
         <v>10</v>
@@ -16273,13 +16273,13 @@
         </is>
       </c>
       <c r="I161" s="4" t="n">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="J161" s="4" t="n">
-        <v>41</v>
+        <v>28</v>
       </c>
       <c r="K161" s="4" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="L161" s="4" t="inlineStr">
         <is>
@@ -16311,17 +16311,17 @@
       <c r="S161" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T161" s="9" t="n">
-        <v>0</v>
+      <c r="T161" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U161" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V161" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W161" s="9" t="n">
-        <v>0</v>
+      <c r="V161" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W161" s="10" t="n">
+        <v>8</v>
       </c>
       <c r="X161" s="10" t="n">
         <v>7</v>
@@ -16344,19 +16344,19 @@
       </c>
       <c r="B162" s="4" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>03</t>
         </is>
       </c>
       <c r="C162" s="4" t="n">
-        <v>28678502</v>
+        <v>4238711</v>
       </c>
       <c r="D162" s="4" t="inlineStr">
         <is>
-          <t>Toast the Most - GGN Club B</t>
+          <t>Turning Point Toastmasters</t>
         </is>
       </c>
       <c r="E162" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F162" s="6" t="n">
         <v>10</v>
@@ -16370,17 +16370,17 @@
         </is>
       </c>
       <c r="I162" s="4" t="n">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="J162" s="4" t="n">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="K162" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L162" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-5</v>
+      </c>
+      <c r="L162" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M162" s="7" t="n">
@@ -16397,10 +16397,10 @@
         </is>
       </c>
       <c r="P162" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q162" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R162" s="9" t="n">
         <v>0</v>
@@ -16414,14 +16414,14 @@
       <c r="U162" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V162" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W162" s="9" t="n">
-        <v>0</v>
+      <c r="V162" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W162" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="X162" s="10" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y162" s="9" t="n">
         <v>0</v>
@@ -16445,15 +16445,15 @@
         </is>
       </c>
       <c r="C163" s="4" t="n">
-        <v>28676260</v>
+        <v>28678501</v>
       </c>
       <c r="D163" s="4" t="inlineStr">
         <is>
-          <t>Toastmasters at Gartner India</t>
+          <t>Toast the Most - GGN Club A</t>
         </is>
       </c>
       <c r="E163" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F163" s="6" t="n">
         <v>10</v>
@@ -16467,17 +16467,17 @@
         </is>
       </c>
       <c r="I163" s="4" t="n">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="J163" s="4" t="n">
-        <v>9</v>
+        <v>41</v>
       </c>
       <c r="K163" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L163" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>-12</v>
+      </c>
+      <c r="L163" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M163" s="7" t="n">
@@ -16494,10 +16494,10 @@
         </is>
       </c>
       <c r="P163" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q163" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R163" s="9" t="n">
         <v>0</v>
@@ -16512,19 +16512,19 @@
         <v>0</v>
       </c>
       <c r="V163" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W163" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X163" s="10" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="Y163" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z163" s="9" t="n">
-        <v>0</v>
+      <c r="Z163" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA163" s="10" t="n">
         <v>1</v>
@@ -16542,15 +16542,15 @@
         </is>
       </c>
       <c r="C164" s="4" t="n">
-        <v>28678892</v>
+        <v>28678502</v>
       </c>
       <c r="D164" s="4" t="inlineStr">
         <is>
-          <t>Toastmasters BSC Gurgaon</t>
+          <t>Toast the Most - GGN Club B</t>
         </is>
       </c>
       <c r="E164" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F164" s="6" t="n">
         <v>10</v>
@@ -16564,17 +16564,17 @@
         </is>
       </c>
       <c r="I164" s="4" t="n">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="J164" s="4" t="n">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="K164" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L164" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>-4</v>
+      </c>
+      <c r="L164" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M164" s="7" t="n">
@@ -16614,14 +16614,14 @@
       <c r="W164" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X164" s="9" t="n">
-        <v>2</v>
+      <c r="X164" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="Y164" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z164" s="9" t="n">
-        <v>0</v>
+      <c r="Z164" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA164" s="10" t="n">
         <v>1</v>
@@ -16639,15 +16639,15 @@
         </is>
       </c>
       <c r="C165" s="4" t="n">
-        <v>7428610</v>
+        <v>28676260</v>
       </c>
       <c r="D165" s="4" t="inlineStr">
         <is>
-          <t>Xceedance Tikri Toastmasters</t>
+          <t>Toastmasters at Gartner India</t>
         </is>
       </c>
       <c r="E165" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F165" s="6" t="n">
         <v>10</v>
@@ -16661,17 +16661,17 @@
         </is>
       </c>
       <c r="I165" s="4" t="n">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="J165" s="4" t="n">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="K165" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L165" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-2</v>
+      </c>
+      <c r="L165" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M165" s="7" t="n">
@@ -16688,7 +16688,7 @@
         </is>
       </c>
       <c r="P165" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q165" s="9" t="n">
         <v>0</v>
@@ -16706,26 +16706,220 @@
         <v>0</v>
       </c>
       <c r="V165" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W165" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X165" s="9" t="n">
-        <v>0</v>
+      <c r="X165" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y165" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z165" s="10" t="n">
-        <v>1</v>
+      <c r="Z165" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA165" s="10" t="n">
         <v>1</v>
       </c>
     </row>
+    <row r="166">
+      <c r="A166" s="4" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="B166" s="4" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="C166" s="4" t="n">
+        <v>28678892</v>
+      </c>
+      <c r="D166" s="4" t="inlineStr">
+        <is>
+          <t>Toastmasters BSC Gurgaon</t>
+        </is>
+      </c>
+      <c r="E166" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F166" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="G166" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="H166" s="4" t="inlineStr">
+        <is>
+          <t>Smedley</t>
+        </is>
+      </c>
+      <c r="I166" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J166" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="K166" s="4" t="n">
+        <v>-18</v>
+      </c>
+      <c r="L166" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M166" s="7" t="n">
+        <v>46446</v>
+      </c>
+      <c r="N166" s="4" t="inlineStr">
+        <is>
+          <t>Officers trained Nov-Feb</t>
+        </is>
+      </c>
+      <c r="O166" s="8" t="inlineStr">
+        <is>
+          <t>not yet</t>
+        </is>
+      </c>
+      <c r="P166" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q166" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R166" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S166" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T166" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U166" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V166" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W166" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X166" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y166" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z166" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA166" s="10" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="4" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="B167" s="4" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="C167" s="4" t="n">
+        <v>7428610</v>
+      </c>
+      <c r="D167" s="4" t="inlineStr">
+        <is>
+          <t>Xceedance Tikri Toastmasters</t>
+        </is>
+      </c>
+      <c r="E167" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="F167" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="G167" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="H167" s="4" t="inlineStr">
+        <is>
+          <t>Smedley</t>
+        </is>
+      </c>
+      <c r="I167" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="J167" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="K167" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L167" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="M167" s="7" t="n">
+        <v>46446</v>
+      </c>
+      <c r="N167" s="4" t="inlineStr">
+        <is>
+          <t>Officers trained Nov-Feb</t>
+        </is>
+      </c>
+      <c r="O167" s="8" t="inlineStr">
+        <is>
+          <t>not yet</t>
+        </is>
+      </c>
+      <c r="P167" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q167" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R167" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S167" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T167" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U167" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V167" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W167" s="10" t="n">
+        <v>14</v>
+      </c>
+      <c r="X167" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y167" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z167" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA167" s="10" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AA165"/>
+  <autoFilter ref="A1:AA167"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -16827,7 +17021,7 @@
         <v>1</v>
       </c>
       <c r="I2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
@@ -16878,7 +17072,7 @@
         <v>5</v>
       </c>
       <c r="D4" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -16893,7 +17087,7 @@
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
@@ -16926,7 +17120,7 @@
         <v>1</v>
       </c>
       <c r="I5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -16944,7 +17138,7 @@
         <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="E6" t="n">
         <v>2</v>
@@ -16992,7 +17186,7 @@
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -17025,7 +17219,7 @@
         <v>1</v>
       </c>
       <c r="I8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -17043,7 +17237,7 @@
         <v>4</v>
       </c>
       <c r="D9" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -17058,7 +17252,7 @@
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -17091,7 +17285,7 @@
         <v>1</v>
       </c>
       <c r="I10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11">
@@ -17142,7 +17336,7 @@
         <v>6</v>
       </c>
       <c r="D12" t="n">
-        <v>0.67</v>
+        <v>1.17</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -17157,7 +17351,7 @@
         <v>1</v>
       </c>
       <c r="I12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
@@ -17190,7 +17384,7 @@
         <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -17223,7 +17417,7 @@
         <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -17256,7 +17450,7 @@
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16">
@@ -17274,7 +17468,7 @@
         <v>5</v>
       </c>
       <c r="D16" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -17289,7 +17483,7 @@
         <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -17307,14 +17501,14 @@
         <v>5</v>
       </c>
       <c r="D17" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="E17" t="n">
+        <v>2</v>
+      </c>
+      <c r="F17" t="n">
         <v>3</v>
       </c>
-      <c r="E17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" t="n">
-        <v>5</v>
-      </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
@@ -17322,7 +17516,7 @@
         <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18">
@@ -17340,7 +17534,7 @@
         <v>6</v>
       </c>
       <c r="D18" t="n">
-        <v>1.33</v>
+        <v>1.83</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -17355,7 +17549,7 @@
         <v>2</v>
       </c>
       <c r="I18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -17388,7 +17582,7 @@
         <v>1</v>
       </c>
       <c r="I19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -17403,16 +17597,16 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D20" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -17421,7 +17615,7 @@
         <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21">
@@ -17439,7 +17633,7 @@
         <v>4</v>
       </c>
       <c r="D21" t="n">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="E21" t="n">
         <v>1</v>
@@ -17454,7 +17648,7 @@
         <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22">
@@ -17472,7 +17666,7 @@
         <v>4</v>
       </c>
       <c r="D22" t="n">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -17487,7 +17681,7 @@
         <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23">
@@ -17505,7 +17699,7 @@
         <v>5</v>
       </c>
       <c r="D23" t="n">
-        <v>2.8</v>
+        <v>3.4</v>
       </c>
       <c r="E23" t="n">
         <v>1</v>
@@ -17520,7 +17714,7 @@
         <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24">
@@ -17553,7 +17747,7 @@
         <v>4</v>
       </c>
       <c r="I24" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -17586,7 +17780,7 @@
         <v>0</v>
       </c>
       <c r="I25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -17619,7 +17813,7 @@
         <v>1</v>
       </c>
       <c r="I26" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -17637,7 +17831,7 @@
         <v>4</v>
       </c>
       <c r="D27" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>
@@ -17652,7 +17846,7 @@
         <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="28">
@@ -17670,7 +17864,7 @@
         <v>6</v>
       </c>
       <c r="D28" t="n">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="E28" t="n">
         <v>1</v>
@@ -17685,7 +17879,7 @@
         <v>1</v>
       </c>
       <c r="I28" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -17736,7 +17930,7 @@
         <v>5</v>
       </c>
       <c r="D30" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="E30" t="n">
         <v>0</v>
@@ -17751,7 +17945,7 @@
         <v>1</v>
       </c>
       <c r="I30" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="31">
@@ -17769,7 +17963,7 @@
         <v>5</v>
       </c>
       <c r="D31" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="E31" t="n">
         <v>0</v>
@@ -17784,7 +17978,7 @@
         <v>0</v>
       </c>
       <c r="I31" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -17817,7 +18011,7 @@
         <v>0</v>
       </c>
       <c r="I32" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33">
@@ -17832,16 +18026,16 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D33" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="E33" t="n">
         <v>0</v>
       </c>
       <c r="F33" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -17850,7 +18044,7 @@
         <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="34">
@@ -17868,7 +18062,7 @@
         <v>5</v>
       </c>
       <c r="D34" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="E34" t="n">
         <v>0</v>

--- a/docs/d/224/inyear.xlsx
+++ b/docs/d/224/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:33 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:39 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/224/inyear.xlsx
+++ b/docs/d/224/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:39 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 10:56 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/224/inyear.xlsx
+++ b/docs/d/224/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 10:56 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 11:03 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/224/inyear.xlsx
+++ b/docs/d/224/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 11:03 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 13:06 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/224/inyear.xlsx
+++ b/docs/d/224/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 13:06 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 17-Oct-2026. Built 2026-10-18 11:32 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>262 days remain until 30 June 2027, when these scores become final.</t>
+          <t>255 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (81 days) - 18 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (74 days) - 18 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (140 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (133 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (171 days) - 74 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (164 days) - 74 clubs short</t>
         </is>
       </c>
     </row>
@@ -974,7 +974,7 @@
         </is>
       </c>
       <c r="P3" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q3" s="9" t="n">
         <v>0</v>
@@ -1529,13 +1529,13 @@
         </is>
       </c>
       <c r="I9" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J9" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L9" s="8" t="inlineStr">
         <is>
@@ -1577,7 +1577,7 @@
         <v>4</v>
       </c>
       <c r="W9" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X9" s="10" t="n">
         <v>6</v>
@@ -1612,7 +1612,7 @@
         </is>
       </c>
       <c r="E10" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F10" s="6" t="n">
         <v>10</v>
@@ -1626,13 +1626,13 @@
         </is>
       </c>
       <c r="I10" s="4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J10" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
@@ -1673,8 +1673,8 @@
       <c r="V10" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W10" s="9" t="n">
-        <v>3</v>
+      <c r="W10" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="X10" s="10" t="n">
         <v>5</v>
@@ -2776,7 +2776,7 @@
         </is>
       </c>
       <c r="E22" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F22" s="6" t="n">
         <v>10</v>
@@ -2790,13 +2790,13 @@
         </is>
       </c>
       <c r="I22" s="4" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J22" s="4" t="n">
         <v>38</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="L22" s="4" t="inlineStr">
         <is>
@@ -2837,8 +2837,8 @@
       <c r="V22" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W22" s="9" t="n">
-        <v>3</v>
+      <c r="W22" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="X22" s="10" t="n">
         <v>7</v>
@@ -3399,7 +3399,7 @@
         </is>
       </c>
       <c r="P28" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q28" s="9" t="n">
         <v>0</v>
@@ -4231,7 +4231,7 @@
         </is>
       </c>
       <c r="E37" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F37" s="6" t="n">
         <v>10</v>
@@ -4271,8 +4271,8 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P37" s="9" t="n">
-        <v>3</v>
+      <c r="P37" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Q37" s="9" t="n">
         <v>0</v>
@@ -4633,13 +4633,13 @@
         </is>
       </c>
       <c r="I41" s="4" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J41" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K41" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L41" s="4" t="inlineStr">
         <is>
@@ -4660,7 +4660,7 @@
         </is>
       </c>
       <c r="P41" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q41" s="9" t="n">
         <v>0</v>
@@ -4681,7 +4681,7 @@
         <v>4</v>
       </c>
       <c r="W41" s="10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X41" s="10" t="n">
         <v>6</v>
@@ -4730,13 +4730,13 @@
         </is>
       </c>
       <c r="I42" s="4" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="J42" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K42" s="4" t="n">
-        <v>-16</v>
+        <v>-6</v>
       </c>
       <c r="L42" s="8" t="inlineStr">
         <is>
@@ -6088,13 +6088,13 @@
         </is>
       </c>
       <c r="I56" s="4" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="J56" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K56" s="4" t="n">
-        <v>-7</v>
+        <v>-5</v>
       </c>
       <c r="L56" s="8" t="inlineStr">
         <is>
@@ -6136,7 +6136,7 @@
         <v>4</v>
       </c>
       <c r="W56" s="10" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X56" s="10" t="n">
         <v>7</v>
@@ -6379,13 +6379,13 @@
         </is>
       </c>
       <c r="I59" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J59" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K59" s="4" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="L59" s="8" t="inlineStr">
         <is>
@@ -7141,7 +7141,7 @@
         </is>
       </c>
       <c r="E67" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F67" s="6" t="n">
         <v>10</v>
@@ -7155,13 +7155,13 @@
         </is>
       </c>
       <c r="I67" s="4" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="J67" s="4" t="n">
         <v>33</v>
       </c>
       <c r="K67" s="4" t="n">
-        <v>-5</v>
+        <v>-3</v>
       </c>
       <c r="L67" s="4" t="inlineStr">
         <is>
@@ -7181,8 +7181,8 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P67" s="9" t="n">
-        <v>3</v>
+      <c r="P67" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Q67" s="9" t="n">
         <v>1</v>
@@ -7191,7 +7191,7 @@
         <v>0</v>
       </c>
       <c r="S67" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T67" s="10" t="n">
         <v>1</v>
@@ -7203,7 +7203,7 @@
         <v>4</v>
       </c>
       <c r="W67" s="10" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="X67" s="10" t="n">
         <v>6</v>
@@ -7349,13 +7349,13 @@
         </is>
       </c>
       <c r="I69" s="4" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="J69" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K69" s="4" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="L69" s="8" t="inlineStr">
         <is>
@@ -7397,7 +7397,7 @@
         <v>4</v>
       </c>
       <c r="W69" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X69" s="10" t="n">
         <v>5</v>
@@ -7964,7 +7964,7 @@
         <v>2</v>
       </c>
       <c r="R75" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S75" s="9" t="n">
         <v>0</v>
@@ -8222,13 +8222,13 @@
         </is>
       </c>
       <c r="I78" s="4" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J78" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K78" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L78" s="4" t="inlineStr">
         <is>
@@ -8416,13 +8416,13 @@
         </is>
       </c>
       <c r="I80" s="4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J80" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K80" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L80" s="8" t="inlineStr">
         <is>
@@ -8464,7 +8464,7 @@
         <v>4</v>
       </c>
       <c r="W80" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X80" s="10" t="n">
         <v>5</v>
@@ -10245,7 +10245,7 @@
         </is>
       </c>
       <c r="E99" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F99" s="6" t="n">
         <v>10</v>
@@ -10288,8 +10288,8 @@
       <c r="P99" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="Q99" s="9" t="n">
-        <v>1</v>
+      <c r="Q99" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R99" s="9" t="n">
         <v>0</v>
@@ -10453,13 +10453,13 @@
         </is>
       </c>
       <c r="I101" s="4" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J101" s="4" t="n">
         <v>33</v>
       </c>
       <c r="K101" s="4" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="L101" s="4" t="inlineStr">
         <is>
@@ -10550,13 +10550,13 @@
         </is>
       </c>
       <c r="I102" s="4" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="J102" s="4" t="n">
         <v>31</v>
       </c>
       <c r="K102" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L102" s="4" t="inlineStr">
         <is>
@@ -12684,13 +12684,13 @@
         </is>
       </c>
       <c r="I124" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J124" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K124" s="4" t="n">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="L124" s="8" t="inlineStr">
         <is>
@@ -12729,7 +12729,7 @@
         <v>0</v>
       </c>
       <c r="V124" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W124" s="9" t="n">
         <v>0</v>
@@ -12878,13 +12878,13 @@
         </is>
       </c>
       <c r="I126" s="4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J126" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K126" s="4" t="n">
-        <v>-9</v>
+        <v>-8</v>
       </c>
       <c r="L126" s="8" t="inlineStr">
         <is>
@@ -13446,7 +13446,7 @@
         </is>
       </c>
       <c r="E132" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F132" s="6" t="n">
         <v>10</v>
@@ -13460,13 +13460,13 @@
         </is>
       </c>
       <c r="I132" s="4" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="J132" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K132" s="4" t="n">
-        <v>-4</v>
+        <v>-1</v>
       </c>
       <c r="L132" s="8" t="inlineStr">
         <is>
@@ -13504,11 +13504,11 @@
       <c r="U132" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V132" s="9" t="n">
-        <v>3</v>
+      <c r="V132" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W132" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X132" s="10" t="n">
         <v>7</v>
@@ -13848,13 +13848,13 @@
         </is>
       </c>
       <c r="I136" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J136" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K136" s="4" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="L136" s="8" t="inlineStr">
         <is>
@@ -13972,7 +13972,7 @@
         </is>
       </c>
       <c r="P137" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q137" s="9" t="n">
         <v>1</v>
@@ -14951,7 +14951,7 @@
         <v>0</v>
       </c>
       <c r="S147" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T147" s="9" t="n">
         <v>0</v>
@@ -15095,7 +15095,7 @@
         </is>
       </c>
       <c r="E149" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F149" s="6" t="n">
         <v>10</v>
@@ -15136,7 +15136,7 @@
         </is>
       </c>
       <c r="P149" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q149" s="9" t="n">
         <v>1</v>
@@ -15147,8 +15147,8 @@
       <c r="S149" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="T149" s="9" t="n">
-        <v>0</v>
+      <c r="T149" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U149" s="9" t="n">
         <v>0</v>
@@ -16065,7 +16065,7 @@
         </is>
       </c>
       <c r="E159" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F159" s="6" t="n">
         <v>10</v>
@@ -16079,13 +16079,13 @@
         </is>
       </c>
       <c r="I159" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J159" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K159" s="4" t="n">
-        <v>-13</v>
+        <v>-12</v>
       </c>
       <c r="L159" s="8" t="inlineStr">
         <is>
@@ -16120,8 +16120,8 @@
       <c r="T159" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U159" s="9" t="n">
-        <v>0</v>
+      <c r="U159" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V159" s="10" t="n">
         <v>4</v>
@@ -16370,13 +16370,13 @@
         </is>
       </c>
       <c r="I162" s="4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J162" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K162" s="4" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="L162" s="8" t="inlineStr">
         <is>
@@ -17039,7 +17039,7 @@
         <v>6</v>
       </c>
       <c r="D3" t="n">
-        <v>1.67</v>
+        <v>1.83</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -17105,13 +17105,13 @@
         <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -17237,7 +17237,7 @@
         <v>4</v>
       </c>
       <c r="D9" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -17435,7 +17435,7 @@
         <v>4</v>
       </c>
       <c r="D15" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="E15" t="n">
         <v>1</v>
@@ -17666,7 +17666,7 @@
         <v>4</v>
       </c>
       <c r="D22" t="n">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -17864,7 +17864,7 @@
         <v>6</v>
       </c>
       <c r="D28" t="n">
-        <v>1.17</v>
+        <v>1.33</v>
       </c>
       <c r="E28" t="n">
         <v>1</v>
@@ -17963,7 +17963,7 @@
         <v>5</v>
       </c>
       <c r="D31" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="E31" t="n">
         <v>0</v>
@@ -18029,7 +18029,7 @@
         <v>5</v>
       </c>
       <c r="D33" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="E33" t="n">
         <v>0</v>

--- a/docs/d/224/inyear.xlsx
+++ b/docs/d/224/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 17-Oct-2026. Built 2026-10-18 11:32 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 24-Oct-2026. Built 2026-10-25 11:50 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>255 days remain until 30 June 2027, when these scores become final.</t>
+          <t>248 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (74 days) - 18 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (67 days) - 18 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (133 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (126 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (164 days) - 74 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (157 days) - 74 clubs short</t>
         </is>
       </c>
     </row>
@@ -2347,7 +2347,7 @@
         <v>1</v>
       </c>
       <c r="U17" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="V17" s="9" t="n">
         <v>0</v>
@@ -3472,10 +3472,10 @@
         <v>11</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-10</v>
+        <v>-12</v>
       </c>
       <c r="L29" s="8" t="inlineStr">
         <is>
@@ -3857,13 +3857,13 @@
         </is>
       </c>
       <c r="I33" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J33" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-8</v>
+        <v>-7</v>
       </c>
       <c r="L33" s="8" t="inlineStr">
         <is>
@@ -4231,7 +4231,7 @@
         </is>
       </c>
       <c r="E37" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F37" s="6" t="n">
         <v>10</v>
@@ -4274,8 +4274,8 @@
       <c r="P37" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="Q37" s="9" t="n">
-        <v>0</v>
+      <c r="Q37" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R37" s="9" t="n">
         <v>0</v>
@@ -4536,13 +4536,13 @@
         </is>
       </c>
       <c r="I40" s="4" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J40" s="4" t="n">
         <v>44</v>
       </c>
       <c r="K40" s="4" t="n">
-        <v>-14</v>
+        <v>-13</v>
       </c>
       <c r="L40" s="4" t="inlineStr">
         <is>
@@ -4730,17 +4730,17 @@
         </is>
       </c>
       <c r="I42" s="4" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="J42" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K42" s="4" t="n">
-        <v>-6</v>
-      </c>
-      <c r="L42" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>-3</v>
+      </c>
+      <c r="L42" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M42" s="7" t="n">
@@ -5797,13 +5797,13 @@
         </is>
       </c>
       <c r="I53" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J53" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K53" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L53" s="8" t="inlineStr">
         <is>
@@ -5845,7 +5845,7 @@
         <v>4</v>
       </c>
       <c r="W53" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X53" s="10" t="n">
         <v>7</v>
@@ -7482,13 +7482,13 @@
         <v>0</v>
       </c>
       <c r="S70" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T70" s="10" t="n">
         <v>1</v>
       </c>
       <c r="U70" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V70" s="9" t="n">
         <v>3</v>
@@ -8446,7 +8446,7 @@
         <v>4</v>
       </c>
       <c r="Q80" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R80" s="9" t="n">
         <v>0</v>
@@ -8540,7 +8540,7 @@
         </is>
       </c>
       <c r="P81" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q81" s="9" t="n">
         <v>0</v>
@@ -8998,17 +8998,17 @@
         </is>
       </c>
       <c r="I86" s="4" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J86" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K86" s="4" t="n">
-        <v>-5</v>
-      </c>
-      <c r="L86" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>-2</v>
+      </c>
+      <c r="L86" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M86" s="7" t="n">
@@ -9046,7 +9046,7 @@
         <v>4</v>
       </c>
       <c r="W86" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="X86" s="10" t="n">
         <v>4</v>
@@ -9122,7 +9122,7 @@
         </is>
       </c>
       <c r="P87" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q87" s="9" t="n">
         <v>0</v>
@@ -9968,13 +9968,13 @@
         </is>
       </c>
       <c r="I96" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J96" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K96" s="4" t="n">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="L96" s="8" t="inlineStr">
         <is>
@@ -10013,7 +10013,7 @@
         <v>0</v>
       </c>
       <c r="V96" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W96" s="9" t="n">
         <v>0</v>
@@ -10051,7 +10051,7 @@
         </is>
       </c>
       <c r="E97" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F97" s="6" t="n">
         <v>10</v>
@@ -10095,7 +10095,7 @@
         <v>1</v>
       </c>
       <c r="Q97" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R97" s="9" t="n">
         <v>0</v>
@@ -10103,8 +10103,8 @@
       <c r="S97" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="T97" s="9" t="n">
-        <v>0</v>
+      <c r="T97" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U97" s="9" t="n">
         <v>0</v>
@@ -10453,13 +10453,13 @@
         </is>
       </c>
       <c r="I101" s="4" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="J101" s="4" t="n">
         <v>33</v>
       </c>
       <c r="K101" s="4" t="n">
-        <v>-4</v>
+        <v>-2</v>
       </c>
       <c r="L101" s="4" t="inlineStr">
         <is>
@@ -10480,7 +10480,7 @@
         </is>
       </c>
       <c r="P101" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q101" s="9" t="n">
         <v>0</v>
@@ -10501,7 +10501,7 @@
         <v>4</v>
       </c>
       <c r="W101" s="10" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="X101" s="10" t="n">
         <v>7</v>
@@ -12573,7 +12573,7 @@
         </is>
       </c>
       <c r="E123" s="5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F123" s="6" t="n">
         <v>10</v>
@@ -12587,10 +12587,10 @@
         </is>
       </c>
       <c r="I123" s="4" t="n">
+        <v>54</v>
+      </c>
+      <c r="J123" s="4" t="n">
         <v>53</v>
-      </c>
-      <c r="J123" s="4" t="n">
-        <v>52</v>
       </c>
       <c r="K123" s="4" t="n">
         <v>1</v>
@@ -12613,8 +12613,8 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P123" s="9" t="n">
-        <v>3</v>
+      <c r="P123" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="Q123" s="10" t="n">
         <v>2</v>
@@ -12670,7 +12670,7 @@
         </is>
       </c>
       <c r="E124" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F124" s="6" t="n">
         <v>10</v>
@@ -12722,8 +12722,8 @@
       <c r="S124" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T124" s="9" t="n">
-        <v>0</v>
+      <c r="T124" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U124" s="9" t="n">
         <v>0</v>
@@ -13848,13 +13848,13 @@
         </is>
       </c>
       <c r="I136" s="4" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="J136" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K136" s="4" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="L136" s="8" t="inlineStr">
         <is>
@@ -13945,13 +13945,13 @@
         </is>
       </c>
       <c r="I137" s="4" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="J137" s="4" t="n">
         <v>38</v>
       </c>
       <c r="K137" s="4" t="n">
-        <v>-6</v>
+        <v>-3</v>
       </c>
       <c r="L137" s="4" t="inlineStr">
         <is>
@@ -13981,7 +13981,7 @@
         <v>0</v>
       </c>
       <c r="S137" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T137" s="9" t="n">
         <v>0</v>
@@ -13993,7 +13993,7 @@
         <v>4</v>
       </c>
       <c r="W137" s="10" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="X137" s="10" t="n">
         <v>7</v>
@@ -14166,7 +14166,7 @@
         </is>
       </c>
       <c r="P139" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q139" s="10" t="n">
         <v>2</v>
@@ -14236,13 +14236,13 @@
         </is>
       </c>
       <c r="I140" s="4" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J140" s="4" t="n">
         <v>40</v>
       </c>
       <c r="K140" s="4" t="n">
-        <v>-40</v>
+        <v>-31</v>
       </c>
       <c r="L140" s="8" t="inlineStr">
         <is>
@@ -15524,7 +15524,7 @@
         </is>
       </c>
       <c r="P153" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q153" s="9" t="n">
         <v>0</v>
@@ -17237,7 +17237,7 @@
         <v>4</v>
       </c>
       <c r="D9" t="n">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -17285,7 +17285,7 @@
         <v>1</v>
       </c>
       <c r="I10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11">
@@ -17582,7 +17582,7 @@
         <v>1</v>
       </c>
       <c r="I19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20">
@@ -17633,7 +17633,7 @@
         <v>4</v>
       </c>
       <c r="D21" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="E21" t="n">
         <v>1</v>
@@ -17798,7 +17798,7 @@
         <v>7</v>
       </c>
       <c r="D26" t="n">
-        <v>1.57</v>
+        <v>1.86</v>
       </c>
       <c r="E26" t="n">
         <v>1</v>
